--- a/tests/scen_results_test_2025_stillbirths.xlsx
+++ b/tests/scen_results_test_2025_stillbirths.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="768" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1015" uniqueCount="96">
   <si>
     <t>Version</t>
   </si>
@@ -28,7 +28,7 @@
     <t>2.0.11</t>
   </si>
   <si>
-    <t>2025-06-24</t>
+    <t>2025-06-30</t>
   </si>
   <si>
     <t>Scenario</t>
@@ -40,7 +40,7 @@
     <t>Outcome</t>
   </si>
   <si>
-    <t>Total</t>
+    <t>Cumulative</t>
   </si>
   <si>
     <t>Baseline</t>
@@ -292,10 +292,10 @@
     <t>Economic cost of child anemia (discounted)</t>
   </si>
   <si>
-    <t>Economic benefits of EBF (discounted)</t>
+    <t>Economic benefits of early breastfeeding (discounted)</t>
   </si>
   <si>
-    <t>Economic cost of low birth weight chidren (discounted)</t>
+    <t>Economic cost of low birth weight children (discounted)</t>
   </si>
   <si>
     <t>Economic cost of maternal deaths (discounted)</t>
@@ -803,7 +803,9 @@
       </c>
     </row>
     <row r="3" spans="1:18">
-      <c r="A3" s="2"/>
+      <c r="A3" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B3" s="3" t="s">
         <v>9</v>
       </c>
@@ -857,7 +859,9 @@
       </c>
     </row>
     <row r="4" spans="1:18">
-      <c r="A4" s="2"/>
+      <c r="A4" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B4" s="3" t="s">
         <v>9</v>
       </c>
@@ -911,7 +915,9 @@
       </c>
     </row>
     <row r="5" spans="1:18">
-      <c r="A5" s="2"/>
+      <c r="A5" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B5" s="3" t="s">
         <v>9</v>
       </c>
@@ -965,7 +971,9 @@
       </c>
     </row>
     <row r="6" spans="1:18">
-      <c r="A6" s="2"/>
+      <c r="A6" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B6" s="3" t="s">
         <v>9</v>
       </c>
@@ -1019,7 +1027,9 @@
       </c>
     </row>
     <row r="7" spans="1:18">
-      <c r="A7" s="2"/>
+      <c r="A7" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
@@ -1073,7 +1083,9 @@
       </c>
     </row>
     <row r="8" spans="1:18">
-      <c r="A8" s="2"/>
+      <c r="A8" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
@@ -1127,7 +1139,9 @@
       </c>
     </row>
     <row r="9" spans="1:18">
-      <c r="A9" s="2"/>
+      <c r="A9" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
@@ -1181,7 +1195,9 @@
       </c>
     </row>
     <row r="10" spans="1:18">
-      <c r="A10" s="2"/>
+      <c r="A10" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
@@ -1235,7 +1251,9 @@
       </c>
     </row>
     <row r="11" spans="1:18">
-      <c r="A11" s="2"/>
+      <c r="A11" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B11" s="3" t="s">
         <v>9</v>
       </c>
@@ -1289,7 +1307,9 @@
       </c>
     </row>
     <row r="12" spans="1:18">
-      <c r="A12" s="2"/>
+      <c r="A12" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B12" s="3" t="s">
         <v>9</v>
       </c>
@@ -1343,7 +1363,9 @@
       </c>
     </row>
     <row r="13" spans="1:18">
-      <c r="A13" s="2"/>
+      <c r="A13" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B13" s="3" t="s">
         <v>9</v>
       </c>
@@ -1397,7 +1419,9 @@
       </c>
     </row>
     <row r="14" spans="1:18">
-      <c r="A14" s="2"/>
+      <c r="A14" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B14" s="3" t="s">
         <v>9</v>
       </c>
@@ -1451,7 +1475,9 @@
       </c>
     </row>
     <row r="15" spans="1:18">
-      <c r="A15" s="2"/>
+      <c r="A15" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B15" s="3" t="s">
         <v>9</v>
       </c>
@@ -1505,7 +1531,9 @@
       </c>
     </row>
     <row r="16" spans="1:18">
-      <c r="A16" s="2"/>
+      <c r="A16" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B16" s="3" t="s">
         <v>9</v>
       </c>
@@ -1559,7 +1587,9 @@
       </c>
     </row>
     <row r="17" spans="1:18">
-      <c r="A17" s="2"/>
+      <c r="A17" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B17" s="3" t="s">
         <v>9</v>
       </c>
@@ -1613,7 +1643,9 @@
       </c>
     </row>
     <row r="18" spans="1:18">
-      <c r="A18" s="2"/>
+      <c r="A18" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B18" s="3" t="s">
         <v>9</v>
       </c>
@@ -1667,7 +1699,9 @@
       </c>
     </row>
     <row r="19" spans="1:18">
-      <c r="A19" s="2"/>
+      <c r="A19" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B19" s="3" t="s">
         <v>9</v>
       </c>
@@ -1721,7 +1755,9 @@
       </c>
     </row>
     <row r="20" spans="1:18">
-      <c r="A20" s="2"/>
+      <c r="A20" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B20" s="3" t="s">
         <v>9</v>
       </c>
@@ -1775,7 +1811,9 @@
       </c>
     </row>
     <row r="21" spans="1:18">
-      <c r="A21" s="2"/>
+      <c r="A21" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B21" s="3" t="s">
         <v>9</v>
       </c>
@@ -1829,7 +1867,9 @@
       </c>
     </row>
     <row r="22" spans="1:18">
-      <c r="A22" s="2"/>
+      <c r="A22" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B22" s="3" t="s">
         <v>9</v>
       </c>
@@ -1883,7 +1923,9 @@
       </c>
     </row>
     <row r="23" spans="1:18">
-      <c r="A23" s="2"/>
+      <c r="A23" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B23" s="3" t="s">
         <v>9</v>
       </c>
@@ -1937,7 +1979,9 @@
       </c>
     </row>
     <row r="24" spans="1:18">
-      <c r="A24" s="2"/>
+      <c r="A24" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B24" s="3" t="s">
         <v>9</v>
       </c>
@@ -1991,7 +2035,9 @@
       </c>
     </row>
     <row r="25" spans="1:18">
-      <c r="A25" s="2"/>
+      <c r="A25" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B25" s="3" t="s">
         <v>9</v>
       </c>
@@ -2045,7 +2091,9 @@
       </c>
     </row>
     <row r="26" spans="1:18">
-      <c r="A26" s="2"/>
+      <c r="A26" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B26" s="3" t="s">
         <v>9</v>
       </c>
@@ -2099,7 +2147,9 @@
       </c>
     </row>
     <row r="27" spans="1:18">
-      <c r="A27" s="2"/>
+      <c r="A27" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B27" s="3" t="s">
         <v>9</v>
       </c>
@@ -2153,7 +2203,9 @@
       </c>
     </row>
     <row r="28" spans="1:18">
-      <c r="A28" s="2"/>
+      <c r="A28" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B28" s="3" t="s">
         <v>9</v>
       </c>
@@ -2207,7 +2259,9 @@
       </c>
     </row>
     <row r="29" spans="1:18">
-      <c r="A29" s="2"/>
+      <c r="A29" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B29" s="3" t="s">
         <v>9</v>
       </c>
@@ -2333,7 +2387,9 @@
       </c>
     </row>
     <row r="32" spans="1:18">
-      <c r="A32" s="2"/>
+      <c r="A32" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B32" s="3" t="s">
         <v>39</v>
       </c>
@@ -2387,7 +2443,9 @@
       </c>
     </row>
     <row r="33" spans="1:18">
-      <c r="A33" s="2"/>
+      <c r="A33" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B33" s="3" t="s">
         <v>39</v>
       </c>
@@ -2441,7 +2499,9 @@
       </c>
     </row>
     <row r="34" spans="1:18">
-      <c r="A34" s="2"/>
+      <c r="A34" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B34" s="3" t="s">
         <v>39</v>
       </c>
@@ -2495,7 +2555,9 @@
       </c>
     </row>
     <row r="35" spans="1:18">
-      <c r="A35" s="2"/>
+      <c r="A35" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B35" s="3" t="s">
         <v>39</v>
       </c>
@@ -2549,7 +2611,9 @@
       </c>
     </row>
     <row r="36" spans="1:18">
-      <c r="A36" s="2"/>
+      <c r="A36" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B36" s="3" t="s">
         <v>39</v>
       </c>
@@ -2603,7 +2667,9 @@
       </c>
     </row>
     <row r="37" spans="1:18">
-      <c r="A37" s="2"/>
+      <c r="A37" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B37" s="3" t="s">
         <v>39</v>
       </c>
@@ -2657,7 +2723,9 @@
       </c>
     </row>
     <row r="38" spans="1:18">
-      <c r="A38" s="2"/>
+      <c r="A38" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B38" s="3" t="s">
         <v>39</v>
       </c>
@@ -2711,7 +2779,9 @@
       </c>
     </row>
     <row r="39" spans="1:18">
-      <c r="A39" s="2"/>
+      <c r="A39" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B39" s="3" t="s">
         <v>39</v>
       </c>
@@ -2765,7 +2835,9 @@
       </c>
     </row>
     <row r="40" spans="1:18">
-      <c r="A40" s="2"/>
+      <c r="A40" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B40" s="3" t="s">
         <v>39</v>
       </c>
@@ -2819,7 +2891,9 @@
       </c>
     </row>
     <row r="41" spans="1:18">
-      <c r="A41" s="2"/>
+      <c r="A41" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B41" s="3" t="s">
         <v>39</v>
       </c>
@@ -2873,7 +2947,9 @@
       </c>
     </row>
     <row r="42" spans="1:18">
-      <c r="A42" s="2"/>
+      <c r="A42" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B42" s="3" t="s">
         <v>39</v>
       </c>
@@ -2927,7 +3003,9 @@
       </c>
     </row>
     <row r="43" spans="1:18">
-      <c r="A43" s="2"/>
+      <c r="A43" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B43" s="3" t="s">
         <v>39</v>
       </c>
@@ -2981,7 +3059,9 @@
       </c>
     </row>
     <row r="44" spans="1:18">
-      <c r="A44" s="2"/>
+      <c r="A44" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B44" s="3" t="s">
         <v>39</v>
       </c>
@@ -3035,7 +3115,9 @@
       </c>
     </row>
     <row r="45" spans="1:18">
-      <c r="A45" s="2"/>
+      <c r="A45" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B45" s="3" t="s">
         <v>39</v>
       </c>
@@ -3089,7 +3171,9 @@
       </c>
     </row>
     <row r="46" spans="1:18">
-      <c r="A46" s="2"/>
+      <c r="A46" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B46" s="3" t="s">
         <v>39</v>
       </c>
@@ -3143,7 +3227,9 @@
       </c>
     </row>
     <row r="47" spans="1:18">
-      <c r="A47" s="2"/>
+      <c r="A47" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B47" s="3" t="s">
         <v>39</v>
       </c>
@@ -3197,7 +3283,9 @@
       </c>
     </row>
     <row r="48" spans="1:18">
-      <c r="A48" s="2"/>
+      <c r="A48" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B48" s="3" t="s">
         <v>39</v>
       </c>
@@ -3251,7 +3339,9 @@
       </c>
     </row>
     <row r="49" spans="1:18">
-      <c r="A49" s="2"/>
+      <c r="A49" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B49" s="3" t="s">
         <v>39</v>
       </c>
@@ -3305,7 +3395,9 @@
       </c>
     </row>
     <row r="50" spans="1:18">
-      <c r="A50" s="2"/>
+      <c r="A50" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B50" s="3" t="s">
         <v>39</v>
       </c>
@@ -3359,7 +3451,9 @@
       </c>
     </row>
     <row r="51" spans="1:18">
-      <c r="A51" s="2"/>
+      <c r="A51" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B51" s="3" t="s">
         <v>39</v>
       </c>
@@ -3413,7 +3507,9 @@
       </c>
     </row>
     <row r="52" spans="1:18">
-      <c r="A52" s="2"/>
+      <c r="A52" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B52" s="3" t="s">
         <v>39</v>
       </c>
@@ -3467,7 +3563,9 @@
       </c>
     </row>
     <row r="53" spans="1:18">
-      <c r="A53" s="2"/>
+      <c r="A53" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B53" s="3" t="s">
         <v>39</v>
       </c>
@@ -3521,7 +3619,9 @@
       </c>
     </row>
     <row r="54" spans="1:18">
-      <c r="A54" s="2"/>
+      <c r="A54" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B54" s="3" t="s">
         <v>39</v>
       </c>
@@ -3575,7 +3675,9 @@
       </c>
     </row>
     <row r="55" spans="1:18">
-      <c r="A55" s="2"/>
+      <c r="A55" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B55" s="3" t="s">
         <v>39</v>
       </c>
@@ -3629,7 +3731,9 @@
       </c>
     </row>
     <row r="56" spans="1:18">
-      <c r="A56" s="2"/>
+      <c r="A56" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B56" s="3" t="s">
         <v>39</v>
       </c>
@@ -3683,7 +3787,9 @@
       </c>
     </row>
     <row r="57" spans="1:18">
-      <c r="A57" s="2"/>
+      <c r="A57" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B57" s="3" t="s">
         <v>39</v>
       </c>
@@ -3737,7 +3843,9 @@
       </c>
     </row>
     <row r="58" spans="1:18">
-      <c r="A58" s="2"/>
+      <c r="A58" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B58" s="3" t="s">
         <v>39</v>
       </c>
@@ -3863,7 +3971,9 @@
       </c>
     </row>
     <row r="61" spans="1:18">
-      <c r="A61" s="2"/>
+      <c r="A61" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B61" s="3" t="s">
         <v>40</v>
       </c>
@@ -3917,7 +4027,9 @@
       </c>
     </row>
     <row r="62" spans="1:18">
-      <c r="A62" s="2"/>
+      <c r="A62" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B62" s="3" t="s">
         <v>40</v>
       </c>
@@ -3971,7 +4083,9 @@
       </c>
     </row>
     <row r="63" spans="1:18">
-      <c r="A63" s="2"/>
+      <c r="A63" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B63" s="3" t="s">
         <v>40</v>
       </c>
@@ -4025,7 +4139,9 @@
       </c>
     </row>
     <row r="64" spans="1:18">
-      <c r="A64" s="2"/>
+      <c r="A64" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B64" s="3" t="s">
         <v>40</v>
       </c>
@@ -4079,7 +4195,9 @@
       </c>
     </row>
     <row r="65" spans="1:18">
-      <c r="A65" s="2"/>
+      <c r="A65" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B65" s="3" t="s">
         <v>40</v>
       </c>
@@ -4133,7 +4251,9 @@
       </c>
     </row>
     <row r="66" spans="1:18">
-      <c r="A66" s="2"/>
+      <c r="A66" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B66" s="3" t="s">
         <v>40</v>
       </c>
@@ -4187,7 +4307,9 @@
       </c>
     </row>
     <row r="67" spans="1:18">
-      <c r="A67" s="2"/>
+      <c r="A67" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B67" s="3" t="s">
         <v>40</v>
       </c>
@@ -4241,7 +4363,9 @@
       </c>
     </row>
     <row r="68" spans="1:18">
-      <c r="A68" s="2"/>
+      <c r="A68" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B68" s="3" t="s">
         <v>40</v>
       </c>
@@ -4295,7 +4419,9 @@
       </c>
     </row>
     <row r="69" spans="1:18">
-      <c r="A69" s="2"/>
+      <c r="A69" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B69" s="3" t="s">
         <v>40</v>
       </c>
@@ -4349,7 +4475,9 @@
       </c>
     </row>
     <row r="70" spans="1:18">
-      <c r="A70" s="2"/>
+      <c r="A70" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B70" s="3" t="s">
         <v>40</v>
       </c>
@@ -4403,7 +4531,9 @@
       </c>
     </row>
     <row r="71" spans="1:18">
-      <c r="A71" s="2"/>
+      <c r="A71" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B71" s="3" t="s">
         <v>40</v>
       </c>
@@ -4457,7 +4587,9 @@
       </c>
     </row>
     <row r="72" spans="1:18">
-      <c r="A72" s="2"/>
+      <c r="A72" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B72" s="3" t="s">
         <v>40</v>
       </c>
@@ -4511,7 +4643,9 @@
       </c>
     </row>
     <row r="73" spans="1:18">
-      <c r="A73" s="2"/>
+      <c r="A73" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B73" s="3" t="s">
         <v>40</v>
       </c>
@@ -4565,7 +4699,9 @@
       </c>
     </row>
     <row r="74" spans="1:18">
-      <c r="A74" s="2"/>
+      <c r="A74" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B74" s="3" t="s">
         <v>40</v>
       </c>
@@ -4619,7 +4755,9 @@
       </c>
     </row>
     <row r="75" spans="1:18">
-      <c r="A75" s="2"/>
+      <c r="A75" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B75" s="3" t="s">
         <v>40</v>
       </c>
@@ -4673,7 +4811,9 @@
       </c>
     </row>
     <row r="76" spans="1:18">
-      <c r="A76" s="2"/>
+      <c r="A76" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B76" s="3" t="s">
         <v>40</v>
       </c>
@@ -4727,7 +4867,9 @@
       </c>
     </row>
     <row r="77" spans="1:18">
-      <c r="A77" s="2"/>
+      <c r="A77" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B77" s="3" t="s">
         <v>40</v>
       </c>
@@ -4781,7 +4923,9 @@
       </c>
     </row>
     <row r="78" spans="1:18">
-      <c r="A78" s="2"/>
+      <c r="A78" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B78" s="3" t="s">
         <v>40</v>
       </c>
@@ -4835,7 +4979,9 @@
       </c>
     </row>
     <row r="79" spans="1:18">
-      <c r="A79" s="2"/>
+      <c r="A79" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B79" s="3" t="s">
         <v>40</v>
       </c>
@@ -4889,7 +5035,9 @@
       </c>
     </row>
     <row r="80" spans="1:18">
-      <c r="A80" s="2"/>
+      <c r="A80" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B80" s="3" t="s">
         <v>40</v>
       </c>
@@ -4943,7 +5091,9 @@
       </c>
     </row>
     <row r="81" spans="1:18">
-      <c r="A81" s="2"/>
+      <c r="A81" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B81" s="3" t="s">
         <v>40</v>
       </c>
@@ -4997,7 +5147,9 @@
       </c>
     </row>
     <row r="82" spans="1:18">
-      <c r="A82" s="2"/>
+      <c r="A82" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B82" s="3" t="s">
         <v>40</v>
       </c>
@@ -5051,7 +5203,9 @@
       </c>
     </row>
     <row r="83" spans="1:18">
-      <c r="A83" s="2"/>
+      <c r="A83" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B83" s="3" t="s">
         <v>40</v>
       </c>
@@ -5105,7 +5259,9 @@
       </c>
     </row>
     <row r="84" spans="1:18">
-      <c r="A84" s="2"/>
+      <c r="A84" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B84" s="3" t="s">
         <v>40</v>
       </c>
@@ -5159,7 +5315,9 @@
       </c>
     </row>
     <row r="85" spans="1:18">
-      <c r="A85" s="2"/>
+      <c r="A85" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B85" s="3" t="s">
         <v>40</v>
       </c>
@@ -5213,7 +5371,9 @@
       </c>
     </row>
     <row r="86" spans="1:18">
-      <c r="A86" s="2"/>
+      <c r="A86" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B86" s="3" t="s">
         <v>40</v>
       </c>
@@ -5267,7 +5427,9 @@
       </c>
     </row>
     <row r="87" spans="1:18">
-      <c r="A87" s="2"/>
+      <c r="A87" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B87" s="3" t="s">
         <v>40</v>
       </c>
@@ -5350,50 +5512,52 @@
         <v>0</v>
       </c>
       <c r="E89" s="3">
-        <v>1174469.602552741</v>
+        <v>1174470.564488229</v>
       </c>
       <c r="F89" s="3">
-        <v>1180348.498594058</v>
+        <v>1180362.166311358</v>
       </c>
       <c r="G89" s="3">
-        <v>1187835.275589135</v>
+        <v>1187887.875818716</v>
       </c>
       <c r="H89" s="3">
-        <v>1198428.690813583</v>
+        <v>1198563.092551954</v>
       </c>
       <c r="I89" s="3">
-        <v>1213311.839350733</v>
+        <v>1213559.702023957</v>
       </c>
       <c r="J89" s="3">
-        <v>1231403.91972198</v>
+        <v>1231763.6410625</v>
       </c>
       <c r="K89" s="3">
-        <v>1252034.277604343</v>
+        <v>1252488.678118279</v>
       </c>
       <c r="L89" s="3">
-        <v>1274423.355048983</v>
+        <v>1274953.275575672</v>
       </c>
       <c r="M89" s="3">
-        <v>1298118.50597655</v>
+        <v>1298707.763879189</v>
       </c>
       <c r="N89" s="3">
-        <v>1323333.239961506</v>
+        <v>1323969.72262592</v>
       </c>
       <c r="O89" s="3">
-        <v>1349659.404285876</v>
+        <v>1350334.195091417</v>
       </c>
       <c r="P89" s="3">
-        <v>1376662.182423925</v>
+        <v>1377368.769660801</v>
       </c>
       <c r="Q89" s="3">
-        <v>1404364.939825188</v>
+        <v>1405098.773319175</v>
       </c>
       <c r="R89" s="3">
-        <v>16464393.7317486</v>
+        <v>16469528.22052717</v>
       </c>
     </row>
     <row r="90" spans="1:18">
-      <c r="A90" s="2"/>
+      <c r="A90" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B90" s="3" t="s">
         <v>9</v>
       </c>
@@ -5404,50 +5568,52 @@
         <v>0</v>
       </c>
       <c r="E90" s="3">
-        <v>193928.931581806</v>
+        <v>193927.1819143076</v>
       </c>
       <c r="F90" s="3">
-        <v>192086.8905337932</v>
+        <v>191983.2692651195</v>
       </c>
       <c r="G90" s="3">
-        <v>191765.224775813</v>
+        <v>191585.9422291364</v>
       </c>
       <c r="H90" s="3">
-        <v>194458.7343213629</v>
+        <v>194270.9677249837</v>
       </c>
       <c r="I90" s="3">
-        <v>197932.0982005337</v>
+        <v>197738.2823889303</v>
       </c>
       <c r="J90" s="3">
-        <v>201706.2454557714</v>
+        <v>201507.1433024198</v>
       </c>
       <c r="K90" s="3">
-        <v>205143.8779641993</v>
+        <v>204940.5525152267</v>
       </c>
       <c r="L90" s="3">
-        <v>209535.9485394092</v>
+        <v>209327.272927229</v>
       </c>
       <c r="M90" s="3">
-        <v>213752.9956215514</v>
+        <v>213539.6490140942</v>
       </c>
       <c r="N90" s="3">
-        <v>217957.8459470233</v>
+        <v>217740.006622895</v>
       </c>
       <c r="O90" s="3">
-        <v>222196.051504428</v>
+        <v>221973.7924617403</v>
       </c>
       <c r="P90" s="3">
-        <v>226957.6937138271</v>
+        <v>226730.3465713201</v>
       </c>
       <c r="Q90" s="3">
-        <v>231392.7655104123</v>
+        <v>231160.9848038323</v>
       </c>
       <c r="R90" s="3">
-        <v>2698815.30366993</v>
+        <v>2696425.391741235</v>
       </c>
     </row>
     <row r="91" spans="1:18">
-      <c r="A91" s="2"/>
+      <c r="A91" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B91" s="3" t="s">
         <v>9</v>
       </c>
@@ -5458,50 +5624,52 @@
         <v>0</v>
       </c>
       <c r="E91" s="3">
-        <v>762208.289299886</v>
+        <v>762207.3326391844</v>
       </c>
       <c r="F91" s="3">
-        <v>765164.6915882451</v>
+        <v>765151.5011895188</v>
       </c>
       <c r="G91" s="3">
-        <v>767624.59933076</v>
+        <v>767579.4270635044</v>
       </c>
       <c r="H91" s="3">
-        <v>769733.2767026147</v>
+        <v>769627.2783479833</v>
       </c>
       <c r="I91" s="3">
-        <v>772873.8634455042</v>
+        <v>772685.5688594325</v>
       </c>
       <c r="J91" s="3">
-        <v>778235.9995709701</v>
+        <v>777967.6197276112</v>
       </c>
       <c r="K91" s="3">
-        <v>786249.3552228917</v>
+        <v>785913.7300629588</v>
       </c>
       <c r="L91" s="3">
-        <v>796504.2026793713</v>
+        <v>796115.213951361</v>
       </c>
       <c r="M91" s="3">
-        <v>808528.7509241498</v>
+        <v>808097.962295133</v>
       </c>
       <c r="N91" s="3">
-        <v>822225.9997174609</v>
+        <v>821761.9823144501</v>
       </c>
       <c r="O91" s="3">
-        <v>837148.1530868794</v>
+        <v>836657.1760506548</v>
       </c>
       <c r="P91" s="3">
-        <v>852876.138192059</v>
+        <v>852362.7558037416</v>
       </c>
       <c r="Q91" s="3">
-        <v>869313.6486369655</v>
+        <v>868781.0200065498</v>
       </c>
       <c r="R91" s="3">
-        <v>10388686.96839776</v>
+        <v>10384908.56831208</v>
       </c>
     </row>
     <row r="92" spans="1:18">
-      <c r="A92" s="2"/>
+      <c r="A92" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B92" s="3" t="s">
         <v>9</v>
       </c>
@@ -5512,50 +5680,52 @@
         <v>0</v>
       </c>
       <c r="E92" s="3">
-        <v>57451.85179301147</v>
+        <v>57451.85194948882</v>
       </c>
       <c r="F92" s="3">
-        <v>57713.95229631097</v>
+        <v>57713.96645604092</v>
       </c>
       <c r="G92" s="3">
-        <v>58009.022250783</v>
+        <v>58009.24260244417</v>
       </c>
       <c r="H92" s="3">
-        <v>58385.83180924075</v>
+        <v>58386.67440005046</v>
       </c>
       <c r="I92" s="3">
-        <v>58920.50872811377</v>
+        <v>58922.27582471209</v>
       </c>
       <c r="J92" s="3">
-        <v>59616.28171946103</v>
+        <v>59618.99137922403</v>
       </c>
       <c r="K92" s="3">
-        <v>60466.00195001468</v>
+        <v>60469.52543942071</v>
       </c>
       <c r="L92" s="3">
-        <v>61434.38907481802</v>
+        <v>61438.56983861184</v>
       </c>
       <c r="M92" s="3">
-        <v>62494.01952321304</v>
+        <v>62498.72053893703</v>
       </c>
       <c r="N92" s="3">
-        <v>63648.34956278957</v>
+        <v>63653.46577167449</v>
       </c>
       <c r="O92" s="3">
-        <v>64871.98734211465</v>
+        <v>64877.44020625729</v>
       </c>
       <c r="P92" s="3">
-        <v>66139.60209993264</v>
+        <v>66145.33355190608</v>
       </c>
       <c r="Q92" s="3">
-        <v>67449.03003168652</v>
+        <v>67454.99880535329</v>
       </c>
       <c r="R92" s="3">
-        <v>796600.8281814901</v>
+        <v>796641.0567641213</v>
       </c>
     </row>
     <row r="93" spans="1:18">
-      <c r="A93" s="2"/>
+      <c r="A93" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B93" s="3" t="s">
         <v>9</v>
       </c>
@@ -5566,50 +5736,52 @@
         <v>0</v>
       </c>
       <c r="E93" s="3">
-        <v>393416.7469509427</v>
+        <v>393416.7480224628</v>
       </c>
       <c r="F93" s="3">
-        <v>395211.549453633</v>
+        <v>395211.6464161282</v>
       </c>
       <c r="G93" s="3">
-        <v>397232.1189912275</v>
+        <v>397233.6279074943</v>
       </c>
       <c r="H93" s="3">
-        <v>399812.4220812405</v>
+        <v>399818.1919446134</v>
       </c>
       <c r="I93" s="3">
-        <v>403473.7636660277</v>
+        <v>403485.8643272518</v>
       </c>
       <c r="J93" s="3">
-        <v>408238.2532051699</v>
+        <v>408256.8083169032</v>
       </c>
       <c r="K93" s="3">
-        <v>414056.9371725245</v>
+        <v>414081.0651979367</v>
       </c>
       <c r="L93" s="3">
-        <v>420688.2240769381</v>
+        <v>420716.8529625213</v>
       </c>
       <c r="M93" s="3">
-        <v>427944.3237668082</v>
+        <v>427976.5152150519</v>
       </c>
       <c r="N93" s="3">
-        <v>435848.9039483854</v>
+        <v>435883.9385415866</v>
       </c>
       <c r="O93" s="3">
-        <v>444228.0872047014</v>
+        <v>444265.4271338005</v>
       </c>
       <c r="P93" s="3">
-        <v>452908.4144499309</v>
+        <v>452947.6620828673</v>
       </c>
       <c r="Q93" s="3">
-        <v>461875.0684602021</v>
+        <v>461915.9412161877</v>
       </c>
       <c r="R93" s="3">
-        <v>5454934.813427731</v>
+        <v>5455210.289284806</v>
       </c>
     </row>
     <row r="94" spans="1:18">
-      <c r="A94" s="2"/>
+      <c r="A94" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B94" s="3" t="s">
         <v>9</v>
       </c>
@@ -5620,50 +5792,52 @@
         <v>0</v>
       </c>
       <c r="E94" s="3">
-        <v>1543261.144901684</v>
+        <v>1543261.149104951</v>
       </c>
       <c r="F94" s="3">
-        <v>1550301.64072867</v>
+        <v>1550302.021084749</v>
       </c>
       <c r="G94" s="3">
-        <v>1558227.755928668</v>
+        <v>1558233.674974726</v>
       </c>
       <c r="H94" s="3">
-        <v>1568349.545434957</v>
+        <v>1568372.178955324</v>
       </c>
       <c r="I94" s="3">
-        <v>1582711.939130209</v>
+        <v>1582759.406556138</v>
       </c>
       <c r="J94" s="3">
-        <v>1601401.66608778</v>
+        <v>1601474.452473208</v>
       </c>
       <c r="K94" s="3">
-        <v>1624226.69565471</v>
+        <v>1624321.342983301</v>
       </c>
       <c r="L94" s="3">
-        <v>1650239.333651417</v>
+        <v>1650351.636564511</v>
       </c>
       <c r="M94" s="3">
-        <v>1678702.933133892</v>
+        <v>1678829.21095927</v>
       </c>
       <c r="N94" s="3">
-        <v>1709710.335730582</v>
+        <v>1709847.766398782</v>
       </c>
       <c r="O94" s="3">
-        <v>1742579.470168054</v>
+        <v>1742725.944008271</v>
       </c>
       <c r="P94" s="3">
-        <v>1776629.906166053</v>
+        <v>1776783.863381676</v>
       </c>
       <c r="Q94" s="3">
-        <v>1811803.520001952</v>
+        <v>1811963.852109537</v>
       </c>
       <c r="R94" s="3">
-        <v>21398145.88671863</v>
+        <v>21399226.49955444</v>
       </c>
     </row>
     <row r="95" spans="1:18">
-      <c r="A95" s="2"/>
+      <c r="A95" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B95" s="3" t="s">
         <v>9</v>
       </c>
@@ -5674,50 +5848,52 @@
         <v>0</v>
       </c>
       <c r="E95" s="3">
-        <v>1879226.040059616</v>
+        <v>1879226.045177925</v>
       </c>
       <c r="F95" s="3">
-        <v>1887799.237885993</v>
+        <v>1887799.701044837</v>
       </c>
       <c r="G95" s="3">
-        <v>1897450.852669112</v>
+        <v>1897458.060279776</v>
       </c>
       <c r="H95" s="3">
-        <v>1909776.135706957</v>
+        <v>1909803.696499887</v>
       </c>
       <c r="I95" s="3">
-        <v>1927265.194068123</v>
+        <v>1927322.995058678</v>
       </c>
       <c r="J95" s="3">
-        <v>1950023.637573489</v>
+        <v>1950112.269410887</v>
       </c>
       <c r="K95" s="3">
-        <v>1977817.63087722</v>
+        <v>1977932.882741817</v>
       </c>
       <c r="L95" s="3">
-        <v>2009493.168653537</v>
+        <v>2009629.919688421</v>
       </c>
       <c r="M95" s="3">
-        <v>2044153.237377487</v>
+        <v>2044307.005635385</v>
       </c>
       <c r="N95" s="3">
-        <v>2081910.890116178</v>
+        <v>2082078.239168695</v>
       </c>
       <c r="O95" s="3">
-        <v>2121935.57003064</v>
+        <v>2122113.930935815</v>
       </c>
       <c r="P95" s="3">
-        <v>2163398.718516051</v>
+        <v>2163586.191912637</v>
       </c>
       <c r="Q95" s="3">
-        <v>2206229.558430467</v>
+        <v>2206424.794520372</v>
       </c>
       <c r="R95" s="3">
-        <v>26056479.87196487</v>
+        <v>26057795.73207513</v>
       </c>
     </row>
     <row r="96" spans="1:18">
-      <c r="A96" s="2"/>
+      <c r="A96" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B96" s="3" t="s">
         <v>9</v>
       </c>
@@ -5728,50 +5904,52 @@
         <v>0</v>
       </c>
       <c r="E96" s="3">
-        <v>908124.5884913096</v>
+        <v>908125.332280052</v>
       </c>
       <c r="F96" s="3">
-        <v>912670.2745071077</v>
+        <v>912680.8426734712</v>
       </c>
       <c r="G96" s="3">
-        <v>918459.207880098</v>
+        <v>918499.879483466</v>
       </c>
       <c r="H96" s="3">
-        <v>926650.2592453352</v>
+        <v>926754.1814950773</v>
       </c>
       <c r="I96" s="3">
-        <v>938158.2225943885</v>
+        <v>938349.8752243377</v>
       </c>
       <c r="J96" s="3">
-        <v>952147.399501462</v>
+        <v>952425.5436046568</v>
       </c>
       <c r="K96" s="3">
-        <v>968099.2259443336</v>
+        <v>968450.5779749278</v>
       </c>
       <c r="L96" s="3">
-        <v>985410.9313277013</v>
+        <v>985820.677019872</v>
       </c>
       <c r="M96" s="3">
-        <v>1003732.520186677</v>
+        <v>1004188.14678543</v>
       </c>
       <c r="N96" s="3">
-        <v>1023229.082613015</v>
+        <v>1023721.224390415</v>
       </c>
       <c r="O96" s="3">
-        <v>1043585.026344261</v>
+        <v>1044106.788781763</v>
       </c>
       <c r="P96" s="3">
-        <v>1064464.142101228</v>
+        <v>1065010.49020792</v>
       </c>
       <c r="Q96" s="3">
-        <v>1085884.496540727</v>
+        <v>1086451.912026236</v>
       </c>
       <c r="R96" s="3">
-        <v>12730615.37727764</v>
+        <v>12734585.47194763</v>
       </c>
     </row>
     <row r="97" spans="1:18">
-      <c r="A97" s="2"/>
+      <c r="A97" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B97" s="3" t="s">
         <v>9</v>
       </c>
@@ -5782,50 +5960,52 @@
         <v>0.3411657413950535</v>
       </c>
       <c r="E97" s="3">
-        <v>0.341503508243522</v>
+        <v>0.3414756308196623</v>
       </c>
       <c r="F97" s="3">
-        <v>0.3395910521529794</v>
+        <v>0.3395248622331123</v>
       </c>
       <c r="G97" s="3">
-        <v>0.3356195986171639</v>
+        <v>0.3354690534468856</v>
       </c>
       <c r="H97" s="3">
-        <v>0.3330246703148766</v>
+        <v>0.3328203683486027</v>
       </c>
       <c r="I97" s="3">
-        <v>0.3310667538953671</v>
+        <v>0.3308244870091084</v>
       </c>
       <c r="J97" s="3">
-        <v>0.329654003785305</v>
+        <v>0.32938472911393</v>
       </c>
       <c r="K97" s="3">
-        <v>0.3287925897812508</v>
+        <v>0.3285044173624377</v>
       </c>
       <c r="L97" s="3">
-        <v>0.3279875340945028</v>
+        <v>0.3276859020605284</v>
       </c>
       <c r="M97" s="3">
-        <v>0.3275050997987259</v>
+        <v>0.3271941425810864</v>
       </c>
       <c r="N97" s="3">
-        <v>0.3272059167595403</v>
+        <v>0.3268884986583647</v>
       </c>
       <c r="O97" s="3">
-        <v>0.327018233141082</v>
+        <v>0.3266963425957151</v>
       </c>
       <c r="P97" s="3">
-        <v>0.3267909944084084</v>
+        <v>0.3264659069228734</v>
       </c>
       <c r="Q97" s="3">
-        <v>0.3267315596011877</v>
+        <v>0.3264043380401774</v>
       </c>
       <c r="R97" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="98" spans="1:18">
-      <c r="A98" s="2"/>
+      <c r="A98" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B98" s="3" t="s">
         <v>9</v>
       </c>
@@ -5836,50 +6016,52 @@
         <v>0.04535037632743646</v>
       </c>
       <c r="E98" s="3">
-        <v>0.04508285735237934</v>
+        <v>0.04508112659104896</v>
       </c>
       <c r="F98" s="3">
-        <v>0.04510657669418154</v>
+        <v>0.0451038930524234</v>
       </c>
       <c r="G98" s="3">
-        <v>0.04506397468984043</v>
+        <v>0.04505783891726733</v>
       </c>
       <c r="H98" s="3">
-        <v>0.04515200007270073</v>
+        <v>0.04514578190408319</v>
       </c>
       <c r="I98" s="3">
-        <v>0.04524238311887923</v>
+        <v>0.04523599597289983</v>
       </c>
       <c r="J98" s="3">
-        <v>0.04531416580256997</v>
+        <v>0.04530762511913378</v>
       </c>
       <c r="K98" s="3">
-        <v>0.04533789279714293</v>
+        <v>0.04533125452199877</v>
       </c>
       <c r="L98" s="3">
-        <v>0.04539368473379825</v>
+        <v>0.04538693207800329</v>
       </c>
       <c r="M98" s="3">
-        <v>0.04541996951849121</v>
+        <v>0.04541315727707147</v>
       </c>
       <c r="N98" s="3">
-        <v>0.04542988429388071</v>
+        <v>0.04542303212010726</v>
       </c>
       <c r="O98" s="3">
-        <v>0.04543108760837875</v>
+        <v>0.0454242094492842</v>
       </c>
       <c r="P98" s="3">
-        <v>0.04545143379021323</v>
+        <v>0.0454445193125879</v>
       </c>
       <c r="Q98" s="3">
-        <v>0.04544699031415047</v>
+        <v>0.04544007192056253</v>
       </c>
       <c r="R98" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="99" spans="1:18">
-      <c r="A99" s="2"/>
+      <c r="A99" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B99" s="3" t="s">
         <v>9</v>
       </c>
@@ -5890,50 +6072,52 @@
         <v>0.2195512735036556</v>
       </c>
       <c r="E99" s="3">
-        <v>0.2202947100495307</v>
+        <v>0.2202947133808399</v>
       </c>
       <c r="F99" s="3">
-        <v>0.2199459132551207</v>
+        <v>0.2199457895900764</v>
       </c>
       <c r="G99" s="3">
-        <v>0.2199173691445453</v>
+        <v>0.2199175586355219</v>
       </c>
       <c r="H99" s="3">
-        <v>0.21998458392773</v>
+        <v>0.2199852032180821</v>
       </c>
       <c r="I99" s="3">
-        <v>0.2200182411012028</v>
+        <v>0.2200189541053627</v>
       </c>
       <c r="J99" s="3">
-        <v>0.2200745981184572</v>
+        <v>0.220075267601815</v>
       </c>
       <c r="K99" s="3">
-        <v>0.2201592363776455</v>
+        <v>0.2201598312025241</v>
       </c>
       <c r="L99" s="3">
-        <v>0.2201334090690076</v>
+        <v>0.2201339357242751</v>
       </c>
       <c r="M99" s="3">
-        <v>0.2201867029847521</v>
+        <v>0.220187175547978</v>
       </c>
       <c r="N99" s="3">
-        <v>0.2202175155444787</v>
+        <v>0.2202179477368554</v>
       </c>
       <c r="O99" s="3">
-        <v>0.2202324080989497</v>
+        <v>0.2202328109387467</v>
       </c>
       <c r="P99" s="3">
-        <v>0.2202107458997489</v>
+        <v>0.2202111285667104</v>
       </c>
       <c r="Q99" s="3">
-        <v>0.2202462237571965</v>
+        <v>0.2202465911679047</v>
       </c>
       <c r="R99" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="100" spans="1:18">
-      <c r="A100" s="2"/>
+      <c r="A100" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B100" s="3" t="s">
         <v>9</v>
       </c>
@@ -5987,7 +6171,9 @@
       </c>
     </row>
     <row r="101" spans="1:18">
-      <c r="A101" s="2"/>
+      <c r="A101" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B101" s="3" t="s">
         <v>9</v>
       </c>
@@ -6041,7 +6227,9 @@
       </c>
     </row>
     <row r="102" spans="1:18">
-      <c r="A102" s="2"/>
+      <c r="A102" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B102" s="3" t="s">
         <v>9</v>
       </c>
@@ -6095,7 +6283,9 @@
       </c>
     </row>
     <row r="103" spans="1:18">
-      <c r="A103" s="2"/>
+      <c r="A103" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B103" s="3" t="s">
         <v>9</v>
       </c>
@@ -6149,7 +6339,9 @@
       </c>
     </row>
     <row r="104" spans="1:18">
-      <c r="A104" s="2"/>
+      <c r="A104" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B104" s="3" t="s">
         <v>9</v>
       </c>
@@ -6203,7 +6395,9 @@
       </c>
     </row>
     <row r="105" spans="1:18">
-      <c r="A105" s="2"/>
+      <c r="A105" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B105" s="3" t="s">
         <v>9</v>
       </c>
@@ -6214,50 +6408,52 @@
         <v>0</v>
       </c>
       <c r="E105" s="3">
-        <v>90.19950306130511</v>
+        <v>90.19868926246866</v>
       </c>
       <c r="F105" s="3">
-        <v>88.73926945186187</v>
+        <v>88.71504624814416</v>
       </c>
       <c r="G105" s="3">
-        <v>87.67542441447834</v>
+        <v>87.63222965228583</v>
       </c>
       <c r="H105" s="3">
-        <v>87.06198209839629</v>
+        <v>87.00872166105381</v>
       </c>
       <c r="I105" s="3">
-        <v>86.62248923333115</v>
+        <v>86.56300388593549</v>
       </c>
       <c r="J105" s="3">
-        <v>86.29441272968191</v>
+        <v>86.23069122421924</v>
       </c>
       <c r="K105" s="3">
-        <v>86.06387517707998</v>
+        <v>85.99708370875774</v>
       </c>
       <c r="L105" s="3">
-        <v>85.85270299635761</v>
+        <v>85.78358291490004</v>
       </c>
       <c r="M105" s="3">
-        <v>85.68828876697954</v>
+        <v>85.6173375193454</v>
       </c>
       <c r="N105" s="3">
-        <v>85.55611669950247</v>
+        <v>85.48369088191362</v>
       </c>
       <c r="O105" s="3">
-        <v>85.44869734728036</v>
+        <v>85.37505951052947</v>
       </c>
       <c r="P105" s="3">
-        <v>85.34841017500928</v>
+        <v>85.27376018462134</v>
       </c>
       <c r="Q105" s="3">
-        <v>85.27062570837063</v>
+        <v>85.19511506291421</v>
       </c>
       <c r="R105" s="3">
-        <v>1125.821797859634</v>
+        <v>1125.074011717089</v>
       </c>
     </row>
     <row r="106" spans="1:18">
-      <c r="A106" s="2"/>
+      <c r="A106" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B106" s="3" t="s">
         <v>9</v>
       </c>
@@ -6268,50 +6464,52 @@
         <v>0.01226890863757641</v>
       </c>
       <c r="E106" s="3">
-        <v>0.01212261372273152</v>
+        <v>0.01212187098697855</v>
       </c>
       <c r="F106" s="3">
-        <v>0.01214748994944895</v>
+        <v>0.01214632991042082</v>
       </c>
       <c r="G106" s="3">
-        <v>0.01212459234698479</v>
+        <v>0.01212192229525904</v>
       </c>
       <c r="H106" s="3">
-        <v>0.01215360681612595</v>
+        <v>0.01215088026758059</v>
       </c>
       <c r="I106" s="3">
-        <v>0.01218529792066025</v>
+        <v>0.01218250051527842</v>
       </c>
       <c r="J106" s="3">
-        <v>0.01220884994948308</v>
+        <v>0.01220599595765091</v>
       </c>
       <c r="K106" s="3">
-        <v>0.01221300753789345</v>
+        <v>0.01221012144069673</v>
       </c>
       <c r="L106" s="3">
-        <v>0.01223510572707452</v>
+        <v>0.01223217861465354</v>
       </c>
       <c r="M106" s="3">
-        <v>0.0122419531580071</v>
+        <v>0.01223900659050749</v>
       </c>
       <c r="N106" s="3">
-        <v>0.01224393122677965</v>
+        <v>0.01224097199504091</v>
       </c>
       <c r="O106" s="3">
-        <v>0.01224355233921942</v>
+        <v>0.01224058516928337</v>
       </c>
       <c r="P106" s="3">
-        <v>0.01225228600211074</v>
+        <v>0.01224930550619412</v>
       </c>
       <c r="Q106" s="3">
-        <v>0.01224870104917637</v>
+        <v>0.01224572049960609</v>
       </c>
       <c r="R106" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="107" spans="1:18">
-      <c r="A107" s="2"/>
+      <c r="A107" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B107" s="3" t="s">
         <v>9</v>
       </c>
@@ -6322,50 +6520,52 @@
         <v>0.03308146768986005</v>
       </c>
       <c r="E107" s="3">
-        <v>0.03296024362964781</v>
+        <v>0.0329592556040704</v>
       </c>
       <c r="F107" s="3">
-        <v>0.03295908674473259</v>
+        <v>0.03295756314200257</v>
       </c>
       <c r="G107" s="3">
-        <v>0.03293938234285565</v>
+        <v>0.03293591662200829</v>
       </c>
       <c r="H107" s="3">
-        <v>0.03299839325657477</v>
+        <v>0.0329949016365026</v>
       </c>
       <c r="I107" s="3">
-        <v>0.03305708519821898</v>
+        <v>0.03305349545762141</v>
       </c>
       <c r="J107" s="3">
-        <v>0.03310531585308688</v>
+        <v>0.03310162916148288</v>
       </c>
       <c r="K107" s="3">
-        <v>0.03312488525924948</v>
+        <v>0.03312113308130203</v>
       </c>
       <c r="L107" s="3">
-        <v>0.03315857900672373</v>
+        <v>0.03315475346334975</v>
       </c>
       <c r="M107" s="3">
-        <v>0.03317801636048411</v>
+        <v>0.03317415068656398</v>
       </c>
       <c r="N107" s="3">
-        <v>0.03318595306710106</v>
+        <v>0.03318206012506635</v>
       </c>
       <c r="O107" s="3">
-        <v>0.03318753526915933</v>
+        <v>0.03318362428000084</v>
       </c>
       <c r="P107" s="3">
-        <v>0.0331991477881025</v>
+        <v>0.03319521380639378</v>
       </c>
       <c r="Q107" s="3">
-        <v>0.0331982892649741</v>
+        <v>0.03319435142095644</v>
       </c>
       <c r="R107" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="108" spans="1:18">
-      <c r="A108" s="2"/>
+      <c r="A108" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B108" s="3" t="s">
         <v>9</v>
       </c>
@@ -6376,50 +6576,52 @@
         <v>121000.9090850509</v>
       </c>
       <c r="E108" s="3">
-        <v>119793.1858126559</v>
+        <v>119785.8673953782</v>
       </c>
       <c r="F108" s="3">
-        <v>120797.009982191</v>
+        <v>120786.7483361921</v>
       </c>
       <c r="G108" s="3">
-        <v>121694.1696022819</v>
+        <v>121670.7250294812</v>
       </c>
       <c r="H108" s="3">
-        <v>123411.9687967252</v>
+        <v>123389.5815439164</v>
       </c>
       <c r="I108" s="3">
-        <v>125511.3893978646</v>
+        <v>125489.5238110962</v>
       </c>
       <c r="J108" s="3">
-        <v>127813.0501148647</v>
+        <v>127791.4490647403</v>
       </c>
       <c r="K108" s="3">
-        <v>130013.0565728651</v>
+        <v>129991.6449744721</v>
       </c>
       <c r="L108" s="3">
-        <v>132689.6520108651</v>
+        <v>132668.0651975361</v>
       </c>
       <c r="M108" s="3">
-        <v>135329.8226509302</v>
+        <v>135308.0845616393</v>
       </c>
       <c r="N108" s="3">
-        <v>138002.2913135996</v>
+        <v>137980.3297657509</v>
       </c>
       <c r="O108" s="3">
-        <v>140703.8017242349</v>
+        <v>140681.5652031453</v>
       </c>
       <c r="P108" s="3">
-        <v>143665.1272339865</v>
+        <v>143642.468282387</v>
       </c>
       <c r="Q108" s="3">
-        <v>146500.6623441356</v>
+        <v>146477.6733735201</v>
       </c>
       <c r="R108" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="109" spans="1:18">
-      <c r="A109" s="2"/>
+      <c r="A109" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B109" s="3" t="s">
         <v>9</v>
       </c>
@@ -6430,50 +6632,52 @@
         <v>326262.7331074112</v>
       </c>
       <c r="E109" s="3">
-        <v>325706.3765178798</v>
+        <v>325696.6705453799</v>
       </c>
       <c r="F109" s="3">
-        <v>327751.5887706472</v>
+        <v>327739.8946320324</v>
       </c>
       <c r="G109" s="3">
-        <v>330611.5922670792</v>
+        <v>330585.9217128941</v>
       </c>
       <c r="H109" s="3">
-        <v>335077.2112784687</v>
+        <v>335056.1454278387</v>
       </c>
       <c r="I109" s="3">
-        <v>340495.630036039</v>
+        <v>340477.5070657441</v>
       </c>
       <c r="J109" s="3">
-        <v>346575.7554320807</v>
+        <v>346559.6065758212</v>
       </c>
       <c r="K109" s="3">
-        <v>352629.568746119</v>
+        <v>352614.8854102781</v>
       </c>
       <c r="L109" s="3">
-        <v>359604.600705724</v>
+        <v>359590.6446963293</v>
       </c>
       <c r="M109" s="3">
-        <v>366769.5025476562</v>
+        <v>366756.1376949989</v>
       </c>
       <c r="N109" s="3">
-        <v>374041.431453717</v>
+        <v>374028.435014676</v>
       </c>
       <c r="O109" s="3">
-        <v>381393.5900996487</v>
+        <v>381380.8031447995</v>
       </c>
       <c r="P109" s="3">
-        <v>389279.1753486656</v>
+        <v>389266.3501535504</v>
       </c>
       <c r="Q109" s="3">
-        <v>397068.3378167641</v>
+        <v>397055.556301575</v>
       </c>
       <c r="R109" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="110" spans="1:18">
-      <c r="A110" s="2"/>
+      <c r="A110" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B110" s="3" t="s">
         <v>9</v>
       </c>
@@ -6484,50 +6688,52 @@
         <v>0</v>
       </c>
       <c r="E110" s="3">
-        <v>59253.67933843113</v>
+        <v>59060.58428194568</v>
       </c>
       <c r="F110" s="3">
-        <v>55069.84498576695</v>
+        <v>54739.03994189482</v>
       </c>
       <c r="G110" s="3">
-        <v>38766.3615286725</v>
+        <v>38015.2712339257</v>
       </c>
       <c r="H110" s="3">
-        <v>39458.61798454166</v>
+        <v>38694.11536310295</v>
       </c>
       <c r="I110" s="3">
-        <v>40323.9385543781</v>
+        <v>39542.6705245745</v>
       </c>
       <c r="J110" s="3">
-        <v>41189.25912421454</v>
+        <v>40391.22568604605</v>
       </c>
       <c r="K110" s="3">
-        <v>41881.51558008369</v>
+        <v>41070.0698152233</v>
       </c>
       <c r="L110" s="3">
-        <v>42919.90026388742</v>
+        <v>42088.33600898917</v>
       </c>
       <c r="M110" s="3">
-        <v>43785.22083372385</v>
+        <v>42936.89117046072</v>
       </c>
       <c r="N110" s="3">
-        <v>44650.5414035603</v>
+        <v>43785.44633193229</v>
       </c>
       <c r="O110" s="3">
-        <v>45515.86197339674</v>
+        <v>44634.00149340383</v>
       </c>
       <c r="P110" s="3">
-        <v>46554.24665720046</v>
+        <v>45652.2676871697</v>
       </c>
       <c r="Q110" s="3">
-        <v>47419.5672270369</v>
+        <v>46500.82284864126</v>
       </c>
       <c r="R110" s="3">
-        <v>586788.5554548943</v>
+        <v>577110.74238731</v>
       </c>
     </row>
     <row r="111" spans="1:18">
-      <c r="A111" s="2"/>
+      <c r="A111" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B111" s="3" t="s">
         <v>9</v>
       </c>
@@ -6538,50 +6744,52 @@
         <v>0.5092287374537772</v>
       </c>
       <c r="E111" s="3">
-        <v>0.512364529130546</v>
+        <v>0.5123644980325339</v>
       </c>
       <c r="F111" s="3">
-        <v>0.5124948694486169</v>
+        <v>0.5124922729671789</v>
       </c>
       <c r="G111" s="3">
-        <v>0.512404338137268</v>
+        <v>0.5123997793298147</v>
       </c>
       <c r="H111" s="3">
-        <v>0.5123959064310672</v>
+        <v>0.5123911958929208</v>
       </c>
       <c r="I111" s="3">
-        <v>0.5124142146566532</v>
+        <v>0.5124094917035621</v>
       </c>
       <c r="J111" s="3">
-        <v>0.5124132397411397</v>
+        <v>0.5124085159793111</v>
       </c>
       <c r="K111" s="3">
-        <v>0.5123915249324071</v>
+        <v>0.512386802093489</v>
       </c>
       <c r="L111" s="3">
-        <v>0.5124271472619203</v>
+        <v>0.5124224227875337</v>
       </c>
       <c r="M111" s="3">
-        <v>0.5124080729867992</v>
+        <v>0.5124033493986837</v>
       </c>
       <c r="N111" s="3">
-        <v>0.5124049606478666</v>
+        <v>0.5124002371910323</v>
       </c>
       <c r="O111" s="3">
-        <v>0.5124029737625007</v>
+        <v>0.5123982503933832</v>
       </c>
       <c r="P111" s="3">
-        <v>0.5124187661907632</v>
+        <v>0.5124140421030653</v>
       </c>
       <c r="Q111" s="3">
-        <v>0.5124001985965468</v>
+        <v>0.512395475361492</v>
       </c>
       <c r="R111" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="112" spans="1:18">
-      <c r="A112" s="2"/>
+      <c r="A112" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B112" s="3" t="s">
         <v>9</v>
       </c>
@@ -6592,50 +6800,52 @@
         <v>0</v>
       </c>
       <c r="E112" s="3">
-        <v>846363.6666769785</v>
+        <v>846364.2424713157</v>
       </c>
       <c r="F112" s="3">
-        <v>863148.8846429052</v>
+        <v>863187.5797019337</v>
       </c>
       <c r="G112" s="3">
-        <v>880283.1609082582</v>
+        <v>880353.3207799774</v>
       </c>
       <c r="H112" s="3">
-        <v>896167.8896814022</v>
+        <v>896242.3010956908</v>
       </c>
       <c r="I112" s="3">
-        <v>915453.7582513781</v>
+        <v>915530.0004184692</v>
       </c>
       <c r="J112" s="3">
-        <v>935118.6423906023</v>
+        <v>935196.5399292326</v>
       </c>
       <c r="K112" s="3">
-        <v>951286.9790036227</v>
+        <v>951366.2281323501</v>
       </c>
       <c r="L112" s="3">
-        <v>974112.7902316045</v>
+        <v>974193.9355633106</v>
       </c>
       <c r="M112" s="3">
-        <v>994167.114600198</v>
+        <v>994249.9331869534</v>
       </c>
       <c r="N112" s="3">
-        <v>1013883.753977611</v>
+        <v>1013968.215793604</v>
       </c>
       <c r="O112" s="3">
-        <v>1033577.614014342</v>
+        <v>1033663.716828032</v>
       </c>
       <c r="P112" s="3">
-        <v>1056791.975151552</v>
+        <v>1056880.009127689</v>
       </c>
       <c r="Q112" s="3">
-        <v>1076872.510047073</v>
+        <v>1076962.219872999</v>
       </c>
       <c r="R112" s="3">
-        <v>12437228.73957753</v>
+        <v>12438158.24290156</v>
       </c>
     </row>
     <row r="113" spans="1:18">
-      <c r="A113" s="2"/>
+      <c r="A113" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B113" s="3" t="s">
         <v>9</v>
       </c>
@@ -6646,50 +6856,52 @@
         <v>0</v>
       </c>
       <c r="E113" s="3">
-        <v>3028619.676424752</v>
+        <v>3028620.770462731</v>
       </c>
       <c r="F113" s="3">
-        <v>3035675.956307787</v>
+        <v>3035728.954175335</v>
       </c>
       <c r="G113" s="3">
-        <v>3074176.225079975</v>
+        <v>3074326.198262082</v>
       </c>
       <c r="H113" s="3">
-        <v>3125314.908133927</v>
+        <v>3125540.169479474</v>
       </c>
       <c r="I113" s="3">
-        <v>3183920.971359708</v>
+        <v>3184182.759143597</v>
       </c>
       <c r="J113" s="3">
-        <v>3249178.17864972</v>
+        <v>3249457.727630356</v>
       </c>
       <c r="K113" s="3">
-        <v>3313306.003922229</v>
+        <v>3313595.605921817</v>
       </c>
       <c r="L113" s="3">
-        <v>3381047.781227214</v>
+        <v>3381344.912518767</v>
       </c>
       <c r="M113" s="3">
-        <v>3453800.911584619</v>
+        <v>3454105.009433927</v>
       </c>
       <c r="N113" s="3">
-        <v>3525308.190060901</v>
+        <v>3525618.798222512</v>
       </c>
       <c r="O113" s="3">
-        <v>3595874.045863258</v>
+        <v>3596190.953593507</v>
       </c>
       <c r="P113" s="3">
-        <v>3670132.446360121</v>
+        <v>3670455.913947621</v>
       </c>
       <c r="Q113" s="3">
-        <v>3745832.552875779</v>
+        <v>3746162.706658171</v>
       </c>
       <c r="R113" s="3">
-        <v>43382187.84784999</v>
+        <v>43385330.47944989</v>
       </c>
     </row>
     <row r="114" spans="1:18">
-      <c r="A114" s="2"/>
+      <c r="A114" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B114" s="3" t="s">
         <v>9</v>
       </c>
@@ -6700,50 +6912,52 @@
         <v>9862402</v>
       </c>
       <c r="E114" s="3">
-        <v>9881795.176565569</v>
+        <v>9881796.920958281</v>
       </c>
       <c r="F114" s="3">
-        <v>9944195.095849473</v>
+        <v>9944299.984192284</v>
       </c>
       <c r="G114" s="3">
-        <v>10036969.99615376</v>
+        <v>10037246.73908093</v>
       </c>
       <c r="H114" s="3">
-        <v>10154349.29431621</v>
+        <v>10154785.40045601</v>
       </c>
       <c r="I114" s="3">
-        <v>10300231.49331944</v>
+        <v>10300801.84718369</v>
       </c>
       <c r="J114" s="3">
-        <v>10468885.32857071</v>
+        <v>10469563.44309115</v>
       </c>
       <c r="K114" s="3">
-        <v>10645457.81777928</v>
+        <v>10646220.48239469</v>
       </c>
       <c r="L114" s="3">
-        <v>10844994.31151151</v>
+        <v>10845824.71994043</v>
       </c>
       <c r="M114" s="3">
-        <v>11054594.05898926</v>
+        <v>11055479.34475201</v>
       </c>
       <c r="N114" s="3">
-        <v>11271076.97336327</v>
+        <v>11272007.63318875</v>
       </c>
       <c r="O114" s="3">
-        <v>11492073.36448609</v>
+        <v>11493042.46958494</v>
       </c>
       <c r="P114" s="3">
-        <v>11725577.35015628</v>
+        <v>11726580.59754907</v>
       </c>
       <c r="Q114" s="3">
-        <v>11960505.99618371</v>
+        <v>11961539.81941951</v>
       </c>
       <c r="R114" s="3">
-        <v>149643108.2572446</v>
+        <v>149651591.4017918</v>
       </c>
     </row>
     <row r="115" spans="1:18">
-      <c r="A115" s="2"/>
+      <c r="A115" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B115" s="3" t="s">
         <v>9</v>
       </c>
@@ -6797,7 +7011,9 @@
       </c>
     </row>
     <row r="116" spans="1:18">
-      <c r="A116" s="2"/>
+      <c r="A116" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B116" s="3" t="s">
         <v>9</v>
       </c>
@@ -6880,50 +7096,52 @@
         <v>0</v>
       </c>
       <c r="E118" s="3">
-        <v>1174469.602552741</v>
+        <v>1174470.564488229</v>
       </c>
       <c r="F118" s="3">
-        <v>1180348.498594058</v>
+        <v>1180362.166311358</v>
       </c>
       <c r="G118" s="3">
-        <v>1187835.275589135</v>
+        <v>1187887.875818716</v>
       </c>
       <c r="H118" s="3">
-        <v>1198428.690813583</v>
+        <v>1198563.092551954</v>
       </c>
       <c r="I118" s="3">
-        <v>1213311.839350733</v>
+        <v>1213559.702023957</v>
       </c>
       <c r="J118" s="3">
-        <v>1231403.91972198</v>
+        <v>1231763.6410625</v>
       </c>
       <c r="K118" s="3">
-        <v>1252034.277604343</v>
+        <v>1252488.678118279</v>
       </c>
       <c r="L118" s="3">
-        <v>1274423.355048983</v>
+        <v>1274953.275575672</v>
       </c>
       <c r="M118" s="3">
-        <v>1298118.50597655</v>
+        <v>1298707.763879189</v>
       </c>
       <c r="N118" s="3">
-        <v>1323333.239961506</v>
+        <v>1323969.72262592</v>
       </c>
       <c r="O118" s="3">
-        <v>1349659.404285876</v>
+        <v>1350334.195091417</v>
       </c>
       <c r="P118" s="3">
-        <v>1376662.182423925</v>
+        <v>1377368.769660801</v>
       </c>
       <c r="Q118" s="3">
-        <v>1404364.939825188</v>
+        <v>1405098.773319175</v>
       </c>
       <c r="R118" s="3">
-        <v>16464393.7317486</v>
+        <v>16469528.22052717</v>
       </c>
     </row>
     <row r="119" spans="1:18">
-      <c r="A119" s="2"/>
+      <c r="A119" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B119" s="3" t="s">
         <v>39</v>
       </c>
@@ -6934,50 +7152,52 @@
         <v>0</v>
       </c>
       <c r="E119" s="3">
-        <v>193928.931581806</v>
+        <v>193927.1819143076</v>
       </c>
       <c r="F119" s="3">
-        <v>192086.8905337932</v>
+        <v>191983.2692651195</v>
       </c>
       <c r="G119" s="3">
-        <v>191765.224775813</v>
+        <v>191585.9422291364</v>
       </c>
       <c r="H119" s="3">
-        <v>194458.7343213629</v>
+        <v>194270.9677249837</v>
       </c>
       <c r="I119" s="3">
-        <v>197932.0982005337</v>
+        <v>197738.2823889303</v>
       </c>
       <c r="J119" s="3">
-        <v>201706.2454557714</v>
+        <v>201507.1433024198</v>
       </c>
       <c r="K119" s="3">
-        <v>205143.8779641993</v>
+        <v>204940.5525152267</v>
       </c>
       <c r="L119" s="3">
-        <v>209535.9485394092</v>
+        <v>209327.272927229</v>
       </c>
       <c r="M119" s="3">
-        <v>213752.9956215514</v>
+        <v>213539.6490140942</v>
       </c>
       <c r="N119" s="3">
-        <v>217957.8459470233</v>
+        <v>217740.006622895</v>
       </c>
       <c r="O119" s="3">
-        <v>222196.051504428</v>
+        <v>221973.7924617403</v>
       </c>
       <c r="P119" s="3">
-        <v>226957.6937138271</v>
+        <v>226730.3465713201</v>
       </c>
       <c r="Q119" s="3">
-        <v>231392.7655104123</v>
+        <v>231160.9848038323</v>
       </c>
       <c r="R119" s="3">
-        <v>2698815.30366993</v>
+        <v>2696425.391741235</v>
       </c>
     </row>
     <row r="120" spans="1:18">
-      <c r="A120" s="2"/>
+      <c r="A120" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B120" s="3" t="s">
         <v>39</v>
       </c>
@@ -6988,50 +7208,52 @@
         <v>0</v>
       </c>
       <c r="E120" s="3">
-        <v>762208.289299886</v>
+        <v>762207.3326391844</v>
       </c>
       <c r="F120" s="3">
-        <v>765164.6915882451</v>
+        <v>765151.5011895188</v>
       </c>
       <c r="G120" s="3">
-        <v>767624.59933076</v>
+        <v>767579.4270635044</v>
       </c>
       <c r="H120" s="3">
-        <v>769733.2767026147</v>
+        <v>769627.2783479833</v>
       </c>
       <c r="I120" s="3">
-        <v>772873.8634455042</v>
+        <v>772685.5688594325</v>
       </c>
       <c r="J120" s="3">
-        <v>778235.9995709701</v>
+        <v>777967.6197276112</v>
       </c>
       <c r="K120" s="3">
-        <v>786249.3552228917</v>
+        <v>785913.7300629588</v>
       </c>
       <c r="L120" s="3">
-        <v>796504.2026793713</v>
+        <v>796115.213951361</v>
       </c>
       <c r="M120" s="3">
-        <v>808528.7509241498</v>
+        <v>808097.962295133</v>
       </c>
       <c r="N120" s="3">
-        <v>822225.9997174609</v>
+        <v>821761.9823144501</v>
       </c>
       <c r="O120" s="3">
-        <v>837148.1530868794</v>
+        <v>836657.1760506548</v>
       </c>
       <c r="P120" s="3">
-        <v>852876.138192059</v>
+        <v>852362.7558037416</v>
       </c>
       <c r="Q120" s="3">
-        <v>869313.6486369655</v>
+        <v>868781.0200065498</v>
       </c>
       <c r="R120" s="3">
-        <v>10388686.96839776</v>
+        <v>10384908.56831208</v>
       </c>
     </row>
     <row r="121" spans="1:18">
-      <c r="A121" s="2"/>
+      <c r="A121" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B121" s="3" t="s">
         <v>39</v>
       </c>
@@ -7042,50 +7264,52 @@
         <v>0</v>
       </c>
       <c r="E121" s="3">
-        <v>57451.85179301147</v>
+        <v>57451.85194948882</v>
       </c>
       <c r="F121" s="3">
-        <v>57713.95229631097</v>
+        <v>57713.96645604092</v>
       </c>
       <c r="G121" s="3">
-        <v>58009.022250783</v>
+        <v>58009.24260244417</v>
       </c>
       <c r="H121" s="3">
-        <v>58385.83180924075</v>
+        <v>58386.67440005046</v>
       </c>
       <c r="I121" s="3">
-        <v>58920.50872811377</v>
+        <v>58922.27582471209</v>
       </c>
       <c r="J121" s="3">
-        <v>59616.28171946103</v>
+        <v>59618.99137922403</v>
       </c>
       <c r="K121" s="3">
-        <v>60466.00195001468</v>
+        <v>60469.52543942071</v>
       </c>
       <c r="L121" s="3">
-        <v>61434.38907481802</v>
+        <v>61438.56983861184</v>
       </c>
       <c r="M121" s="3">
-        <v>62494.01952321304</v>
+        <v>62498.72053893703</v>
       </c>
       <c r="N121" s="3">
-        <v>63648.34956278957</v>
+        <v>63653.46577167449</v>
       </c>
       <c r="O121" s="3">
-        <v>64871.98734211465</v>
+        <v>64877.44020625729</v>
       </c>
       <c r="P121" s="3">
-        <v>66139.60209993264</v>
+        <v>66145.33355190608</v>
       </c>
       <c r="Q121" s="3">
-        <v>67449.03003168652</v>
+        <v>67454.99880535329</v>
       </c>
       <c r="R121" s="3">
-        <v>796600.8281814901</v>
+        <v>796641.0567641213</v>
       </c>
     </row>
     <row r="122" spans="1:18">
-      <c r="A122" s="2"/>
+      <c r="A122" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B122" s="3" t="s">
         <v>39</v>
       </c>
@@ -7096,50 +7320,52 @@
         <v>0</v>
       </c>
       <c r="E122" s="3">
-        <v>393416.7469509427</v>
+        <v>393416.7480224628</v>
       </c>
       <c r="F122" s="3">
-        <v>395211.549453633</v>
+        <v>395211.6464161282</v>
       </c>
       <c r="G122" s="3">
-        <v>397232.1189912275</v>
+        <v>397233.6279074943</v>
       </c>
       <c r="H122" s="3">
-        <v>399812.4220812405</v>
+        <v>399818.1919446134</v>
       </c>
       <c r="I122" s="3">
-        <v>403473.7636660277</v>
+        <v>403485.8643272518</v>
       </c>
       <c r="J122" s="3">
-        <v>408238.2532051699</v>
+        <v>408256.8083169032</v>
       </c>
       <c r="K122" s="3">
-        <v>414056.9371725245</v>
+        <v>414081.0651979367</v>
       </c>
       <c r="L122" s="3">
-        <v>420688.2240769381</v>
+        <v>420716.8529625213</v>
       </c>
       <c r="M122" s="3">
-        <v>427944.3237668082</v>
+        <v>427976.5152150519</v>
       </c>
       <c r="N122" s="3">
-        <v>435848.9039483854</v>
+        <v>435883.9385415866</v>
       </c>
       <c r="O122" s="3">
-        <v>444228.0872047014</v>
+        <v>444265.4271338005</v>
       </c>
       <c r="P122" s="3">
-        <v>452908.4144499309</v>
+        <v>452947.6620828673</v>
       </c>
       <c r="Q122" s="3">
-        <v>461875.0684602021</v>
+        <v>461915.9412161877</v>
       </c>
       <c r="R122" s="3">
-        <v>5454934.813427731</v>
+        <v>5455210.289284806</v>
       </c>
     </row>
     <row r="123" spans="1:18">
-      <c r="A123" s="2"/>
+      <c r="A123" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B123" s="3" t="s">
         <v>39</v>
       </c>
@@ -7150,50 +7376,52 @@
         <v>0</v>
       </c>
       <c r="E123" s="3">
-        <v>1543261.144901684</v>
+        <v>1543261.149104951</v>
       </c>
       <c r="F123" s="3">
-        <v>1550301.64072867</v>
+        <v>1550302.021084749</v>
       </c>
       <c r="G123" s="3">
-        <v>1558227.755928668</v>
+        <v>1558233.674974726</v>
       </c>
       <c r="H123" s="3">
-        <v>1568349.545434957</v>
+        <v>1568372.178955324</v>
       </c>
       <c r="I123" s="3">
-        <v>1582711.939130209</v>
+        <v>1582759.406556138</v>
       </c>
       <c r="J123" s="3">
-        <v>1601401.66608778</v>
+        <v>1601474.452473208</v>
       </c>
       <c r="K123" s="3">
-        <v>1624226.69565471</v>
+        <v>1624321.342983301</v>
       </c>
       <c r="L123" s="3">
-        <v>1650239.333651417</v>
+        <v>1650351.636564511</v>
       </c>
       <c r="M123" s="3">
-        <v>1678702.933133892</v>
+        <v>1678829.21095927</v>
       </c>
       <c r="N123" s="3">
-        <v>1709710.335730582</v>
+        <v>1709847.766398782</v>
       </c>
       <c r="O123" s="3">
-        <v>1742579.470168054</v>
+        <v>1742725.944008271</v>
       </c>
       <c r="P123" s="3">
-        <v>1776629.906166053</v>
+        <v>1776783.863381676</v>
       </c>
       <c r="Q123" s="3">
-        <v>1811803.520001952</v>
+        <v>1811963.852109537</v>
       </c>
       <c r="R123" s="3">
-        <v>21398145.88671863</v>
+        <v>21399226.49955444</v>
       </c>
     </row>
     <row r="124" spans="1:18">
-      <c r="A124" s="2"/>
+      <c r="A124" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B124" s="3" t="s">
         <v>39</v>
       </c>
@@ -7204,50 +7432,52 @@
         <v>0</v>
       </c>
       <c r="E124" s="3">
-        <v>1879226.040059616</v>
+        <v>1879226.045177925</v>
       </c>
       <c r="F124" s="3">
-        <v>1887799.237885993</v>
+        <v>1887799.701044837</v>
       </c>
       <c r="G124" s="3">
-        <v>1897450.852669112</v>
+        <v>1897458.060279776</v>
       </c>
       <c r="H124" s="3">
-        <v>1909776.135706957</v>
+        <v>1909803.696499887</v>
       </c>
       <c r="I124" s="3">
-        <v>1927265.194068123</v>
+        <v>1927322.995058678</v>
       </c>
       <c r="J124" s="3">
-        <v>1950023.637573489</v>
+        <v>1950112.269410887</v>
       </c>
       <c r="K124" s="3">
-        <v>1977817.63087722</v>
+        <v>1977932.882741817</v>
       </c>
       <c r="L124" s="3">
-        <v>2009493.168653537</v>
+        <v>2009629.919688421</v>
       </c>
       <c r="M124" s="3">
-        <v>2044153.237377487</v>
+        <v>2044307.005635385</v>
       </c>
       <c r="N124" s="3">
-        <v>2081910.890116178</v>
+        <v>2082078.239168695</v>
       </c>
       <c r="O124" s="3">
-        <v>2121935.57003064</v>
+        <v>2122113.930935815</v>
       </c>
       <c r="P124" s="3">
-        <v>2163398.718516051</v>
+        <v>2163586.191912637</v>
       </c>
       <c r="Q124" s="3">
-        <v>2206229.558430467</v>
+        <v>2206424.794520372</v>
       </c>
       <c r="R124" s="3">
-        <v>26056479.87196487</v>
+        <v>26057795.73207513</v>
       </c>
     </row>
     <row r="125" spans="1:18">
-      <c r="A125" s="2"/>
+      <c r="A125" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B125" s="3" t="s">
         <v>39</v>
       </c>
@@ -7258,50 +7488,52 @@
         <v>0</v>
       </c>
       <c r="E125" s="3">
-        <v>908124.5884913096</v>
+        <v>908125.332280052</v>
       </c>
       <c r="F125" s="3">
-        <v>912670.2745071077</v>
+        <v>912680.8426734712</v>
       </c>
       <c r="G125" s="3">
-        <v>918459.207880098</v>
+        <v>918499.879483466</v>
       </c>
       <c r="H125" s="3">
-        <v>926650.2592453352</v>
+        <v>926754.1814950773</v>
       </c>
       <c r="I125" s="3">
-        <v>938158.2225943885</v>
+        <v>938349.8752243377</v>
       </c>
       <c r="J125" s="3">
-        <v>952147.399501462</v>
+        <v>952425.5436046568</v>
       </c>
       <c r="K125" s="3">
-        <v>968099.2259443336</v>
+        <v>968450.5779749278</v>
       </c>
       <c r="L125" s="3">
-        <v>985410.9313277013</v>
+        <v>985820.677019872</v>
       </c>
       <c r="M125" s="3">
-        <v>1003732.520186677</v>
+        <v>1004188.14678543</v>
       </c>
       <c r="N125" s="3">
-        <v>1023229.082613015</v>
+        <v>1023721.224390415</v>
       </c>
       <c r="O125" s="3">
-        <v>1043585.026344261</v>
+        <v>1044106.788781763</v>
       </c>
       <c r="P125" s="3">
-        <v>1064464.142101228</v>
+        <v>1065010.49020792</v>
       </c>
       <c r="Q125" s="3">
-        <v>1085884.496540727</v>
+        <v>1086451.912026236</v>
       </c>
       <c r="R125" s="3">
-        <v>12730615.37727764</v>
+        <v>12734585.47194763</v>
       </c>
     </row>
     <row r="126" spans="1:18">
-      <c r="A126" s="2"/>
+      <c r="A126" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B126" s="3" t="s">
         <v>39</v>
       </c>
@@ -7312,50 +7544,52 @@
         <v>0.3411657413950535</v>
       </c>
       <c r="E126" s="3">
-        <v>0.341503508243522</v>
+        <v>0.3414756308196623</v>
       </c>
       <c r="F126" s="3">
-        <v>0.3395910521529794</v>
+        <v>0.3395248622331123</v>
       </c>
       <c r="G126" s="3">
-        <v>0.3356195986171639</v>
+        <v>0.3354690534468856</v>
       </c>
       <c r="H126" s="3">
-        <v>0.3330246703148766</v>
+        <v>0.3328203683486027</v>
       </c>
       <c r="I126" s="3">
-        <v>0.3310667538953671</v>
+        <v>0.3308244870091084</v>
       </c>
       <c r="J126" s="3">
-        <v>0.329654003785305</v>
+        <v>0.32938472911393</v>
       </c>
       <c r="K126" s="3">
-        <v>0.3287925897812508</v>
+        <v>0.3285044173624377</v>
       </c>
       <c r="L126" s="3">
-        <v>0.3279875340945028</v>
+        <v>0.3276859020605284</v>
       </c>
       <c r="M126" s="3">
-        <v>0.3275050997987259</v>
+        <v>0.3271941425810864</v>
       </c>
       <c r="N126" s="3">
-        <v>0.3272059167595403</v>
+        <v>0.3268884986583647</v>
       </c>
       <c r="O126" s="3">
-        <v>0.327018233141082</v>
+        <v>0.3266963425957151</v>
       </c>
       <c r="P126" s="3">
-        <v>0.3267909944084084</v>
+        <v>0.3264659069228734</v>
       </c>
       <c r="Q126" s="3">
-        <v>0.3267315596011877</v>
+        <v>0.3264043380401774</v>
       </c>
       <c r="R126" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="127" spans="1:18">
-      <c r="A127" s="2"/>
+      <c r="A127" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B127" s="3" t="s">
         <v>39</v>
       </c>
@@ -7366,50 +7600,52 @@
         <v>0.04535037632743646</v>
       </c>
       <c r="E127" s="3">
-        <v>0.04508285735237934</v>
+        <v>0.04508112659104896</v>
       </c>
       <c r="F127" s="3">
-        <v>0.04510657669418154</v>
+        <v>0.0451038930524234</v>
       </c>
       <c r="G127" s="3">
-        <v>0.04506397468984043</v>
+        <v>0.04505783891726733</v>
       </c>
       <c r="H127" s="3">
-        <v>0.04515200007270073</v>
+        <v>0.04514578190408319</v>
       </c>
       <c r="I127" s="3">
-        <v>0.04524238311887923</v>
+        <v>0.04523599597289983</v>
       </c>
       <c r="J127" s="3">
-        <v>0.04531416580256997</v>
+        <v>0.04530762511913378</v>
       </c>
       <c r="K127" s="3">
-        <v>0.04533789279714293</v>
+        <v>0.04533125452199877</v>
       </c>
       <c r="L127" s="3">
-        <v>0.04539368473379825</v>
+        <v>0.04538693207800329</v>
       </c>
       <c r="M127" s="3">
-        <v>0.04541996951849121</v>
+        <v>0.04541315727707147</v>
       </c>
       <c r="N127" s="3">
-        <v>0.04542988429388071</v>
+        <v>0.04542303212010726</v>
       </c>
       <c r="O127" s="3">
-        <v>0.04543108760837875</v>
+        <v>0.0454242094492842</v>
       </c>
       <c r="P127" s="3">
-        <v>0.04545143379021323</v>
+        <v>0.0454445193125879</v>
       </c>
       <c r="Q127" s="3">
-        <v>0.04544699031415047</v>
+        <v>0.04544007192056253</v>
       </c>
       <c r="R127" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="128" spans="1:18">
-      <c r="A128" s="2"/>
+      <c r="A128" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B128" s="3" t="s">
         <v>39</v>
       </c>
@@ -7420,50 +7656,52 @@
         <v>0.2195512735036556</v>
       </c>
       <c r="E128" s="3">
-        <v>0.2202947100495307</v>
+        <v>0.2202947133808399</v>
       </c>
       <c r="F128" s="3">
-        <v>0.2199459132551207</v>
+        <v>0.2199457895900764</v>
       </c>
       <c r="G128" s="3">
-        <v>0.2199173691445453</v>
+        <v>0.2199175586355219</v>
       </c>
       <c r="H128" s="3">
-        <v>0.21998458392773</v>
+        <v>0.2199852032180821</v>
       </c>
       <c r="I128" s="3">
-        <v>0.2200182411012028</v>
+        <v>0.2200189541053627</v>
       </c>
       <c r="J128" s="3">
-        <v>0.2200745981184572</v>
+        <v>0.220075267601815</v>
       </c>
       <c r="K128" s="3">
-        <v>0.2201592363776455</v>
+        <v>0.2201598312025241</v>
       </c>
       <c r="L128" s="3">
-        <v>0.2201334090690076</v>
+        <v>0.2201339357242751</v>
       </c>
       <c r="M128" s="3">
-        <v>0.2201867029847521</v>
+        <v>0.220187175547978</v>
       </c>
       <c r="N128" s="3">
-        <v>0.2202175155444787</v>
+        <v>0.2202179477368554</v>
       </c>
       <c r="O128" s="3">
-        <v>0.2202324080989497</v>
+        <v>0.2202328109387467</v>
       </c>
       <c r="P128" s="3">
-        <v>0.2202107458997489</v>
+        <v>0.2202111285667104</v>
       </c>
       <c r="Q128" s="3">
-        <v>0.2202462237571965</v>
+        <v>0.2202465911679047</v>
       </c>
       <c r="R128" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="129" spans="1:18">
-      <c r="A129" s="2"/>
+      <c r="A129" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B129" s="3" t="s">
         <v>39</v>
       </c>
@@ -7517,7 +7755,9 @@
       </c>
     </row>
     <row r="130" spans="1:18">
-      <c r="A130" s="2"/>
+      <c r="A130" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B130" s="3" t="s">
         <v>39</v>
       </c>
@@ -7571,7 +7811,9 @@
       </c>
     </row>
     <row r="131" spans="1:18">
-      <c r="A131" s="2"/>
+      <c r="A131" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B131" s="3" t="s">
         <v>39</v>
       </c>
@@ -7625,7 +7867,9 @@
       </c>
     </row>
     <row r="132" spans="1:18">
-      <c r="A132" s="2"/>
+      <c r="A132" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B132" s="3" t="s">
         <v>39</v>
       </c>
@@ -7679,7 +7923,9 @@
       </c>
     </row>
     <row r="133" spans="1:18">
-      <c r="A133" s="2"/>
+      <c r="A133" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B133" s="3" t="s">
         <v>39</v>
       </c>
@@ -7733,7 +7979,9 @@
       </c>
     </row>
     <row r="134" spans="1:18">
-      <c r="A134" s="2"/>
+      <c r="A134" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B134" s="3" t="s">
         <v>39</v>
       </c>
@@ -7744,50 +7992,52 @@
         <v>0</v>
       </c>
       <c r="E134" s="3">
-        <v>90.19950306130511</v>
+        <v>90.19868926246866</v>
       </c>
       <c r="F134" s="3">
-        <v>88.73926945186187</v>
+        <v>88.71504624814416</v>
       </c>
       <c r="G134" s="3">
-        <v>87.67542441447834</v>
+        <v>87.63222965228583</v>
       </c>
       <c r="H134" s="3">
-        <v>87.06198209839629</v>
+        <v>87.00872166105381</v>
       </c>
       <c r="I134" s="3">
-        <v>86.62248923333115</v>
+        <v>86.56300388593549</v>
       </c>
       <c r="J134" s="3">
-        <v>86.29441272968191</v>
+        <v>86.23069122421924</v>
       </c>
       <c r="K134" s="3">
-        <v>86.06387517707998</v>
+        <v>85.99708370875774</v>
       </c>
       <c r="L134" s="3">
-        <v>85.85270299635761</v>
+        <v>85.78358291490004</v>
       </c>
       <c r="M134" s="3">
-        <v>85.68828876697954</v>
+        <v>85.6173375193454</v>
       </c>
       <c r="N134" s="3">
-        <v>85.55611669950247</v>
+        <v>85.48369088191362</v>
       </c>
       <c r="O134" s="3">
-        <v>85.44869734728036</v>
+        <v>85.37505951052947</v>
       </c>
       <c r="P134" s="3">
-        <v>85.34841017500928</v>
+        <v>85.27376018462134</v>
       </c>
       <c r="Q134" s="3">
-        <v>85.27062570837063</v>
+        <v>85.19511506291421</v>
       </c>
       <c r="R134" s="3">
-        <v>1125.821797859634</v>
+        <v>1125.074011717089</v>
       </c>
     </row>
     <row r="135" spans="1:18">
-      <c r="A135" s="2"/>
+      <c r="A135" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B135" s="3" t="s">
         <v>39</v>
       </c>
@@ -7798,50 +8048,52 @@
         <v>0.01226890863757641</v>
       </c>
       <c r="E135" s="3">
-        <v>0.01212261372273152</v>
+        <v>0.01212187098697855</v>
       </c>
       <c r="F135" s="3">
-        <v>0.01214748994944895</v>
+        <v>0.01214632991042082</v>
       </c>
       <c r="G135" s="3">
-        <v>0.01212459234698479</v>
+        <v>0.01212192229525904</v>
       </c>
       <c r="H135" s="3">
-        <v>0.01215360681612595</v>
+        <v>0.01215088026758059</v>
       </c>
       <c r="I135" s="3">
-        <v>0.01218529792066025</v>
+        <v>0.01218250051527842</v>
       </c>
       <c r="J135" s="3">
-        <v>0.01220884994948308</v>
+        <v>0.01220599595765091</v>
       </c>
       <c r="K135" s="3">
-        <v>0.01221300753789345</v>
+        <v>0.01221012144069673</v>
       </c>
       <c r="L135" s="3">
-        <v>0.01223510572707452</v>
+        <v>0.01223217861465354</v>
       </c>
       <c r="M135" s="3">
-        <v>0.0122419531580071</v>
+        <v>0.01223900659050749</v>
       </c>
       <c r="N135" s="3">
-        <v>0.01224393122677965</v>
+        <v>0.01224097199504091</v>
       </c>
       <c r="O135" s="3">
-        <v>0.01224355233921942</v>
+        <v>0.01224058516928337</v>
       </c>
       <c r="P135" s="3">
-        <v>0.01225228600211074</v>
+        <v>0.01224930550619412</v>
       </c>
       <c r="Q135" s="3">
-        <v>0.01224870104917637</v>
+        <v>0.01224572049960609</v>
       </c>
       <c r="R135" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="136" spans="1:18">
-      <c r="A136" s="2"/>
+      <c r="A136" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B136" s="3" t="s">
         <v>39</v>
       </c>
@@ -7852,50 +8104,52 @@
         <v>0.03308146768986005</v>
       </c>
       <c r="E136" s="3">
-        <v>0.03296024362964781</v>
+        <v>0.0329592556040704</v>
       </c>
       <c r="F136" s="3">
-        <v>0.03295908674473259</v>
+        <v>0.03295756314200257</v>
       </c>
       <c r="G136" s="3">
-        <v>0.03293938234285565</v>
+        <v>0.03293591662200829</v>
       </c>
       <c r="H136" s="3">
-        <v>0.03299839325657477</v>
+        <v>0.0329949016365026</v>
       </c>
       <c r="I136" s="3">
-        <v>0.03305708519821898</v>
+        <v>0.03305349545762141</v>
       </c>
       <c r="J136" s="3">
-        <v>0.03310531585308688</v>
+        <v>0.03310162916148288</v>
       </c>
       <c r="K136" s="3">
-        <v>0.03312488525924948</v>
+        <v>0.03312113308130203</v>
       </c>
       <c r="L136" s="3">
-        <v>0.03315857900672373</v>
+        <v>0.03315475346334975</v>
       </c>
       <c r="M136" s="3">
-        <v>0.03317801636048411</v>
+        <v>0.03317415068656398</v>
       </c>
       <c r="N136" s="3">
-        <v>0.03318595306710106</v>
+        <v>0.03318206012506635</v>
       </c>
       <c r="O136" s="3">
-        <v>0.03318753526915933</v>
+        <v>0.03318362428000084</v>
       </c>
       <c r="P136" s="3">
-        <v>0.0331991477881025</v>
+        <v>0.03319521380639378</v>
       </c>
       <c r="Q136" s="3">
-        <v>0.0331982892649741</v>
+        <v>0.03319435142095644</v>
       </c>
       <c r="R136" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="137" spans="1:18">
-      <c r="A137" s="2"/>
+      <c r="A137" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B137" s="3" t="s">
         <v>39</v>
       </c>
@@ -7906,50 +8160,52 @@
         <v>121000.9090850509</v>
       </c>
       <c r="E137" s="3">
-        <v>119793.1858126559</v>
+        <v>119785.8673953782</v>
       </c>
       <c r="F137" s="3">
-        <v>120797.009982191</v>
+        <v>120786.7483361921</v>
       </c>
       <c r="G137" s="3">
-        <v>121694.1696022819</v>
+        <v>121670.7250294812</v>
       </c>
       <c r="H137" s="3">
-        <v>123411.9687967252</v>
+        <v>123389.5815439164</v>
       </c>
       <c r="I137" s="3">
-        <v>125511.3893978646</v>
+        <v>125489.5238110962</v>
       </c>
       <c r="J137" s="3">
-        <v>127813.0501148647</v>
+        <v>127791.4490647403</v>
       </c>
       <c r="K137" s="3">
-        <v>130013.0565728651</v>
+        <v>129991.6449744721</v>
       </c>
       <c r="L137" s="3">
-        <v>132689.6520108651</v>
+        <v>132668.0651975361</v>
       </c>
       <c r="M137" s="3">
-        <v>135329.8226509302</v>
+        <v>135308.0845616393</v>
       </c>
       <c r="N137" s="3">
-        <v>138002.2913135996</v>
+        <v>137980.3297657509</v>
       </c>
       <c r="O137" s="3">
-        <v>140703.8017242349</v>
+        <v>140681.5652031453</v>
       </c>
       <c r="P137" s="3">
-        <v>143665.1272339865</v>
+        <v>143642.468282387</v>
       </c>
       <c r="Q137" s="3">
-        <v>146500.6623441356</v>
+        <v>146477.6733735201</v>
       </c>
       <c r="R137" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="138" spans="1:18">
-      <c r="A138" s="2"/>
+      <c r="A138" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B138" s="3" t="s">
         <v>39</v>
       </c>
@@ -7960,50 +8216,52 @@
         <v>326262.7331074112</v>
       </c>
       <c r="E138" s="3">
-        <v>325706.3765178798</v>
+        <v>325696.6705453799</v>
       </c>
       <c r="F138" s="3">
-        <v>327751.5887706472</v>
+        <v>327739.8946320324</v>
       </c>
       <c r="G138" s="3">
-        <v>330611.5922670792</v>
+        <v>330585.9217128941</v>
       </c>
       <c r="H138" s="3">
-        <v>335077.2112784687</v>
+        <v>335056.1454278387</v>
       </c>
       <c r="I138" s="3">
-        <v>340495.630036039</v>
+        <v>340477.5070657441</v>
       </c>
       <c r="J138" s="3">
-        <v>346575.7554320807</v>
+        <v>346559.6065758212</v>
       </c>
       <c r="K138" s="3">
-        <v>352629.568746119</v>
+        <v>352614.8854102781</v>
       </c>
       <c r="L138" s="3">
-        <v>359604.600705724</v>
+        <v>359590.6446963293</v>
       </c>
       <c r="M138" s="3">
-        <v>366769.5025476562</v>
+        <v>366756.1376949989</v>
       </c>
       <c r="N138" s="3">
-        <v>374041.431453717</v>
+        <v>374028.435014676</v>
       </c>
       <c r="O138" s="3">
-        <v>381393.5900996487</v>
+        <v>381380.8031447995</v>
       </c>
       <c r="P138" s="3">
-        <v>389279.1753486656</v>
+        <v>389266.3501535504</v>
       </c>
       <c r="Q138" s="3">
-        <v>397068.3378167641</v>
+        <v>397055.556301575</v>
       </c>
       <c r="R138" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="139" spans="1:18">
-      <c r="A139" s="2"/>
+      <c r="A139" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B139" s="3" t="s">
         <v>39</v>
       </c>
@@ -8014,50 +8272,52 @@
         <v>0</v>
       </c>
       <c r="E139" s="3">
-        <v>59253.67933843113</v>
+        <v>59060.58428194568</v>
       </c>
       <c r="F139" s="3">
-        <v>55069.84498576695</v>
+        <v>54739.03994189482</v>
       </c>
       <c r="G139" s="3">
-        <v>38766.3615286725</v>
+        <v>38015.2712339257</v>
       </c>
       <c r="H139" s="3">
-        <v>39458.61798454166</v>
+        <v>38694.11536310295</v>
       </c>
       <c r="I139" s="3">
-        <v>40323.9385543781</v>
+        <v>39542.6705245745</v>
       </c>
       <c r="J139" s="3">
-        <v>41189.25912421454</v>
+        <v>40391.22568604605</v>
       </c>
       <c r="K139" s="3">
-        <v>41881.51558008369</v>
+        <v>41070.0698152233</v>
       </c>
       <c r="L139" s="3">
-        <v>42919.90026388742</v>
+        <v>42088.33600898917</v>
       </c>
       <c r="M139" s="3">
-        <v>43785.22083372385</v>
+        <v>42936.89117046072</v>
       </c>
       <c r="N139" s="3">
-        <v>44650.5414035603</v>
+        <v>43785.44633193229</v>
       </c>
       <c r="O139" s="3">
-        <v>45515.86197339674</v>
+        <v>44634.00149340383</v>
       </c>
       <c r="P139" s="3">
-        <v>46554.24665720046</v>
+        <v>45652.2676871697</v>
       </c>
       <c r="Q139" s="3">
-        <v>47419.5672270369</v>
+        <v>46500.82284864126</v>
       </c>
       <c r="R139" s="3">
-        <v>586788.5554548943</v>
+        <v>577110.74238731</v>
       </c>
     </row>
     <row r="140" spans="1:18">
-      <c r="A140" s="2"/>
+      <c r="A140" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B140" s="3" t="s">
         <v>39</v>
       </c>
@@ -8068,50 +8328,52 @@
         <v>0.5092287374537772</v>
       </c>
       <c r="E140" s="3">
-        <v>0.512364529130546</v>
+        <v>0.5123644980325339</v>
       </c>
       <c r="F140" s="3">
-        <v>0.5124948694486169</v>
+        <v>0.5124922729671789</v>
       </c>
       <c r="G140" s="3">
-        <v>0.512404338137268</v>
+        <v>0.5123997793298147</v>
       </c>
       <c r="H140" s="3">
-        <v>0.5123959064310672</v>
+        <v>0.5123911958929208</v>
       </c>
       <c r="I140" s="3">
-        <v>0.5124142146566532</v>
+        <v>0.5124094917035621</v>
       </c>
       <c r="J140" s="3">
-        <v>0.5124132397411397</v>
+        <v>0.5124085159793111</v>
       </c>
       <c r="K140" s="3">
-        <v>0.5123915249324071</v>
+        <v>0.512386802093489</v>
       </c>
       <c r="L140" s="3">
-        <v>0.5124271472619203</v>
+        <v>0.5124224227875337</v>
       </c>
       <c r="M140" s="3">
-        <v>0.5124080729867992</v>
+        <v>0.5124033493986837</v>
       </c>
       <c r="N140" s="3">
-        <v>0.5124049606478666</v>
+        <v>0.5124002371910323</v>
       </c>
       <c r="O140" s="3">
-        <v>0.5124029737625007</v>
+        <v>0.5123982503933832</v>
       </c>
       <c r="P140" s="3">
-        <v>0.5124187661907632</v>
+        <v>0.5124140421030653</v>
       </c>
       <c r="Q140" s="3">
-        <v>0.5124001985965468</v>
+        <v>0.512395475361492</v>
       </c>
       <c r="R140" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="141" spans="1:18">
-      <c r="A141" s="2"/>
+      <c r="A141" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B141" s="3" t="s">
         <v>39</v>
       </c>
@@ -8122,50 +8384,52 @@
         <v>0</v>
       </c>
       <c r="E141" s="3">
-        <v>846363.6666769785</v>
+        <v>846364.2424713157</v>
       </c>
       <c r="F141" s="3">
-        <v>863148.8846429052</v>
+        <v>863187.5797019337</v>
       </c>
       <c r="G141" s="3">
-        <v>880283.1609082582</v>
+        <v>880353.3207799774</v>
       </c>
       <c r="H141" s="3">
-        <v>896167.8896814022</v>
+        <v>896242.3010956908</v>
       </c>
       <c r="I141" s="3">
-        <v>915453.7582513781</v>
+        <v>915530.0004184692</v>
       </c>
       <c r="J141" s="3">
-        <v>935118.6423906023</v>
+        <v>935196.5399292326</v>
       </c>
       <c r="K141" s="3">
-        <v>951286.9790036227</v>
+        <v>951366.2281323501</v>
       </c>
       <c r="L141" s="3">
-        <v>974112.7902316045</v>
+        <v>974193.9355633106</v>
       </c>
       <c r="M141" s="3">
-        <v>994167.114600198</v>
+        <v>994249.9331869534</v>
       </c>
       <c r="N141" s="3">
-        <v>1013883.753977611</v>
+        <v>1013968.215793604</v>
       </c>
       <c r="O141" s="3">
-        <v>1033577.614014342</v>
+        <v>1033663.716828032</v>
       </c>
       <c r="P141" s="3">
-        <v>1056791.975151552</v>
+        <v>1056880.009127689</v>
       </c>
       <c r="Q141" s="3">
-        <v>1076872.510047073</v>
+        <v>1076962.219872999</v>
       </c>
       <c r="R141" s="3">
-        <v>12437228.73957753</v>
+        <v>12438158.24290156</v>
       </c>
     </row>
     <row r="142" spans="1:18">
-      <c r="A142" s="2"/>
+      <c r="A142" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B142" s="3" t="s">
         <v>39</v>
       </c>
@@ -8176,50 +8440,52 @@
         <v>0</v>
       </c>
       <c r="E142" s="3">
-        <v>3028619.676424752</v>
+        <v>3028620.770462731</v>
       </c>
       <c r="F142" s="3">
-        <v>3035675.956307787</v>
+        <v>3035728.954175335</v>
       </c>
       <c r="G142" s="3">
-        <v>3074176.225079975</v>
+        <v>3074326.198262082</v>
       </c>
       <c r="H142" s="3">
-        <v>3125314.908133927</v>
+        <v>3125540.169479474</v>
       </c>
       <c r="I142" s="3">
-        <v>3183920.971359708</v>
+        <v>3184182.759143597</v>
       </c>
       <c r="J142" s="3">
-        <v>3249178.17864972</v>
+        <v>3249457.727630356</v>
       </c>
       <c r="K142" s="3">
-        <v>3313306.003922229</v>
+        <v>3313595.605921817</v>
       </c>
       <c r="L142" s="3">
-        <v>3381047.781227214</v>
+        <v>3381344.912518767</v>
       </c>
       <c r="M142" s="3">
-        <v>3453800.911584619</v>
+        <v>3454105.009433927</v>
       </c>
       <c r="N142" s="3">
-        <v>3525308.190060901</v>
+        <v>3525618.798222512</v>
       </c>
       <c r="O142" s="3">
-        <v>3595874.045863258</v>
+        <v>3596190.953593507</v>
       </c>
       <c r="P142" s="3">
-        <v>3670132.446360121</v>
+        <v>3670455.913947621</v>
       </c>
       <c r="Q142" s="3">
-        <v>3745832.552875779</v>
+        <v>3746162.706658171</v>
       </c>
       <c r="R142" s="3">
-        <v>43382187.84784999</v>
+        <v>43385330.47944989</v>
       </c>
     </row>
     <row r="143" spans="1:18">
-      <c r="A143" s="2"/>
+      <c r="A143" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B143" s="3" t="s">
         <v>39</v>
       </c>
@@ -8230,50 +8496,52 @@
         <v>9862402</v>
       </c>
       <c r="E143" s="3">
-        <v>9881795.176565569</v>
+        <v>9881796.920958281</v>
       </c>
       <c r="F143" s="3">
-        <v>9944195.095849473</v>
+        <v>9944299.984192284</v>
       </c>
       <c r="G143" s="3">
-        <v>10036969.99615376</v>
+        <v>10037246.73908093</v>
       </c>
       <c r="H143" s="3">
-        <v>10154349.29431621</v>
+        <v>10154785.40045601</v>
       </c>
       <c r="I143" s="3">
-        <v>10300231.49331944</v>
+        <v>10300801.84718369</v>
       </c>
       <c r="J143" s="3">
-        <v>10468885.32857071</v>
+        <v>10469563.44309115</v>
       </c>
       <c r="K143" s="3">
-        <v>10645457.81777928</v>
+        <v>10646220.48239469</v>
       </c>
       <c r="L143" s="3">
-        <v>10844994.31151151</v>
+        <v>10845824.71994043</v>
       </c>
       <c r="M143" s="3">
-        <v>11054594.05898926</v>
+        <v>11055479.34475201</v>
       </c>
       <c r="N143" s="3">
-        <v>11271076.97336327</v>
+        <v>11272007.63318875</v>
       </c>
       <c r="O143" s="3">
-        <v>11492073.36448609</v>
+        <v>11493042.46958494</v>
       </c>
       <c r="P143" s="3">
-        <v>11725577.35015628</v>
+        <v>11726580.59754907</v>
       </c>
       <c r="Q143" s="3">
-        <v>11960505.99618371</v>
+        <v>11961539.81941951</v>
       </c>
       <c r="R143" s="3">
-        <v>149643108.2572446</v>
+        <v>149651591.4017918</v>
       </c>
     </row>
     <row r="144" spans="1:18">
-      <c r="A144" s="2"/>
+      <c r="A144" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B144" s="3" t="s">
         <v>39</v>
       </c>
@@ -8327,7 +8595,9 @@
       </c>
     </row>
     <row r="145" spans="1:18">
-      <c r="A145" s="2"/>
+      <c r="A145" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B145" s="3" t="s">
         <v>39</v>
       </c>
@@ -8410,50 +8680,52 @@
         <v>0</v>
       </c>
       <c r="E147" s="3">
-        <v>1174469.602552741</v>
+        <v>1174470.564488229</v>
       </c>
       <c r="F147" s="3">
-        <v>1180348.498594058</v>
+        <v>1180362.166311358</v>
       </c>
       <c r="G147" s="3">
-        <v>1187835.275589135</v>
+        <v>1187887.875818716</v>
       </c>
       <c r="H147" s="3">
-        <v>1198428.690813583</v>
+        <v>1198563.092551954</v>
       </c>
       <c r="I147" s="3">
-        <v>1213311.839350733</v>
+        <v>1213559.702023957</v>
       </c>
       <c r="J147" s="3">
-        <v>1231403.91972198</v>
+        <v>1231763.6410625</v>
       </c>
       <c r="K147" s="3">
-        <v>1252034.277604343</v>
+        <v>1252488.678118279</v>
       </c>
       <c r="L147" s="3">
-        <v>1274423.355048983</v>
+        <v>1274953.275575672</v>
       </c>
       <c r="M147" s="3">
-        <v>1298118.50597655</v>
+        <v>1298707.763879189</v>
       </c>
       <c r="N147" s="3">
-        <v>1323333.239961506</v>
+        <v>1323969.72262592</v>
       </c>
       <c r="O147" s="3">
-        <v>1349659.404285876</v>
+        <v>1350334.195091417</v>
       </c>
       <c r="P147" s="3">
-        <v>1376662.182423925</v>
+        <v>1377368.769660801</v>
       </c>
       <c r="Q147" s="3">
-        <v>1404364.939825188</v>
+        <v>1405098.773319175</v>
       </c>
       <c r="R147" s="3">
-        <v>16464393.7317486</v>
+        <v>16469528.22052717</v>
       </c>
     </row>
     <row r="148" spans="1:18">
-      <c r="A148" s="2"/>
+      <c r="A148" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B148" s="3" t="s">
         <v>40</v>
       </c>
@@ -8464,50 +8736,52 @@
         <v>0</v>
       </c>
       <c r="E148" s="3">
-        <v>193928.931581806</v>
+        <v>193927.1819143076</v>
       </c>
       <c r="F148" s="3">
-        <v>192086.8905337932</v>
+        <v>191983.2692651195</v>
       </c>
       <c r="G148" s="3">
-        <v>191765.224775813</v>
+        <v>191585.9422291364</v>
       </c>
       <c r="H148" s="3">
-        <v>194458.7343213629</v>
+        <v>194270.9677249837</v>
       </c>
       <c r="I148" s="3">
-        <v>197932.0982005337</v>
+        <v>197738.2823889303</v>
       </c>
       <c r="J148" s="3">
-        <v>201706.2454557714</v>
+        <v>201507.1433024198</v>
       </c>
       <c r="K148" s="3">
-        <v>205143.8779641993</v>
+        <v>204940.5525152267</v>
       </c>
       <c r="L148" s="3">
-        <v>209535.9485394092</v>
+        <v>209327.272927229</v>
       </c>
       <c r="M148" s="3">
-        <v>213752.9956215514</v>
+        <v>213539.6490140942</v>
       </c>
       <c r="N148" s="3">
-        <v>217957.8459470233</v>
+        <v>217740.006622895</v>
       </c>
       <c r="O148" s="3">
-        <v>222196.051504428</v>
+        <v>221973.7924617403</v>
       </c>
       <c r="P148" s="3">
-        <v>226957.6937138271</v>
+        <v>226730.3465713201</v>
       </c>
       <c r="Q148" s="3">
-        <v>231392.7655104123</v>
+        <v>231160.9848038323</v>
       </c>
       <c r="R148" s="3">
-        <v>2698815.30366993</v>
+        <v>2696425.391741235</v>
       </c>
     </row>
     <row r="149" spans="1:18">
-      <c r="A149" s="2"/>
+      <c r="A149" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B149" s="3" t="s">
         <v>40</v>
       </c>
@@ -8518,50 +8792,52 @@
         <v>0</v>
       </c>
       <c r="E149" s="3">
-        <v>762208.289299886</v>
+        <v>762207.3326391844</v>
       </c>
       <c r="F149" s="3">
-        <v>765164.6915882451</v>
+        <v>765151.5011895188</v>
       </c>
       <c r="G149" s="3">
-        <v>767624.59933076</v>
+        <v>767579.4270635044</v>
       </c>
       <c r="H149" s="3">
-        <v>769733.2767026147</v>
+        <v>769627.2783479833</v>
       </c>
       <c r="I149" s="3">
-        <v>772873.8634455042</v>
+        <v>772685.5688594325</v>
       </c>
       <c r="J149" s="3">
-        <v>778235.9995709701</v>
+        <v>777967.6197276112</v>
       </c>
       <c r="K149" s="3">
-        <v>786249.3552228917</v>
+        <v>785913.7300629588</v>
       </c>
       <c r="L149" s="3">
-        <v>796504.2026793713</v>
+        <v>796115.213951361</v>
       </c>
       <c r="M149" s="3">
-        <v>808528.7509241498</v>
+        <v>808097.962295133</v>
       </c>
       <c r="N149" s="3">
-        <v>822225.9997174609</v>
+        <v>821761.9823144501</v>
       </c>
       <c r="O149" s="3">
-        <v>837148.1530868794</v>
+        <v>836657.1760506548</v>
       </c>
       <c r="P149" s="3">
-        <v>852876.138192059</v>
+        <v>852362.7558037416</v>
       </c>
       <c r="Q149" s="3">
-        <v>869313.6486369655</v>
+        <v>868781.0200065498</v>
       </c>
       <c r="R149" s="3">
-        <v>10388686.96839776</v>
+        <v>10384908.56831208</v>
       </c>
     </row>
     <row r="150" spans="1:18">
-      <c r="A150" s="2"/>
+      <c r="A150" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B150" s="3" t="s">
         <v>40</v>
       </c>
@@ -8572,50 +8848,52 @@
         <v>0</v>
       </c>
       <c r="E150" s="3">
-        <v>57451.85179301147</v>
+        <v>57451.85194948882</v>
       </c>
       <c r="F150" s="3">
-        <v>57713.95229631097</v>
+        <v>57713.96645604092</v>
       </c>
       <c r="G150" s="3">
-        <v>58009.022250783</v>
+        <v>58009.24260244417</v>
       </c>
       <c r="H150" s="3">
-        <v>58385.83180924075</v>
+        <v>58386.67440005046</v>
       </c>
       <c r="I150" s="3">
-        <v>58920.50872811377</v>
+        <v>58922.27582471209</v>
       </c>
       <c r="J150" s="3">
-        <v>59616.28171946103</v>
+        <v>59618.99137922403</v>
       </c>
       <c r="K150" s="3">
-        <v>60466.00195001468</v>
+        <v>60469.52543942071</v>
       </c>
       <c r="L150" s="3">
-        <v>61434.38907481802</v>
+        <v>61438.56983861184</v>
       </c>
       <c r="M150" s="3">
-        <v>62494.01952321304</v>
+        <v>62498.72053893703</v>
       </c>
       <c r="N150" s="3">
-        <v>63648.34956278957</v>
+        <v>63653.46577167449</v>
       </c>
       <c r="O150" s="3">
-        <v>64871.98734211465</v>
+        <v>64877.44020625729</v>
       </c>
       <c r="P150" s="3">
-        <v>66139.60209993264</v>
+        <v>66145.33355190608</v>
       </c>
       <c r="Q150" s="3">
-        <v>67449.03003168652</v>
+        <v>67454.99880535329</v>
       </c>
       <c r="R150" s="3">
-        <v>796600.8281814901</v>
+        <v>796641.0567641213</v>
       </c>
     </row>
     <row r="151" spans="1:18">
-      <c r="A151" s="2"/>
+      <c r="A151" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B151" s="3" t="s">
         <v>40</v>
       </c>
@@ -8626,50 +8904,52 @@
         <v>0</v>
       </c>
       <c r="E151" s="3">
-        <v>393416.7469509427</v>
+        <v>393416.7480224628</v>
       </c>
       <c r="F151" s="3">
-        <v>395211.549453633</v>
+        <v>395211.6464161282</v>
       </c>
       <c r="G151" s="3">
-        <v>397232.1189912275</v>
+        <v>397233.6279074943</v>
       </c>
       <c r="H151" s="3">
-        <v>399812.4220812405</v>
+        <v>399818.1919446134</v>
       </c>
       <c r="I151" s="3">
-        <v>403473.7636660277</v>
+        <v>403485.8643272518</v>
       </c>
       <c r="J151" s="3">
-        <v>408238.2532051699</v>
+        <v>408256.8083169032</v>
       </c>
       <c r="K151" s="3">
-        <v>414056.9371725245</v>
+        <v>414081.0651979367</v>
       </c>
       <c r="L151" s="3">
-        <v>420688.2240769381</v>
+        <v>420716.8529625213</v>
       </c>
       <c r="M151" s="3">
-        <v>427944.3237668082</v>
+        <v>427976.5152150519</v>
       </c>
       <c r="N151" s="3">
-        <v>435848.9039483854</v>
+        <v>435883.9385415866</v>
       </c>
       <c r="O151" s="3">
-        <v>444228.0872047014</v>
+        <v>444265.4271338005</v>
       </c>
       <c r="P151" s="3">
-        <v>452908.4144499309</v>
+        <v>452947.6620828673</v>
       </c>
       <c r="Q151" s="3">
-        <v>461875.0684602021</v>
+        <v>461915.9412161877</v>
       </c>
       <c r="R151" s="3">
-        <v>5454934.813427731</v>
+        <v>5455210.289284806</v>
       </c>
     </row>
     <row r="152" spans="1:18">
-      <c r="A152" s="2"/>
+      <c r="A152" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B152" s="3" t="s">
         <v>40</v>
       </c>
@@ -8680,50 +8960,52 @@
         <v>0</v>
       </c>
       <c r="E152" s="3">
-        <v>1543261.144901684</v>
+        <v>1543261.149104951</v>
       </c>
       <c r="F152" s="3">
-        <v>1550301.64072867</v>
+        <v>1550302.021084749</v>
       </c>
       <c r="G152" s="3">
-        <v>1558227.755928668</v>
+        <v>1558233.674974726</v>
       </c>
       <c r="H152" s="3">
-        <v>1568349.545434957</v>
+        <v>1568372.178955324</v>
       </c>
       <c r="I152" s="3">
-        <v>1582711.939130209</v>
+        <v>1582759.406556138</v>
       </c>
       <c r="J152" s="3">
-        <v>1601401.66608778</v>
+        <v>1601474.452473208</v>
       </c>
       <c r="K152" s="3">
-        <v>1624226.69565471</v>
+        <v>1624321.342983301</v>
       </c>
       <c r="L152" s="3">
-        <v>1650239.333651417</v>
+        <v>1650351.636564511</v>
       </c>
       <c r="M152" s="3">
-        <v>1678702.933133892</v>
+        <v>1678829.21095927</v>
       </c>
       <c r="N152" s="3">
-        <v>1709710.335730582</v>
+        <v>1709847.766398782</v>
       </c>
       <c r="O152" s="3">
-        <v>1742579.470168054</v>
+        <v>1742725.944008271</v>
       </c>
       <c r="P152" s="3">
-        <v>1776629.906166053</v>
+        <v>1776783.863381676</v>
       </c>
       <c r="Q152" s="3">
-        <v>1811803.520001952</v>
+        <v>1811963.852109537</v>
       </c>
       <c r="R152" s="3">
-        <v>21398145.88671863</v>
+        <v>21399226.49955444</v>
       </c>
     </row>
     <row r="153" spans="1:18">
-      <c r="A153" s="2"/>
+      <c r="A153" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B153" s="3" t="s">
         <v>40</v>
       </c>
@@ -8734,50 +9016,52 @@
         <v>0</v>
       </c>
       <c r="E153" s="3">
-        <v>1879226.040059616</v>
+        <v>1879226.045177925</v>
       </c>
       <c r="F153" s="3">
-        <v>1887799.237885993</v>
+        <v>1887799.701044837</v>
       </c>
       <c r="G153" s="3">
-        <v>1897450.852669112</v>
+        <v>1897458.060279776</v>
       </c>
       <c r="H153" s="3">
-        <v>1909776.135706957</v>
+        <v>1909803.696499887</v>
       </c>
       <c r="I153" s="3">
-        <v>1927265.194068123</v>
+        <v>1927322.995058678</v>
       </c>
       <c r="J153" s="3">
-        <v>1950023.637573489</v>
+        <v>1950112.269410887</v>
       </c>
       <c r="K153" s="3">
-        <v>1977817.63087722</v>
+        <v>1977932.882741817</v>
       </c>
       <c r="L153" s="3">
-        <v>2009493.168653537</v>
+        <v>2009629.919688421</v>
       </c>
       <c r="M153" s="3">
-        <v>2044153.237377487</v>
+        <v>2044307.005635385</v>
       </c>
       <c r="N153" s="3">
-        <v>2081910.890116178</v>
+        <v>2082078.239168695</v>
       </c>
       <c r="O153" s="3">
-        <v>2121935.57003064</v>
+        <v>2122113.930935815</v>
       </c>
       <c r="P153" s="3">
-        <v>2163398.718516051</v>
+        <v>2163586.191912637</v>
       </c>
       <c r="Q153" s="3">
-        <v>2206229.558430467</v>
+        <v>2206424.794520372</v>
       </c>
       <c r="R153" s="3">
-        <v>26056479.87196487</v>
+        <v>26057795.73207513</v>
       </c>
     </row>
     <row r="154" spans="1:18">
-      <c r="A154" s="2"/>
+      <c r="A154" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B154" s="3" t="s">
         <v>40</v>
       </c>
@@ -8788,50 +9072,52 @@
         <v>0</v>
       </c>
       <c r="E154" s="3">
-        <v>908124.5884913096</v>
+        <v>908125.332280052</v>
       </c>
       <c r="F154" s="3">
-        <v>912670.2745071077</v>
+        <v>912680.8426734712</v>
       </c>
       <c r="G154" s="3">
-        <v>918459.207880098</v>
+        <v>918499.879483466</v>
       </c>
       <c r="H154" s="3">
-        <v>926650.2592453352</v>
+        <v>926754.1814950773</v>
       </c>
       <c r="I154" s="3">
-        <v>938158.2225943885</v>
+        <v>938349.8752243377</v>
       </c>
       <c r="J154" s="3">
-        <v>952147.399501462</v>
+        <v>952425.5436046568</v>
       </c>
       <c r="K154" s="3">
-        <v>968099.2259443336</v>
+        <v>968450.5779749278</v>
       </c>
       <c r="L154" s="3">
-        <v>985410.9313277013</v>
+        <v>985820.677019872</v>
       </c>
       <c r="M154" s="3">
-        <v>1003732.520186677</v>
+        <v>1004188.14678543</v>
       </c>
       <c r="N154" s="3">
-        <v>1023229.082613015</v>
+        <v>1023721.224390415</v>
       </c>
       <c r="O154" s="3">
-        <v>1043585.026344261</v>
+        <v>1044106.788781763</v>
       </c>
       <c r="P154" s="3">
-        <v>1064464.142101228</v>
+        <v>1065010.49020792</v>
       </c>
       <c r="Q154" s="3">
-        <v>1085884.496540727</v>
+        <v>1086451.912026236</v>
       </c>
       <c r="R154" s="3">
-        <v>12730615.37727764</v>
+        <v>12734585.47194763</v>
       </c>
     </row>
     <row r="155" spans="1:18">
-      <c r="A155" s="2"/>
+      <c r="A155" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B155" s="3" t="s">
         <v>40</v>
       </c>
@@ -8842,50 +9128,52 @@
         <v>0.3411657413950535</v>
       </c>
       <c r="E155" s="3">
-        <v>0.341503508243522</v>
+        <v>0.3414756308196623</v>
       </c>
       <c r="F155" s="3">
-        <v>0.3395910521529794</v>
+        <v>0.3395248622331123</v>
       </c>
       <c r="G155" s="3">
-        <v>0.3356195986171639</v>
+        <v>0.3354690534468856</v>
       </c>
       <c r="H155" s="3">
-        <v>0.3330246703148766</v>
+        <v>0.3328203683486027</v>
       </c>
       <c r="I155" s="3">
-        <v>0.3310667538953671</v>
+        <v>0.3308244870091084</v>
       </c>
       <c r="J155" s="3">
-        <v>0.329654003785305</v>
+        <v>0.32938472911393</v>
       </c>
       <c r="K155" s="3">
-        <v>0.3287925897812508</v>
+        <v>0.3285044173624377</v>
       </c>
       <c r="L155" s="3">
-        <v>0.3279875340945028</v>
+        <v>0.3276859020605284</v>
       </c>
       <c r="M155" s="3">
-        <v>0.3275050997987259</v>
+        <v>0.3271941425810864</v>
       </c>
       <c r="N155" s="3">
-        <v>0.3272059167595403</v>
+        <v>0.3268884986583647</v>
       </c>
       <c r="O155" s="3">
-        <v>0.327018233141082</v>
+        <v>0.3266963425957151</v>
       </c>
       <c r="P155" s="3">
-        <v>0.3267909944084084</v>
+        <v>0.3264659069228734</v>
       </c>
       <c r="Q155" s="3">
-        <v>0.3267315596011877</v>
+        <v>0.3264043380401774</v>
       </c>
       <c r="R155" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="156" spans="1:18">
-      <c r="A156" s="2"/>
+      <c r="A156" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B156" s="3" t="s">
         <v>40</v>
       </c>
@@ -8896,50 +9184,52 @@
         <v>0.04535037632743646</v>
       </c>
       <c r="E156" s="3">
-        <v>0.04508285735237934</v>
+        <v>0.04508112659104896</v>
       </c>
       <c r="F156" s="3">
-        <v>0.04510657669418154</v>
+        <v>0.0451038930524234</v>
       </c>
       <c r="G156" s="3">
-        <v>0.04506397468984043</v>
+        <v>0.04505783891726733</v>
       </c>
       <c r="H156" s="3">
-        <v>0.04515200007270073</v>
+        <v>0.04514578190408319</v>
       </c>
       <c r="I156" s="3">
-        <v>0.04524238311887923</v>
+        <v>0.04523599597289983</v>
       </c>
       <c r="J156" s="3">
-        <v>0.04531416580256997</v>
+        <v>0.04530762511913378</v>
       </c>
       <c r="K156" s="3">
-        <v>0.04533789279714293</v>
+        <v>0.04533125452199877</v>
       </c>
       <c r="L156" s="3">
-        <v>0.04539368473379825</v>
+        <v>0.04538693207800329</v>
       </c>
       <c r="M156" s="3">
-        <v>0.04541996951849121</v>
+        <v>0.04541315727707147</v>
       </c>
       <c r="N156" s="3">
-        <v>0.04542988429388071</v>
+        <v>0.04542303212010726</v>
       </c>
       <c r="O156" s="3">
-        <v>0.04543108760837875</v>
+        <v>0.0454242094492842</v>
       </c>
       <c r="P156" s="3">
-        <v>0.04545143379021323</v>
+        <v>0.0454445193125879</v>
       </c>
       <c r="Q156" s="3">
-        <v>0.04544699031415047</v>
+        <v>0.04544007192056253</v>
       </c>
       <c r="R156" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="157" spans="1:18">
-      <c r="A157" s="2"/>
+      <c r="A157" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B157" s="3" t="s">
         <v>40</v>
       </c>
@@ -8950,50 +9240,52 @@
         <v>0.2195512735036556</v>
       </c>
       <c r="E157" s="3">
-        <v>0.2202947100495307</v>
+        <v>0.2202947133808399</v>
       </c>
       <c r="F157" s="3">
-        <v>0.2199459132551207</v>
+        <v>0.2199457895900764</v>
       </c>
       <c r="G157" s="3">
-        <v>0.2199173691445453</v>
+        <v>0.2199175586355219</v>
       </c>
       <c r="H157" s="3">
-        <v>0.21998458392773</v>
+        <v>0.2199852032180821</v>
       </c>
       <c r="I157" s="3">
-        <v>0.2200182411012028</v>
+        <v>0.2200189541053627</v>
       </c>
       <c r="J157" s="3">
-        <v>0.2200745981184572</v>
+        <v>0.220075267601815</v>
       </c>
       <c r="K157" s="3">
-        <v>0.2201592363776455</v>
+        <v>0.2201598312025241</v>
       </c>
       <c r="L157" s="3">
-        <v>0.2201334090690076</v>
+        <v>0.2201339357242751</v>
       </c>
       <c r="M157" s="3">
-        <v>0.2201867029847521</v>
+        <v>0.220187175547978</v>
       </c>
       <c r="N157" s="3">
-        <v>0.2202175155444787</v>
+        <v>0.2202179477368554</v>
       </c>
       <c r="O157" s="3">
-        <v>0.2202324080989497</v>
+        <v>0.2202328109387467</v>
       </c>
       <c r="P157" s="3">
-        <v>0.2202107458997489</v>
+        <v>0.2202111285667104</v>
       </c>
       <c r="Q157" s="3">
-        <v>0.2202462237571965</v>
+        <v>0.2202465911679047</v>
       </c>
       <c r="R157" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="158" spans="1:18">
-      <c r="A158" s="2"/>
+      <c r="A158" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B158" s="3" t="s">
         <v>40</v>
       </c>
@@ -9047,7 +9339,9 @@
       </c>
     </row>
     <row r="159" spans="1:18">
-      <c r="A159" s="2"/>
+      <c r="A159" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B159" s="3" t="s">
         <v>40</v>
       </c>
@@ -9101,7 +9395,9 @@
       </c>
     </row>
     <row r="160" spans="1:18">
-      <c r="A160" s="2"/>
+      <c r="A160" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B160" s="3" t="s">
         <v>40</v>
       </c>
@@ -9155,7 +9451,9 @@
       </c>
     </row>
     <row r="161" spans="1:18">
-      <c r="A161" s="2"/>
+      <c r="A161" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B161" s="3" t="s">
         <v>40</v>
       </c>
@@ -9209,7 +9507,9 @@
       </c>
     </row>
     <row r="162" spans="1:18">
-      <c r="A162" s="2"/>
+      <c r="A162" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B162" s="3" t="s">
         <v>40</v>
       </c>
@@ -9263,7 +9563,9 @@
       </c>
     </row>
     <row r="163" spans="1:18">
-      <c r="A163" s="2"/>
+      <c r="A163" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B163" s="3" t="s">
         <v>40</v>
       </c>
@@ -9274,50 +9576,52 @@
         <v>0</v>
       </c>
       <c r="E163" s="3">
-        <v>90.19950306130511</v>
+        <v>90.19868926246866</v>
       </c>
       <c r="F163" s="3">
-        <v>88.73926945186187</v>
+        <v>88.71504624814416</v>
       </c>
       <c r="G163" s="3">
-        <v>87.67542441447834</v>
+        <v>87.63222965228583</v>
       </c>
       <c r="H163" s="3">
-        <v>87.06198209839629</v>
+        <v>87.00872166105381</v>
       </c>
       <c r="I163" s="3">
-        <v>86.62248923333115</v>
+        <v>86.56300388593549</v>
       </c>
       <c r="J163" s="3">
-        <v>86.29441272968191</v>
+        <v>86.23069122421924</v>
       </c>
       <c r="K163" s="3">
-        <v>86.06387517707998</v>
+        <v>85.99708370875774</v>
       </c>
       <c r="L163" s="3">
-        <v>85.85270299635761</v>
+        <v>85.78358291490004</v>
       </c>
       <c r="M163" s="3">
-        <v>85.68828876697954</v>
+        <v>85.6173375193454</v>
       </c>
       <c r="N163" s="3">
-        <v>85.55611669950247</v>
+        <v>85.48369088191362</v>
       </c>
       <c r="O163" s="3">
-        <v>85.44869734728036</v>
+        <v>85.37505951052947</v>
       </c>
       <c r="P163" s="3">
-        <v>85.34841017500928</v>
+        <v>85.27376018462134</v>
       </c>
       <c r="Q163" s="3">
-        <v>85.27062570837063</v>
+        <v>85.19511506291421</v>
       </c>
       <c r="R163" s="3">
-        <v>1125.821797859634</v>
+        <v>1125.074011717089</v>
       </c>
     </row>
     <row r="164" spans="1:18">
-      <c r="A164" s="2"/>
+      <c r="A164" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B164" s="3" t="s">
         <v>40</v>
       </c>
@@ -9328,50 +9632,52 @@
         <v>0.01226890863757641</v>
       </c>
       <c r="E164" s="3">
-        <v>0.01212261372273152</v>
+        <v>0.01212187098697855</v>
       </c>
       <c r="F164" s="3">
-        <v>0.01214748994944895</v>
+        <v>0.01214632991042082</v>
       </c>
       <c r="G164" s="3">
-        <v>0.01212459234698479</v>
+        <v>0.01212192229525904</v>
       </c>
       <c r="H164" s="3">
-        <v>0.01215360681612595</v>
+        <v>0.01215088026758059</v>
       </c>
       <c r="I164" s="3">
-        <v>0.01218529792066025</v>
+        <v>0.01218250051527842</v>
       </c>
       <c r="J164" s="3">
-        <v>0.01220884994948308</v>
+        <v>0.01220599595765091</v>
       </c>
       <c r="K164" s="3">
-        <v>0.01221300753789345</v>
+        <v>0.01221012144069673</v>
       </c>
       <c r="L164" s="3">
-        <v>0.01223510572707452</v>
+        <v>0.01223217861465354</v>
       </c>
       <c r="M164" s="3">
-        <v>0.0122419531580071</v>
+        <v>0.01223900659050749</v>
       </c>
       <c r="N164" s="3">
-        <v>0.01224393122677965</v>
+        <v>0.01224097199504091</v>
       </c>
       <c r="O164" s="3">
-        <v>0.01224355233921942</v>
+        <v>0.01224058516928337</v>
       </c>
       <c r="P164" s="3">
-        <v>0.01225228600211074</v>
+        <v>0.01224930550619412</v>
       </c>
       <c r="Q164" s="3">
-        <v>0.01224870104917637</v>
+        <v>0.01224572049960609</v>
       </c>
       <c r="R164" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="165" spans="1:18">
-      <c r="A165" s="2"/>
+      <c r="A165" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B165" s="3" t="s">
         <v>40</v>
       </c>
@@ -9382,50 +9688,52 @@
         <v>0.03308146768986005</v>
       </c>
       <c r="E165" s="3">
-        <v>0.03296024362964781</v>
+        <v>0.0329592556040704</v>
       </c>
       <c r="F165" s="3">
-        <v>0.03295908674473259</v>
+        <v>0.03295756314200257</v>
       </c>
       <c r="G165" s="3">
-        <v>0.03293938234285565</v>
+        <v>0.03293591662200829</v>
       </c>
       <c r="H165" s="3">
-        <v>0.03299839325657477</v>
+        <v>0.0329949016365026</v>
       </c>
       <c r="I165" s="3">
-        <v>0.03305708519821898</v>
+        <v>0.03305349545762141</v>
       </c>
       <c r="J165" s="3">
-        <v>0.03310531585308688</v>
+        <v>0.03310162916148288</v>
       </c>
       <c r="K165" s="3">
-        <v>0.03312488525924948</v>
+        <v>0.03312113308130203</v>
       </c>
       <c r="L165" s="3">
-        <v>0.03315857900672373</v>
+        <v>0.03315475346334975</v>
       </c>
       <c r="M165" s="3">
-        <v>0.03317801636048411</v>
+        <v>0.03317415068656398</v>
       </c>
       <c r="N165" s="3">
-        <v>0.03318595306710106</v>
+        <v>0.03318206012506635</v>
       </c>
       <c r="O165" s="3">
-        <v>0.03318753526915933</v>
+        <v>0.03318362428000084</v>
       </c>
       <c r="P165" s="3">
-        <v>0.0331991477881025</v>
+        <v>0.03319521380639378</v>
       </c>
       <c r="Q165" s="3">
-        <v>0.0331982892649741</v>
+        <v>0.03319435142095644</v>
       </c>
       <c r="R165" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="166" spans="1:18">
-      <c r="A166" s="2"/>
+      <c r="A166" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B166" s="3" t="s">
         <v>40</v>
       </c>
@@ -9436,50 +9744,52 @@
         <v>121000.9090850509</v>
       </c>
       <c r="E166" s="3">
-        <v>119793.1858126559</v>
+        <v>119785.8673953782</v>
       </c>
       <c r="F166" s="3">
-        <v>120797.009982191</v>
+        <v>120786.7483361921</v>
       </c>
       <c r="G166" s="3">
-        <v>121694.1696022819</v>
+        <v>121670.7250294812</v>
       </c>
       <c r="H166" s="3">
-        <v>123411.9687967252</v>
+        <v>123389.5815439164</v>
       </c>
       <c r="I166" s="3">
-        <v>125511.3893978646</v>
+        <v>125489.5238110962</v>
       </c>
       <c r="J166" s="3">
-        <v>127813.0501148647</v>
+        <v>127791.4490647403</v>
       </c>
       <c r="K166" s="3">
-        <v>130013.0565728651</v>
+        <v>129991.6449744721</v>
       </c>
       <c r="L166" s="3">
-        <v>132689.6520108651</v>
+        <v>132668.0651975361</v>
       </c>
       <c r="M166" s="3">
-        <v>135329.8226509302</v>
+        <v>135308.0845616393</v>
       </c>
       <c r="N166" s="3">
-        <v>138002.2913135996</v>
+        <v>137980.3297657509</v>
       </c>
       <c r="O166" s="3">
-        <v>140703.8017242349</v>
+        <v>140681.5652031453</v>
       </c>
       <c r="P166" s="3">
-        <v>143665.1272339865</v>
+        <v>143642.468282387</v>
       </c>
       <c r="Q166" s="3">
-        <v>146500.6623441356</v>
+        <v>146477.6733735201</v>
       </c>
       <c r="R166" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="167" spans="1:18">
-      <c r="A167" s="2"/>
+      <c r="A167" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B167" s="3" t="s">
         <v>40</v>
       </c>
@@ -9490,50 +9800,52 @@
         <v>326262.7331074112</v>
       </c>
       <c r="E167" s="3">
-        <v>325706.3765178798</v>
+        <v>325696.6705453799</v>
       </c>
       <c r="F167" s="3">
-        <v>327751.5887706472</v>
+        <v>327739.8946320324</v>
       </c>
       <c r="G167" s="3">
-        <v>330611.5922670792</v>
+        <v>330585.9217128941</v>
       </c>
       <c r="H167" s="3">
-        <v>335077.2112784687</v>
+        <v>335056.1454278387</v>
       </c>
       <c r="I167" s="3">
-        <v>340495.630036039</v>
+        <v>340477.5070657441</v>
       </c>
       <c r="J167" s="3">
-        <v>346575.7554320807</v>
+        <v>346559.6065758212</v>
       </c>
       <c r="K167" s="3">
-        <v>352629.568746119</v>
+        <v>352614.8854102781</v>
       </c>
       <c r="L167" s="3">
-        <v>359604.600705724</v>
+        <v>359590.6446963293</v>
       </c>
       <c r="M167" s="3">
-        <v>366769.5025476562</v>
+        <v>366756.1376949989</v>
       </c>
       <c r="N167" s="3">
-        <v>374041.431453717</v>
+        <v>374028.435014676</v>
       </c>
       <c r="O167" s="3">
-        <v>381393.5900996487</v>
+        <v>381380.8031447995</v>
       </c>
       <c r="P167" s="3">
-        <v>389279.1753486656</v>
+        <v>389266.3501535504</v>
       </c>
       <c r="Q167" s="3">
-        <v>397068.3378167641</v>
+        <v>397055.556301575</v>
       </c>
       <c r="R167" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="168" spans="1:18">
-      <c r="A168" s="2"/>
+      <c r="A168" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B168" s="3" t="s">
         <v>40</v>
       </c>
@@ -9544,50 +9856,52 @@
         <v>0</v>
       </c>
       <c r="E168" s="3">
-        <v>59253.67933843113</v>
+        <v>59060.58428194568</v>
       </c>
       <c r="F168" s="3">
-        <v>55069.84498576695</v>
+        <v>54739.03994189482</v>
       </c>
       <c r="G168" s="3">
-        <v>38766.3615286725</v>
+        <v>38015.2712339257</v>
       </c>
       <c r="H168" s="3">
-        <v>39458.61798454166</v>
+        <v>38694.11536310295</v>
       </c>
       <c r="I168" s="3">
-        <v>40323.9385543781</v>
+        <v>39542.6705245745</v>
       </c>
       <c r="J168" s="3">
-        <v>41189.25912421454</v>
+        <v>40391.22568604605</v>
       </c>
       <c r="K168" s="3">
-        <v>41881.51558008369</v>
+        <v>41070.0698152233</v>
       </c>
       <c r="L168" s="3">
-        <v>42919.90026388742</v>
+        <v>42088.33600898917</v>
       </c>
       <c r="M168" s="3">
-        <v>43785.22083372385</v>
+        <v>42936.89117046072</v>
       </c>
       <c r="N168" s="3">
-        <v>44650.5414035603</v>
+        <v>43785.44633193229</v>
       </c>
       <c r="O168" s="3">
-        <v>45515.86197339674</v>
+        <v>44634.00149340383</v>
       </c>
       <c r="P168" s="3">
-        <v>46554.24665720046</v>
+        <v>45652.2676871697</v>
       </c>
       <c r="Q168" s="3">
-        <v>47419.5672270369</v>
+        <v>46500.82284864126</v>
       </c>
       <c r="R168" s="3">
-        <v>586788.5554548943</v>
+        <v>577110.74238731</v>
       </c>
     </row>
     <row r="169" spans="1:18">
-      <c r="A169" s="2"/>
+      <c r="A169" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B169" s="3" t="s">
         <v>40</v>
       </c>
@@ -9598,50 +9912,52 @@
         <v>0.5092287374537772</v>
       </c>
       <c r="E169" s="3">
-        <v>0.512364529130546</v>
+        <v>0.5123644980325339</v>
       </c>
       <c r="F169" s="3">
-        <v>0.5124948694486169</v>
+        <v>0.5124922729671789</v>
       </c>
       <c r="G169" s="3">
-        <v>0.512404338137268</v>
+        <v>0.5123997793298147</v>
       </c>
       <c r="H169" s="3">
-        <v>0.5123959064310672</v>
+        <v>0.5123911958929208</v>
       </c>
       <c r="I169" s="3">
-        <v>0.5124142146566532</v>
+        <v>0.5124094917035621</v>
       </c>
       <c r="J169" s="3">
-        <v>0.5124132397411397</v>
+        <v>0.5124085159793111</v>
       </c>
       <c r="K169" s="3">
-        <v>0.5123915249324071</v>
+        <v>0.512386802093489</v>
       </c>
       <c r="L169" s="3">
-        <v>0.5124271472619203</v>
+        <v>0.5124224227875337</v>
       </c>
       <c r="M169" s="3">
-        <v>0.5124080729867992</v>
+        <v>0.5124033493986837</v>
       </c>
       <c r="N169" s="3">
-        <v>0.5124049606478666</v>
+        <v>0.5124002371910323</v>
       </c>
       <c r="O169" s="3">
-        <v>0.5124029737625007</v>
+        <v>0.5123982503933832</v>
       </c>
       <c r="P169" s="3">
-        <v>0.5124187661907632</v>
+        <v>0.5124140421030653</v>
       </c>
       <c r="Q169" s="3">
-        <v>0.5124001985965468</v>
+        <v>0.512395475361492</v>
       </c>
       <c r="R169" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="170" spans="1:18">
-      <c r="A170" s="2"/>
+      <c r="A170" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B170" s="3" t="s">
         <v>40</v>
       </c>
@@ -9652,50 +9968,52 @@
         <v>0</v>
       </c>
       <c r="E170" s="3">
-        <v>846363.6666769785</v>
+        <v>846364.2424713157</v>
       </c>
       <c r="F170" s="3">
-        <v>863148.8846429052</v>
+        <v>863187.5797019337</v>
       </c>
       <c r="G170" s="3">
-        <v>880283.1609082582</v>
+        <v>880353.3207799774</v>
       </c>
       <c r="H170" s="3">
-        <v>896167.8896814022</v>
+        <v>896242.3010956908</v>
       </c>
       <c r="I170" s="3">
-        <v>915453.7582513781</v>
+        <v>915530.0004184692</v>
       </c>
       <c r="J170" s="3">
-        <v>935118.6423906023</v>
+        <v>935196.5399292326</v>
       </c>
       <c r="K170" s="3">
-        <v>951286.9790036227</v>
+        <v>951366.2281323501</v>
       </c>
       <c r="L170" s="3">
-        <v>974112.7902316045</v>
+        <v>974193.9355633106</v>
       </c>
       <c r="M170" s="3">
-        <v>994167.114600198</v>
+        <v>994249.9331869534</v>
       </c>
       <c r="N170" s="3">
-        <v>1013883.753977611</v>
+        <v>1013968.215793604</v>
       </c>
       <c r="O170" s="3">
-        <v>1033577.614014342</v>
+        <v>1033663.716828032</v>
       </c>
       <c r="P170" s="3">
-        <v>1056791.975151552</v>
+        <v>1056880.009127689</v>
       </c>
       <c r="Q170" s="3">
-        <v>1076872.510047073</v>
+        <v>1076962.219872999</v>
       </c>
       <c r="R170" s="3">
-        <v>12437228.73957753</v>
+        <v>12438158.24290156</v>
       </c>
     </row>
     <row r="171" spans="1:18">
-      <c r="A171" s="2"/>
+      <c r="A171" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B171" s="3" t="s">
         <v>40</v>
       </c>
@@ -9706,50 +10024,52 @@
         <v>0</v>
       </c>
       <c r="E171" s="3">
-        <v>3028619.676424752</v>
+        <v>3028620.770462731</v>
       </c>
       <c r="F171" s="3">
-        <v>3035675.956307787</v>
+        <v>3035728.954175335</v>
       </c>
       <c r="G171" s="3">
-        <v>3074176.225079975</v>
+        <v>3074326.198262082</v>
       </c>
       <c r="H171" s="3">
-        <v>3125314.908133927</v>
+        <v>3125540.169479474</v>
       </c>
       <c r="I171" s="3">
-        <v>3183920.971359708</v>
+        <v>3184182.759143597</v>
       </c>
       <c r="J171" s="3">
-        <v>3249178.17864972</v>
+        <v>3249457.727630356</v>
       </c>
       <c r="K171" s="3">
-        <v>3313306.003922229</v>
+        <v>3313595.605921817</v>
       </c>
       <c r="L171" s="3">
-        <v>3381047.781227214</v>
+        <v>3381344.912518767</v>
       </c>
       <c r="M171" s="3">
-        <v>3453800.911584619</v>
+        <v>3454105.009433927</v>
       </c>
       <c r="N171" s="3">
-        <v>3525308.190060901</v>
+        <v>3525618.798222512</v>
       </c>
       <c r="O171" s="3">
-        <v>3595874.045863258</v>
+        <v>3596190.953593507</v>
       </c>
       <c r="P171" s="3">
-        <v>3670132.446360121</v>
+        <v>3670455.913947621</v>
       </c>
       <c r="Q171" s="3">
-        <v>3745832.552875779</v>
+        <v>3746162.706658171</v>
       </c>
       <c r="R171" s="3">
-        <v>43382187.84784999</v>
+        <v>43385330.47944989</v>
       </c>
     </row>
     <row r="172" spans="1:18">
-      <c r="A172" s="2"/>
+      <c r="A172" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B172" s="3" t="s">
         <v>40</v>
       </c>
@@ -9760,50 +10080,52 @@
         <v>9862402</v>
       </c>
       <c r="E172" s="3">
-        <v>9881795.176565569</v>
+        <v>9881796.920958281</v>
       </c>
       <c r="F172" s="3">
-        <v>9944195.095849473</v>
+        <v>9944299.984192284</v>
       </c>
       <c r="G172" s="3">
-        <v>10036969.99615376</v>
+        <v>10037246.73908093</v>
       </c>
       <c r="H172" s="3">
-        <v>10154349.29431621</v>
+        <v>10154785.40045601</v>
       </c>
       <c r="I172" s="3">
-        <v>10300231.49331944</v>
+        <v>10300801.84718369</v>
       </c>
       <c r="J172" s="3">
-        <v>10468885.32857071</v>
+        <v>10469563.44309115</v>
       </c>
       <c r="K172" s="3">
-        <v>10645457.81777928</v>
+        <v>10646220.48239469</v>
       </c>
       <c r="L172" s="3">
-        <v>10844994.31151151</v>
+        <v>10845824.71994043</v>
       </c>
       <c r="M172" s="3">
-        <v>11054594.05898926</v>
+        <v>11055479.34475201</v>
       </c>
       <c r="N172" s="3">
-        <v>11271076.97336327</v>
+        <v>11272007.63318875</v>
       </c>
       <c r="O172" s="3">
-        <v>11492073.36448609</v>
+        <v>11493042.46958494</v>
       </c>
       <c r="P172" s="3">
-        <v>11725577.35015628</v>
+        <v>11726580.59754907</v>
       </c>
       <c r="Q172" s="3">
-        <v>11960505.99618371</v>
+        <v>11961539.81941951</v>
       </c>
       <c r="R172" s="3">
-        <v>149643108.2572446</v>
+        <v>149651591.4017918</v>
       </c>
     </row>
     <row r="173" spans="1:18">
-      <c r="A173" s="2"/>
+      <c r="A173" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B173" s="3" t="s">
         <v>40</v>
       </c>
@@ -9857,7 +10179,9 @@
       </c>
     </row>
     <row r="174" spans="1:18">
-      <c r="A174" s="2"/>
+      <c r="A174" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B174" s="3" t="s">
         <v>40</v>
       </c>
@@ -10049,7 +10373,9 @@
       </c>
     </row>
     <row r="3" spans="1:18">
-      <c r="A3" s="2"/>
+      <c r="A3" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B3" s="3" t="s">
         <v>48</v>
       </c>
@@ -10103,7 +10429,9 @@
       </c>
     </row>
     <row r="4" spans="1:18">
-      <c r="A4" s="2"/>
+      <c r="A4" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B4" s="3" t="s">
         <v>49</v>
       </c>
@@ -10157,7 +10485,9 @@
       </c>
     </row>
     <row r="5" spans="1:18">
-      <c r="A5" s="2"/>
+      <c r="A5" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B5" s="3" t="s">
         <v>50</v>
       </c>
@@ -10211,7 +10541,9 @@
       </c>
     </row>
     <row r="6" spans="1:18">
-      <c r="A6" s="2"/>
+      <c r="A6" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B6" s="3" t="s">
         <v>51</v>
       </c>
@@ -10265,7 +10597,9 @@
       </c>
     </row>
     <row r="7" spans="1:18">
-      <c r="A7" s="2"/>
+      <c r="A7" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B7" s="3" t="s">
         <v>52</v>
       </c>
@@ -10319,7 +10653,9 @@
       </c>
     </row>
     <row r="8" spans="1:18">
-      <c r="A8" s="2"/>
+      <c r="A8" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B8" s="3" t="s">
         <v>53</v>
       </c>
@@ -10373,7 +10709,9 @@
       </c>
     </row>
     <row r="9" spans="1:18">
-      <c r="A9" s="2"/>
+      <c r="A9" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B9" s="3" t="s">
         <v>54</v>
       </c>
@@ -10427,7 +10765,9 @@
       </c>
     </row>
     <row r="10" spans="1:18">
-      <c r="A10" s="2"/>
+      <c r="A10" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B10" s="3" t="s">
         <v>55</v>
       </c>
@@ -10481,7 +10821,9 @@
       </c>
     </row>
     <row r="11" spans="1:18">
-      <c r="A11" s="2"/>
+      <c r="A11" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B11" s="3" t="s">
         <v>56</v>
       </c>
@@ -10535,7 +10877,9 @@
       </c>
     </row>
     <row r="12" spans="1:18">
-      <c r="A12" s="2"/>
+      <c r="A12" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B12" s="3" t="s">
         <v>57</v>
       </c>
@@ -10589,7 +10933,9 @@
       </c>
     </row>
     <row r="13" spans="1:18">
-      <c r="A13" s="2"/>
+      <c r="A13" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B13" s="3" t="s">
         <v>58</v>
       </c>
@@ -10643,7 +10989,9 @@
       </c>
     </row>
     <row r="14" spans="1:18">
-      <c r="A14" s="2"/>
+      <c r="A14" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B14" s="3" t="s">
         <v>59</v>
       </c>
@@ -10697,7 +11045,9 @@
       </c>
     </row>
     <row r="15" spans="1:18">
-      <c r="A15" s="2"/>
+      <c r="A15" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B15" s="3" t="s">
         <v>60</v>
       </c>
@@ -10751,7 +11101,9 @@
       </c>
     </row>
     <row r="16" spans="1:18">
-      <c r="A16" s="2"/>
+      <c r="A16" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B16" s="3" t="s">
         <v>61</v>
       </c>
@@ -10805,7 +11157,9 @@
       </c>
     </row>
     <row r="17" spans="1:18">
-      <c r="A17" s="2"/>
+      <c r="A17" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B17" s="3" t="s">
         <v>62</v>
       </c>
@@ -10859,7 +11213,9 @@
       </c>
     </row>
     <row r="18" spans="1:18">
-      <c r="A18" s="2"/>
+      <c r="A18" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B18" s="3" t="s">
         <v>63</v>
       </c>
@@ -10913,7 +11269,9 @@
       </c>
     </row>
     <row r="19" spans="1:18">
-      <c r="A19" s="2"/>
+      <c r="A19" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B19" s="3" t="s">
         <v>64</v>
       </c>
@@ -10967,7 +11325,9 @@
       </c>
     </row>
     <row r="20" spans="1:18">
-      <c r="A20" s="2"/>
+      <c r="A20" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B20" s="3" t="s">
         <v>65</v>
       </c>
@@ -11021,7 +11381,9 @@
       </c>
     </row>
     <row r="21" spans="1:18">
-      <c r="A21" s="2"/>
+      <c r="A21" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B21" s="3" t="s">
         <v>66</v>
       </c>
@@ -11075,7 +11437,9 @@
       </c>
     </row>
     <row r="22" spans="1:18">
-      <c r="A22" s="2"/>
+      <c r="A22" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B22" s="3" t="s">
         <v>67</v>
       </c>
@@ -11129,7 +11493,9 @@
       </c>
     </row>
     <row r="23" spans="1:18">
-      <c r="A23" s="2"/>
+      <c r="A23" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B23" s="3" t="s">
         <v>68</v>
       </c>
@@ -11183,7 +11549,9 @@
       </c>
     </row>
     <row r="24" spans="1:18">
-      <c r="A24" s="2"/>
+      <c r="A24" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B24" s="3" t="s">
         <v>69</v>
       </c>
@@ -11237,7 +11605,9 @@
       </c>
     </row>
     <row r="25" spans="1:18">
-      <c r="A25" s="2"/>
+      <c r="A25" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B25" s="3" t="s">
         <v>70</v>
       </c>
@@ -11291,7 +11661,9 @@
       </c>
     </row>
     <row r="26" spans="1:18">
-      <c r="A26" s="2"/>
+      <c r="A26" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B26" s="3" t="s">
         <v>71</v>
       </c>
@@ -11345,7 +11717,9 @@
       </c>
     </row>
     <row r="27" spans="1:18">
-      <c r="A27" s="2"/>
+      <c r="A27" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B27" s="3" t="s">
         <v>72</v>
       </c>
@@ -11399,7 +11773,9 @@
       </c>
     </row>
     <row r="28" spans="1:18">
-      <c r="A28" s="2"/>
+      <c r="A28" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B28" s="3" t="s">
         <v>73</v>
       </c>
@@ -11453,7 +11829,9 @@
       </c>
     </row>
     <row r="29" spans="1:18">
-      <c r="A29" s="2"/>
+      <c r="A29" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B29" s="3" t="s">
         <v>74</v>
       </c>
@@ -11507,7 +11885,9 @@
       </c>
     </row>
     <row r="30" spans="1:18">
-      <c r="A30" s="2"/>
+      <c r="A30" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B30" s="3" t="s">
         <v>75</v>
       </c>
@@ -11561,7 +11941,9 @@
       </c>
     </row>
     <row r="31" spans="1:18">
-      <c r="A31" s="2"/>
+      <c r="A31" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B31" s="3" t="s">
         <v>76</v>
       </c>
@@ -11615,7 +11997,9 @@
       </c>
     </row>
     <row r="32" spans="1:18">
-      <c r="A32" s="2"/>
+      <c r="A32" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B32" s="3" t="s">
         <v>77</v>
       </c>
@@ -11669,7 +12053,9 @@
       </c>
     </row>
     <row r="33" spans="1:18">
-      <c r="A33" s="2"/>
+      <c r="A33" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B33" s="3" t="s">
         <v>78</v>
       </c>
@@ -11723,7 +12109,9 @@
       </c>
     </row>
     <row r="34" spans="1:18">
-      <c r="A34" s="2"/>
+      <c r="A34" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B34" s="3" t="s">
         <v>79</v>
       </c>
@@ -11777,7 +12165,9 @@
       </c>
     </row>
     <row r="35" spans="1:18">
-      <c r="A35" s="2"/>
+      <c r="A35" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B35" s="3" t="s">
         <v>80</v>
       </c>
@@ -11831,7 +12221,9 @@
       </c>
     </row>
     <row r="36" spans="1:18">
-      <c r="A36" s="2"/>
+      <c r="A36" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B36" s="3" t="s">
         <v>81</v>
       </c>
@@ -11885,7 +12277,9 @@
       </c>
     </row>
     <row r="37" spans="1:18">
-      <c r="A37" s="2"/>
+      <c r="A37" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B37" s="3" t="s">
         <v>82</v>
       </c>
@@ -11939,7 +12333,9 @@
       </c>
     </row>
     <row r="38" spans="1:18">
-      <c r="A38" s="2"/>
+      <c r="A38" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B38" s="3" t="s">
         <v>83</v>
       </c>
@@ -11993,7 +12389,9 @@
       </c>
     </row>
     <row r="39" spans="1:18">
-      <c r="A39" s="2"/>
+      <c r="A39" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B39" s="3" t="s">
         <v>84</v>
       </c>
@@ -14320,50 +14718,52 @@
         <v>0</v>
       </c>
       <c r="E2" s="3">
-        <v>21893233471.9179</v>
+        <v>22757201772.49164</v>
       </c>
       <c r="F2" s="3">
-        <v>22167758537.44982</v>
+        <v>23042560365.86388</v>
       </c>
       <c r="G2" s="3">
-        <v>22489673071.13091</v>
+        <v>23377178548.50349</v>
       </c>
       <c r="H2" s="3">
-        <v>22833775762.75388</v>
+        <v>23734860495.93104</v>
       </c>
       <c r="I2" s="3">
-        <v>23254413737.78478</v>
+        <v>24172098023.37206</v>
       </c>
       <c r="J2" s="3">
-        <v>23705384711.64853</v>
+        <v>24640865574.72158</v>
       </c>
       <c r="K2" s="3">
-        <v>24113345506.5336</v>
+        <v>25064925644.98824</v>
       </c>
       <c r="L2" s="3">
-        <v>24634348495.03687</v>
+        <v>25606488870.38609</v>
       </c>
       <c r="M2" s="3">
-        <v>25132380379.68119</v>
+        <v>26124174487.84058</v>
       </c>
       <c r="N2" s="3">
-        <v>25628188333.97533</v>
+        <v>26639548412.42558</v>
       </c>
       <c r="O2" s="3">
-        <v>26127411536.46332</v>
+        <v>27158472360.46189</v>
       </c>
       <c r="P2" s="3">
-        <v>26688866879.43789</v>
+        <v>27742084303.51749</v>
       </c>
       <c r="Q2" s="3">
-        <v>27210367269.9337</v>
+        <v>28284164559.78339</v>
       </c>
       <c r="R2" s="3">
-        <v>315879147693.7477</v>
+        <v>328344623420.2869</v>
       </c>
     </row>
     <row r="3" spans="1:18">
-      <c r="A3" s="2"/>
+      <c r="A3" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B3" s="3" t="s">
         <v>9</v>
       </c>
@@ -14374,50 +14774,52 @@
         <v>0</v>
       </c>
       <c r="E3" s="3">
-        <v>2717436179.375196</v>
+        <v>2824673820.668513</v>
       </c>
       <c r="F3" s="3">
-        <v>2780632369.593224</v>
+        <v>2890363909.521269</v>
       </c>
       <c r="G3" s="3">
-        <v>2831189321.767645</v>
+        <v>2942915980.603474</v>
       </c>
       <c r="H3" s="3">
-        <v>2881746273.942068</v>
+        <v>2995468051.685678</v>
       </c>
       <c r="I3" s="3">
-        <v>2944942464.160095</v>
+        <v>3061158140.538435</v>
       </c>
       <c r="J3" s="3">
-        <v>3008138654.378123</v>
+        <v>3126848229.391191</v>
       </c>
       <c r="K3" s="3">
-        <v>3058695606.552545</v>
+        <v>3179400300.473396</v>
       </c>
       <c r="L3" s="3">
-        <v>3134531034.814178</v>
+        <v>3258228407.096702</v>
       </c>
       <c r="M3" s="3">
-        <v>3197727225.032207</v>
+        <v>3323918495.949458</v>
       </c>
       <c r="N3" s="3">
-        <v>3260923415.250234</v>
+        <v>3389608584.802216</v>
       </c>
       <c r="O3" s="3">
-        <v>3324119605.468262</v>
+        <v>3455298673.654972</v>
       </c>
       <c r="P3" s="3">
-        <v>3399955033.729896</v>
+        <v>3534126780.278278</v>
       </c>
       <c r="Q3" s="3">
-        <v>3463151223.947923</v>
+        <v>3599816869.131035</v>
       </c>
       <c r="R3" s="3">
-        <v>40003188408.01159</v>
+        <v>41581826243.79461</v>
       </c>
     </row>
     <row r="4" spans="1:18">
-      <c r="A4" s="2"/>
+      <c r="A4" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B4" s="3" t="s">
         <v>9</v>
       </c>
@@ -14428,50 +14830,52 @@
         <v>0</v>
       </c>
       <c r="E4" s="3">
-        <v>56773196440.9739</v>
+        <v>59013625754.90613</v>
       </c>
       <c r="F4" s="3">
-        <v>57031620146.08464</v>
+        <v>59282247583.08624</v>
       </c>
       <c r="G4" s="3">
-        <v>57314654488.60669</v>
+        <v>59576451253.34721</v>
       </c>
       <c r="H4" s="3">
-        <v>57661212307.69167</v>
+        <v>59936685214.44153</v>
       </c>
       <c r="I4" s="3">
-        <v>58151240858.09483</v>
+        <v>60446051663.67387</v>
       </c>
       <c r="J4" s="3">
-        <v>58799713617.25073</v>
+        <v>61120114973.8288</v>
       </c>
       <c r="K4" s="3">
-        <v>59605651415.18334</v>
+        <v>61957857334.14098</v>
       </c>
       <c r="L4" s="3">
-        <v>60535344235.77234</v>
+        <v>62924238436.85561</v>
       </c>
       <c r="M4" s="3">
-        <v>61560883075.37518</v>
+        <v>63990247910.89261</v>
       </c>
       <c r="N4" s="3">
-        <v>62684358587.19784</v>
+        <v>65158058912.48797</v>
       </c>
       <c r="O4" s="3">
-        <v>63879579600.01234</v>
+        <v>66400446693.45375</v>
       </c>
       <c r="P4" s="3">
-        <v>65120666022.78342</v>
+        <v>67690509861.89019</v>
       </c>
       <c r="Q4" s="3">
-        <v>66404783080.29506</v>
+        <v>69025301774.41304</v>
       </c>
       <c r="R4" s="3">
-        <v>785522903875.322</v>
+        <v>816521837367.4178</v>
       </c>
     </row>
     <row r="5" spans="1:18">
-      <c r="A5" s="2"/>
+      <c r="A5" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B5" s="3" t="s">
         <v>9</v>
       </c>
@@ -14482,50 +14886,52 @@
         <v>0</v>
       </c>
       <c r="E5" s="3">
-        <v>529968231.2985607</v>
+        <v>550882261.7792752</v>
       </c>
       <c r="F5" s="3">
-        <v>532251550.2666471</v>
+        <v>553255686.9078362</v>
       </c>
       <c r="G5" s="3">
-        <v>536731534.4416463</v>
+        <v>557912463.8037111</v>
       </c>
       <c r="H5" s="3">
-        <v>542779021.183197</v>
+        <v>564198601.3069019</v>
       </c>
       <c r="I5" s="3">
-        <v>550363603.9510771</v>
+        <v>572082492.9499619</v>
       </c>
       <c r="J5" s="3">
-        <v>559301839.7417635</v>
+        <v>581373456.5547513</v>
       </c>
       <c r="K5" s="3">
-        <v>568797693.6316798</v>
+        <v>591244043.4304688</v>
       </c>
       <c r="L5" s="3">
-        <v>579278496.1094207</v>
+        <v>602138447.7234443</v>
       </c>
       <c r="M5" s="3">
-        <v>590535859.0693423</v>
+        <v>613840057.7498354</v>
       </c>
       <c r="N5" s="3">
-        <v>602126189.5041794</v>
+        <v>625887775.0801128</v>
       </c>
       <c r="O5" s="3">
-        <v>613931824.9792103</v>
+        <v>638159293.9903905</v>
       </c>
       <c r="P5" s="3">
-        <v>626314396.7609556</v>
+        <v>651030516.7296441</v>
       </c>
       <c r="Q5" s="3">
-        <v>638944181.8739184</v>
+        <v>664158708.5304384</v>
       </c>
       <c r="R5" s="3">
-        <v>7471324422.811598</v>
+        <v>7766163806.536771</v>
       </c>
     </row>
     <row r="6" spans="1:18">
-      <c r="A6" s="2"/>
+      <c r="A6" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B6" s="3" t="s">
         <v>9</v>
       </c>
@@ -14536,50 +14942,52 @@
         <v>0</v>
       </c>
       <c r="E6" s="3">
-        <v>371153973.8899809</v>
+        <v>385800749.0446984</v>
       </c>
       <c r="F6" s="3">
-        <v>377989139.1187045</v>
+        <v>392905649.0339075</v>
       </c>
       <c r="G6" s="3">
-        <v>384921674.4202215</v>
+        <v>400111761.5916485</v>
       </c>
       <c r="H6" s="3">
-        <v>391811143.9281518</v>
+        <v>407273108.8589906</v>
       </c>
       <c r="I6" s="3">
-        <v>400253556.4155774</v>
+        <v>416048682.5845155</v>
       </c>
       <c r="J6" s="3">
-        <v>408850339.0199658</v>
+        <v>424984718.3041024</v>
       </c>
       <c r="K6" s="3">
-        <v>415901683.5418094</v>
+        <v>432314328.6267064</v>
       </c>
       <c r="L6" s="3">
-        <v>425910856.3466597</v>
+        <v>442718491.4191913</v>
       </c>
       <c r="M6" s="3">
-        <v>434662943.8007965</v>
+        <v>451815960.7527988</v>
       </c>
       <c r="N6" s="3">
-        <v>443280608.1166174</v>
+        <v>460773702.2346267</v>
       </c>
       <c r="O6" s="3">
-        <v>451889208.1500798</v>
+        <v>469722021.7321313</v>
       </c>
       <c r="P6" s="3">
-        <v>462053042.4917805</v>
+        <v>480286949.4388104</v>
       </c>
       <c r="Q6" s="3">
-        <v>470815557.1323059</v>
+        <v>489395257.4447808</v>
       </c>
       <c r="R6" s="3">
-        <v>5439493726.372651</v>
+        <v>5654151381.066908</v>
       </c>
     </row>
     <row r="7" spans="1:18">
-      <c r="A7" s="2"/>
+      <c r="A7" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
@@ -14590,50 +14998,52 @@
         <v>0</v>
       </c>
       <c r="E7" s="3">
-        <v>253350301.3796923</v>
+        <v>263348213.7307218</v>
       </c>
       <c r="F7" s="3">
-        <v>259242168.8536388</v>
+        <v>269472590.794227</v>
       </c>
       <c r="G7" s="3">
-        <v>263955662.8327957</v>
+        <v>274372092.445031</v>
       </c>
       <c r="H7" s="3">
-        <v>268669156.8119528</v>
+        <v>279271594.0958351</v>
       </c>
       <c r="I7" s="3">
-        <v>274561024.2858991</v>
+        <v>285395971.1593403</v>
       </c>
       <c r="J7" s="3">
-        <v>280452891.7598454</v>
+        <v>291520348.2228454</v>
       </c>
       <c r="K7" s="3">
-        <v>285166385.7390026</v>
+        <v>296419849.8736495</v>
       </c>
       <c r="L7" s="3">
-        <v>292236626.7077382</v>
+        <v>303769102.3498557</v>
       </c>
       <c r="M7" s="3">
-        <v>298128494.1816843</v>
+        <v>309893479.4133608</v>
       </c>
       <c r="N7" s="3">
-        <v>304020361.6556309</v>
+        <v>316017856.4768662</v>
       </c>
       <c r="O7" s="3">
-        <v>309912229.1295773</v>
+        <v>322142233.5403714</v>
       </c>
       <c r="P7" s="3">
-        <v>316982470.0983128</v>
+        <v>329491486.0165773</v>
       </c>
       <c r="Q7" s="3">
-        <v>322874337.5722591</v>
+        <v>335615863.0800826</v>
       </c>
       <c r="R7" s="3">
-        <v>3729552111.00803</v>
+        <v>3876730681.198764</v>
       </c>
     </row>
     <row r="8" spans="1:18">
-      <c r="A8" s="2"/>
+      <c r="A8" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
@@ -14644,50 +15054,52 @@
         <v>0</v>
       </c>
       <c r="E8" s="3">
-        <v>492935409.4793717</v>
+        <v>517454059.0277524</v>
       </c>
       <c r="F8" s="3">
-        <v>502280156.5785067</v>
+        <v>527263614.6491316</v>
       </c>
       <c r="G8" s="3">
-        <v>513961090.4524255</v>
+        <v>539525559.1758556</v>
       </c>
       <c r="H8" s="3">
-        <v>523305837.5515603</v>
+        <v>549335114.7972348</v>
       </c>
       <c r="I8" s="3">
-        <v>532650584.6506955</v>
+        <v>559144670.4186139</v>
       </c>
       <c r="J8" s="3">
-        <v>544331518.5246145</v>
+        <v>571406614.945338</v>
       </c>
       <c r="K8" s="3">
-        <v>556012452.3985329</v>
+        <v>583668559.4720618</v>
       </c>
       <c r="L8" s="3">
-        <v>565357199.4976683</v>
+        <v>593478115.0934411</v>
       </c>
       <c r="M8" s="3">
-        <v>579374320.1463703</v>
+        <v>608192448.5255101</v>
       </c>
       <c r="N8" s="3">
-        <v>591055254.0202894</v>
+        <v>620454393.0522339</v>
       </c>
       <c r="O8" s="3">
-        <v>602736187.8942081</v>
+        <v>632716337.5789579</v>
       </c>
       <c r="P8" s="3">
-        <v>614417121.7681268</v>
+        <v>644978282.1056819</v>
       </c>
       <c r="Q8" s="3">
-        <v>628434242.4168293</v>
+        <v>659692615.5377506</v>
       </c>
       <c r="R8" s="3">
-        <v>7246851375.379198</v>
+        <v>7607310384.379562</v>
       </c>
     </row>
     <row r="9" spans="1:18">
-      <c r="A9" s="2"/>
+      <c r="A9" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
@@ -14741,7 +15153,9 @@
       </c>
     </row>
     <row r="10" spans="1:18">
-      <c r="A10" s="2"/>
+      <c r="A10" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
@@ -14752,46 +15166,46 @@
         <v>0</v>
       </c>
       <c r="E10" s="3">
-        <v>82289051120.54446</v>
+        <v>85541470193.56918</v>
       </c>
       <c r="F10" s="3">
-        <v>82895882827.85736</v>
+        <v>86172345139.93823</v>
       </c>
       <c r="G10" s="3">
-        <v>83565332115.47328</v>
+        <v>86868332756.94853</v>
       </c>
       <c r="H10" s="3">
-        <v>84319767419.17938</v>
+        <v>87652636166.57243</v>
       </c>
       <c r="I10" s="3">
-        <v>85308010897.82478</v>
+        <v>88679974460.84073</v>
       </c>
       <c r="J10" s="3">
-        <v>86488567053.73636</v>
+        <v>89907238638.81313</v>
       </c>
       <c r="K10" s="3">
-        <v>87771863118.46143</v>
+        <v>91241297145.71661</v>
       </c>
       <c r="L10" s="3">
-        <v>89315283347.32379</v>
+        <v>92845721003.81821</v>
       </c>
       <c r="M10" s="3">
-        <v>90924466503.55721</v>
+        <v>94518551013.49059</v>
       </c>
       <c r="N10" s="3">
-        <v>92627493605.49867</v>
+        <v>96288904304.10214</v>
       </c>
       <c r="O10" s="3">
-        <v>94405905825.94839</v>
+        <v>98137617621.09976</v>
       </c>
       <c r="P10" s="3">
-        <v>96305255306.00609</v>
+        <v>100112040705.0183</v>
       </c>
       <c r="Q10" s="3">
-        <v>98197847180.96642</v>
+        <v>102079463535.09</v>
       </c>
       <c r="R10" s="3">
-        <v>1154414726322.378</v>
+        <v>1200045592685.018</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -14824,50 +15238,52 @@
         <v>0</v>
       </c>
       <c r="E12" s="3">
-        <v>21893233471.9179</v>
+        <v>22757201772.49164</v>
       </c>
       <c r="F12" s="3">
-        <v>22167758537.44982</v>
+        <v>23042560365.86388</v>
       </c>
       <c r="G12" s="3">
-        <v>22489673071.13091</v>
+        <v>23377178548.50349</v>
       </c>
       <c r="H12" s="3">
-        <v>22833775762.75388</v>
+        <v>23734860495.93104</v>
       </c>
       <c r="I12" s="3">
-        <v>23254413737.78478</v>
+        <v>24172098023.37206</v>
       </c>
       <c r="J12" s="3">
-        <v>23705384711.64853</v>
+        <v>24640865574.72158</v>
       </c>
       <c r="K12" s="3">
-        <v>24113345506.5336</v>
+        <v>25064925644.98824</v>
       </c>
       <c r="L12" s="3">
-        <v>24634348495.03687</v>
+        <v>25606488870.38609</v>
       </c>
       <c r="M12" s="3">
-        <v>25132380379.68119</v>
+        <v>26124174487.84058</v>
       </c>
       <c r="N12" s="3">
-        <v>25628188333.97533</v>
+        <v>26639548412.42558</v>
       </c>
       <c r="O12" s="3">
-        <v>26127411536.46332</v>
+        <v>27158472360.46189</v>
       </c>
       <c r="P12" s="3">
-        <v>26688866879.43789</v>
+        <v>27742084303.51749</v>
       </c>
       <c r="Q12" s="3">
-        <v>27210367269.9337</v>
+        <v>28284164559.78339</v>
       </c>
       <c r="R12" s="3">
-        <v>315879147693.7477</v>
+        <v>328344623420.2869</v>
       </c>
     </row>
     <row r="13" spans="1:18">
-      <c r="A13" s="2"/>
+      <c r="A13" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B13" s="3" t="s">
         <v>39</v>
       </c>
@@ -14878,50 +15294,52 @@
         <v>0</v>
       </c>
       <c r="E13" s="3">
-        <v>2717436179.375196</v>
+        <v>2824673820.668513</v>
       </c>
       <c r="F13" s="3">
-        <v>2780632369.593224</v>
+        <v>2890363909.521269</v>
       </c>
       <c r="G13" s="3">
-        <v>2831189321.767645</v>
+        <v>2942915980.603474</v>
       </c>
       <c r="H13" s="3">
-        <v>2881746273.942068</v>
+        <v>2995468051.685678</v>
       </c>
       <c r="I13" s="3">
-        <v>2944942464.160095</v>
+        <v>3061158140.538435</v>
       </c>
       <c r="J13" s="3">
-        <v>3008138654.378123</v>
+        <v>3126848229.391191</v>
       </c>
       <c r="K13" s="3">
-        <v>3058695606.552545</v>
+        <v>3179400300.473396</v>
       </c>
       <c r="L13" s="3">
-        <v>3134531034.814178</v>
+        <v>3258228407.096702</v>
       </c>
       <c r="M13" s="3">
-        <v>3197727225.032207</v>
+        <v>3323918495.949458</v>
       </c>
       <c r="N13" s="3">
-        <v>3260923415.250234</v>
+        <v>3389608584.802216</v>
       </c>
       <c r="O13" s="3">
-        <v>3324119605.468262</v>
+        <v>3455298673.654972</v>
       </c>
       <c r="P13" s="3">
-        <v>3399955033.729896</v>
+        <v>3534126780.278278</v>
       </c>
       <c r="Q13" s="3">
-        <v>3463151223.947923</v>
+        <v>3599816869.131035</v>
       </c>
       <c r="R13" s="3">
-        <v>40003188408.01159</v>
+        <v>41581826243.79461</v>
       </c>
     </row>
     <row r="14" spans="1:18">
-      <c r="A14" s="2"/>
+      <c r="A14" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B14" s="3" t="s">
         <v>39</v>
       </c>
@@ -14932,50 +15350,52 @@
         <v>0</v>
       </c>
       <c r="E14" s="3">
-        <v>56773196440.9739</v>
+        <v>59013625754.90613</v>
       </c>
       <c r="F14" s="3">
-        <v>57031620146.08464</v>
+        <v>59282247583.08624</v>
       </c>
       <c r="G14" s="3">
-        <v>57314654488.60669</v>
+        <v>59576451253.34721</v>
       </c>
       <c r="H14" s="3">
-        <v>57661212307.69167</v>
+        <v>59936685214.44153</v>
       </c>
       <c r="I14" s="3">
-        <v>58151240858.09483</v>
+        <v>60446051663.67387</v>
       </c>
       <c r="J14" s="3">
-        <v>58799713617.25073</v>
+        <v>61120114973.8288</v>
       </c>
       <c r="K14" s="3">
-        <v>59605651415.18334</v>
+        <v>61957857334.14098</v>
       </c>
       <c r="L14" s="3">
-        <v>60535344235.77234</v>
+        <v>62924238436.85561</v>
       </c>
       <c r="M14" s="3">
-        <v>61560883075.37518</v>
+        <v>63990247910.89261</v>
       </c>
       <c r="N14" s="3">
-        <v>62684358587.19784</v>
+        <v>65158058912.48797</v>
       </c>
       <c r="O14" s="3">
-        <v>63879579600.01234</v>
+        <v>66400446693.45375</v>
       </c>
       <c r="P14" s="3">
-        <v>65120666022.78342</v>
+        <v>67690509861.89019</v>
       </c>
       <c r="Q14" s="3">
-        <v>66404783080.29506</v>
+        <v>69025301774.41304</v>
       </c>
       <c r="R14" s="3">
-        <v>785522903875.322</v>
+        <v>816521837367.4178</v>
       </c>
     </row>
     <row r="15" spans="1:18">
-      <c r="A15" s="2"/>
+      <c r="A15" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B15" s="3" t="s">
         <v>39</v>
       </c>
@@ -14986,50 +15406,52 @@
         <v>0</v>
       </c>
       <c r="E15" s="3">
-        <v>529968231.2985607</v>
+        <v>550882261.7792752</v>
       </c>
       <c r="F15" s="3">
-        <v>532251550.2666471</v>
+        <v>553255686.9078362</v>
       </c>
       <c r="G15" s="3">
-        <v>536731534.4416463</v>
+        <v>557912463.8037111</v>
       </c>
       <c r="H15" s="3">
-        <v>542779021.183197</v>
+        <v>564198601.3069019</v>
       </c>
       <c r="I15" s="3">
-        <v>550363603.9510771</v>
+        <v>572082492.9499619</v>
       </c>
       <c r="J15" s="3">
-        <v>559301839.7417635</v>
+        <v>581373456.5547513</v>
       </c>
       <c r="K15" s="3">
-        <v>568797693.6316798</v>
+        <v>591244043.4304688</v>
       </c>
       <c r="L15" s="3">
-        <v>579278496.1094207</v>
+        <v>602138447.7234443</v>
       </c>
       <c r="M15" s="3">
-        <v>590535859.0693423</v>
+        <v>613840057.7498354</v>
       </c>
       <c r="N15" s="3">
-        <v>602126189.5041794</v>
+        <v>625887775.0801128</v>
       </c>
       <c r="O15" s="3">
-        <v>613931824.9792103</v>
+        <v>638159293.9903905</v>
       </c>
       <c r="P15" s="3">
-        <v>626314396.7609556</v>
+        <v>651030516.7296441</v>
       </c>
       <c r="Q15" s="3">
-        <v>638944181.8739184</v>
+        <v>664158708.5304384</v>
       </c>
       <c r="R15" s="3">
-        <v>7471324422.811598</v>
+        <v>7766163806.536771</v>
       </c>
     </row>
     <row r="16" spans="1:18">
-      <c r="A16" s="2"/>
+      <c r="A16" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B16" s="3" t="s">
         <v>39</v>
       </c>
@@ -15040,50 +15462,52 @@
         <v>0</v>
       </c>
       <c r="E16" s="3">
-        <v>371153973.8899809</v>
+        <v>385800749.0446984</v>
       </c>
       <c r="F16" s="3">
-        <v>377989139.1187045</v>
+        <v>392905649.0339075</v>
       </c>
       <c r="G16" s="3">
-        <v>384921674.4202215</v>
+        <v>400111761.5916485</v>
       </c>
       <c r="H16" s="3">
-        <v>391811143.9281518</v>
+        <v>407273108.8589906</v>
       </c>
       <c r="I16" s="3">
-        <v>400253556.4155774</v>
+        <v>416048682.5845155</v>
       </c>
       <c r="J16" s="3">
-        <v>408850339.0199658</v>
+        <v>424984718.3041024</v>
       </c>
       <c r="K16" s="3">
-        <v>415901683.5418094</v>
+        <v>432314328.6267064</v>
       </c>
       <c r="L16" s="3">
-        <v>425910856.3466597</v>
+        <v>442718491.4191913</v>
       </c>
       <c r="M16" s="3">
-        <v>434662943.8007965</v>
+        <v>451815960.7527988</v>
       </c>
       <c r="N16" s="3">
-        <v>443280608.1166174</v>
+        <v>460773702.2346267</v>
       </c>
       <c r="O16" s="3">
-        <v>451889208.1500798</v>
+        <v>469722021.7321313</v>
       </c>
       <c r="P16" s="3">
-        <v>462053042.4917805</v>
+        <v>480286949.4388104</v>
       </c>
       <c r="Q16" s="3">
-        <v>470815557.1323059</v>
+        <v>489395257.4447808</v>
       </c>
       <c r="R16" s="3">
-        <v>5439493726.372651</v>
+        <v>5654151381.066908</v>
       </c>
     </row>
     <row r="17" spans="1:18">
-      <c r="A17" s="2"/>
+      <c r="A17" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B17" s="3" t="s">
         <v>39</v>
       </c>
@@ -15094,50 +15518,52 @@
         <v>0</v>
       </c>
       <c r="E17" s="3">
-        <v>253350301.3796923</v>
+        <v>263348213.7307218</v>
       </c>
       <c r="F17" s="3">
-        <v>259242168.8536388</v>
+        <v>269472590.794227</v>
       </c>
       <c r="G17" s="3">
-        <v>263955662.8327957</v>
+        <v>274372092.445031</v>
       </c>
       <c r="H17" s="3">
-        <v>268669156.8119528</v>
+        <v>279271594.0958351</v>
       </c>
       <c r="I17" s="3">
-        <v>274561024.2858991</v>
+        <v>285395971.1593403</v>
       </c>
       <c r="J17" s="3">
-        <v>280452891.7598454</v>
+        <v>291520348.2228454</v>
       </c>
       <c r="K17" s="3">
-        <v>285166385.7390026</v>
+        <v>296419849.8736495</v>
       </c>
       <c r="L17" s="3">
-        <v>292236626.7077382</v>
+        <v>303769102.3498557</v>
       </c>
       <c r="M17" s="3">
-        <v>298128494.1816843</v>
+        <v>309893479.4133608</v>
       </c>
       <c r="N17" s="3">
-        <v>304020361.6556309</v>
+        <v>316017856.4768662</v>
       </c>
       <c r="O17" s="3">
-        <v>309912229.1295773</v>
+        <v>322142233.5403714</v>
       </c>
       <c r="P17" s="3">
-        <v>316982470.0983128</v>
+        <v>329491486.0165773</v>
       </c>
       <c r="Q17" s="3">
-        <v>322874337.5722591</v>
+        <v>335615863.0800826</v>
       </c>
       <c r="R17" s="3">
-        <v>3729552111.00803</v>
+        <v>3876730681.198764</v>
       </c>
     </row>
     <row r="18" spans="1:18">
-      <c r="A18" s="2"/>
+      <c r="A18" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B18" s="3" t="s">
         <v>39</v>
       </c>
@@ -15148,50 +15574,52 @@
         <v>0</v>
       </c>
       <c r="E18" s="3">
-        <v>492935409.4793717</v>
+        <v>517454059.0277524</v>
       </c>
       <c r="F18" s="3">
-        <v>502280156.5785067</v>
+        <v>527263614.6491316</v>
       </c>
       <c r="G18" s="3">
-        <v>513961090.4524255</v>
+        <v>539525559.1758556</v>
       </c>
       <c r="H18" s="3">
-        <v>523305837.5515603</v>
+        <v>549335114.7972348</v>
       </c>
       <c r="I18" s="3">
-        <v>532650584.6506955</v>
+        <v>559144670.4186139</v>
       </c>
       <c r="J18" s="3">
-        <v>544331518.5246145</v>
+        <v>571406614.945338</v>
       </c>
       <c r="K18" s="3">
-        <v>556012452.3985329</v>
+        <v>583668559.4720618</v>
       </c>
       <c r="L18" s="3">
-        <v>565357199.4976683</v>
+        <v>593478115.0934411</v>
       </c>
       <c r="M18" s="3">
-        <v>579374320.1463703</v>
+        <v>608192448.5255101</v>
       </c>
       <c r="N18" s="3">
-        <v>591055254.0202894</v>
+        <v>620454393.0522339</v>
       </c>
       <c r="O18" s="3">
-        <v>602736187.8942081</v>
+        <v>632716337.5789579</v>
       </c>
       <c r="P18" s="3">
-        <v>614417121.7681268</v>
+        <v>644978282.1056819</v>
       </c>
       <c r="Q18" s="3">
-        <v>628434242.4168293</v>
+        <v>659692615.5377506</v>
       </c>
       <c r="R18" s="3">
-        <v>7246851375.379198</v>
+        <v>7607310384.379562</v>
       </c>
     </row>
     <row r="19" spans="1:18">
-      <c r="A19" s="2"/>
+      <c r="A19" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B19" s="3" t="s">
         <v>39</v>
       </c>
@@ -15245,7 +15673,9 @@
       </c>
     </row>
     <row r="20" spans="1:18">
-      <c r="A20" s="2"/>
+      <c r="A20" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B20" s="3" t="s">
         <v>39</v>
       </c>
@@ -15256,46 +15686,46 @@
         <v>0</v>
       </c>
       <c r="E20" s="3">
-        <v>82289051120.54446</v>
+        <v>85541470193.56918</v>
       </c>
       <c r="F20" s="3">
-        <v>82895882827.85736</v>
+        <v>86172345139.93823</v>
       </c>
       <c r="G20" s="3">
-        <v>83565332115.47328</v>
+        <v>86868332756.94853</v>
       </c>
       <c r="H20" s="3">
-        <v>84319767419.17938</v>
+        <v>87652636166.57243</v>
       </c>
       <c r="I20" s="3">
-        <v>85308010897.82478</v>
+        <v>88679974460.84073</v>
       </c>
       <c r="J20" s="3">
-        <v>86488567053.73636</v>
+        <v>89907238638.81313</v>
       </c>
       <c r="K20" s="3">
-        <v>87771863118.46143</v>
+        <v>91241297145.71661</v>
       </c>
       <c r="L20" s="3">
-        <v>89315283347.32379</v>
+        <v>92845721003.81821</v>
       </c>
       <c r="M20" s="3">
-        <v>90924466503.55721</v>
+        <v>94518551013.49059</v>
       </c>
       <c r="N20" s="3">
-        <v>92627493605.49867</v>
+        <v>96288904304.10214</v>
       </c>
       <c r="O20" s="3">
-        <v>94405905825.94839</v>
+        <v>98137617621.09976</v>
       </c>
       <c r="P20" s="3">
-        <v>96305255306.00609</v>
+        <v>100112040705.0183</v>
       </c>
       <c r="Q20" s="3">
-        <v>98197847180.96642</v>
+        <v>102079463535.09</v>
       </c>
       <c r="R20" s="3">
-        <v>1154414726322.378</v>
+        <v>1200045592685.018</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -15328,50 +15758,52 @@
         <v>0</v>
       </c>
       <c r="E22" s="3">
-        <v>21893233471.9179</v>
+        <v>22757201772.49164</v>
       </c>
       <c r="F22" s="3">
-        <v>22167758537.44982</v>
+        <v>23042560365.86388</v>
       </c>
       <c r="G22" s="3">
-        <v>22489673071.13091</v>
+        <v>23377178548.50349</v>
       </c>
       <c r="H22" s="3">
-        <v>22833775762.75388</v>
+        <v>23734860495.93104</v>
       </c>
       <c r="I22" s="3">
-        <v>23254413737.78478</v>
+        <v>24172098023.37206</v>
       </c>
       <c r="J22" s="3">
-        <v>23705384711.64853</v>
+        <v>24640865574.72158</v>
       </c>
       <c r="K22" s="3">
-        <v>24113345506.5336</v>
+        <v>25064925644.98824</v>
       </c>
       <c r="L22" s="3">
-        <v>24634348495.03687</v>
+        <v>25606488870.38609</v>
       </c>
       <c r="M22" s="3">
-        <v>25132380379.68119</v>
+        <v>26124174487.84058</v>
       </c>
       <c r="N22" s="3">
-        <v>25628188333.97533</v>
+        <v>26639548412.42558</v>
       </c>
       <c r="O22" s="3">
-        <v>26127411536.46332</v>
+        <v>27158472360.46189</v>
       </c>
       <c r="P22" s="3">
-        <v>26688866879.43789</v>
+        <v>27742084303.51749</v>
       </c>
       <c r="Q22" s="3">
-        <v>27210367269.9337</v>
+        <v>28284164559.78339</v>
       </c>
       <c r="R22" s="3">
-        <v>315879147693.7477</v>
+        <v>328344623420.2869</v>
       </c>
     </row>
     <row r="23" spans="1:18">
-      <c r="A23" s="2"/>
+      <c r="A23" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B23" s="3" t="s">
         <v>40</v>
       </c>
@@ -15382,50 +15814,52 @@
         <v>0</v>
       </c>
       <c r="E23" s="3">
-        <v>2717436179.375196</v>
+        <v>2824673820.668513</v>
       </c>
       <c r="F23" s="3">
-        <v>2780632369.593224</v>
+        <v>2890363909.521269</v>
       </c>
       <c r="G23" s="3">
-        <v>2831189321.767645</v>
+        <v>2942915980.603474</v>
       </c>
       <c r="H23" s="3">
-        <v>2881746273.942068</v>
+        <v>2995468051.685678</v>
       </c>
       <c r="I23" s="3">
-        <v>2944942464.160095</v>
+        <v>3061158140.538435</v>
       </c>
       <c r="J23" s="3">
-        <v>3008138654.378123</v>
+        <v>3126848229.391191</v>
       </c>
       <c r="K23" s="3">
-        <v>3058695606.552545</v>
+        <v>3179400300.473396</v>
       </c>
       <c r="L23" s="3">
-        <v>3134531034.814178</v>
+        <v>3258228407.096702</v>
       </c>
       <c r="M23" s="3">
-        <v>3197727225.032207</v>
+        <v>3323918495.949458</v>
       </c>
       <c r="N23" s="3">
-        <v>3260923415.250234</v>
+        <v>3389608584.802216</v>
       </c>
       <c r="O23" s="3">
-        <v>3324119605.468262</v>
+        <v>3455298673.654972</v>
       </c>
       <c r="P23" s="3">
-        <v>3399955033.729896</v>
+        <v>3534126780.278278</v>
       </c>
       <c r="Q23" s="3">
-        <v>3463151223.947923</v>
+        <v>3599816869.131035</v>
       </c>
       <c r="R23" s="3">
-        <v>40003188408.01159</v>
+        <v>41581826243.79461</v>
       </c>
     </row>
     <row r="24" spans="1:18">
-      <c r="A24" s="2"/>
+      <c r="A24" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B24" s="3" t="s">
         <v>40</v>
       </c>
@@ -15436,50 +15870,52 @@
         <v>0</v>
       </c>
       <c r="E24" s="3">
-        <v>56773196440.9739</v>
+        <v>59013625754.90613</v>
       </c>
       <c r="F24" s="3">
-        <v>57031620146.08464</v>
+        <v>59282247583.08624</v>
       </c>
       <c r="G24" s="3">
-        <v>57314654488.60669</v>
+        <v>59576451253.34721</v>
       </c>
       <c r="H24" s="3">
-        <v>57661212307.69167</v>
+        <v>59936685214.44153</v>
       </c>
       <c r="I24" s="3">
-        <v>58151240858.09483</v>
+        <v>60446051663.67387</v>
       </c>
       <c r="J24" s="3">
-        <v>58799713617.25073</v>
+        <v>61120114973.8288</v>
       </c>
       <c r="K24" s="3">
-        <v>59605651415.18334</v>
+        <v>61957857334.14098</v>
       </c>
       <c r="L24" s="3">
-        <v>60535344235.77234</v>
+        <v>62924238436.85561</v>
       </c>
       <c r="M24" s="3">
-        <v>61560883075.37518</v>
+        <v>63990247910.89261</v>
       </c>
       <c r="N24" s="3">
-        <v>62684358587.19784</v>
+        <v>65158058912.48797</v>
       </c>
       <c r="O24" s="3">
-        <v>63879579600.01234</v>
+        <v>66400446693.45375</v>
       </c>
       <c r="P24" s="3">
-        <v>65120666022.78342</v>
+        <v>67690509861.89019</v>
       </c>
       <c r="Q24" s="3">
-        <v>66404783080.29506</v>
+        <v>69025301774.41304</v>
       </c>
       <c r="R24" s="3">
-        <v>785522903875.322</v>
+        <v>816521837367.4178</v>
       </c>
     </row>
     <row r="25" spans="1:18">
-      <c r="A25" s="2"/>
+      <c r="A25" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B25" s="3" t="s">
         <v>40</v>
       </c>
@@ -15490,50 +15926,52 @@
         <v>0</v>
       </c>
       <c r="E25" s="3">
-        <v>529968231.2985607</v>
+        <v>550882261.7792752</v>
       </c>
       <c r="F25" s="3">
-        <v>532251550.2666471</v>
+        <v>553255686.9078362</v>
       </c>
       <c r="G25" s="3">
-        <v>536731534.4416463</v>
+        <v>557912463.8037111</v>
       </c>
       <c r="H25" s="3">
-        <v>542779021.183197</v>
+        <v>564198601.3069019</v>
       </c>
       <c r="I25" s="3">
-        <v>550363603.9510771</v>
+        <v>572082492.9499619</v>
       </c>
       <c r="J25" s="3">
-        <v>559301839.7417635</v>
+        <v>581373456.5547513</v>
       </c>
       <c r="K25" s="3">
-        <v>568797693.6316798</v>
+        <v>591244043.4304688</v>
       </c>
       <c r="L25" s="3">
-        <v>579278496.1094207</v>
+        <v>602138447.7234443</v>
       </c>
       <c r="M25" s="3">
-        <v>590535859.0693423</v>
+        <v>613840057.7498354</v>
       </c>
       <c r="N25" s="3">
-        <v>602126189.5041794</v>
+        <v>625887775.0801128</v>
       </c>
       <c r="O25" s="3">
-        <v>613931824.9792103</v>
+        <v>638159293.9903905</v>
       </c>
       <c r="P25" s="3">
-        <v>626314396.7609556</v>
+        <v>651030516.7296441</v>
       </c>
       <c r="Q25" s="3">
-        <v>638944181.8739184</v>
+        <v>664158708.5304384</v>
       </c>
       <c r="R25" s="3">
-        <v>7471324422.811598</v>
+        <v>7766163806.536771</v>
       </c>
     </row>
     <row r="26" spans="1:18">
-      <c r="A26" s="2"/>
+      <c r="A26" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B26" s="3" t="s">
         <v>40</v>
       </c>
@@ -15544,50 +15982,52 @@
         <v>0</v>
       </c>
       <c r="E26" s="3">
-        <v>371153973.8899809</v>
+        <v>385800749.0446984</v>
       </c>
       <c r="F26" s="3">
-        <v>377989139.1187045</v>
+        <v>392905649.0339075</v>
       </c>
       <c r="G26" s="3">
-        <v>384921674.4202215</v>
+        <v>400111761.5916485</v>
       </c>
       <c r="H26" s="3">
-        <v>391811143.9281518</v>
+        <v>407273108.8589906</v>
       </c>
       <c r="I26" s="3">
-        <v>400253556.4155774</v>
+        <v>416048682.5845155</v>
       </c>
       <c r="J26" s="3">
-        <v>408850339.0199658</v>
+        <v>424984718.3041024</v>
       </c>
       <c r="K26" s="3">
-        <v>415901683.5418094</v>
+        <v>432314328.6267064</v>
       </c>
       <c r="L26" s="3">
-        <v>425910856.3466597</v>
+        <v>442718491.4191913</v>
       </c>
       <c r="M26" s="3">
-        <v>434662943.8007965</v>
+        <v>451815960.7527988</v>
       </c>
       <c r="N26" s="3">
-        <v>443280608.1166174</v>
+        <v>460773702.2346267</v>
       </c>
       <c r="O26" s="3">
-        <v>451889208.1500798</v>
+        <v>469722021.7321313</v>
       </c>
       <c r="P26" s="3">
-        <v>462053042.4917805</v>
+        <v>480286949.4388104</v>
       </c>
       <c r="Q26" s="3">
-        <v>470815557.1323059</v>
+        <v>489395257.4447808</v>
       </c>
       <c r="R26" s="3">
-        <v>5439493726.372651</v>
+        <v>5654151381.066908</v>
       </c>
     </row>
     <row r="27" spans="1:18">
-      <c r="A27" s="2"/>
+      <c r="A27" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B27" s="3" t="s">
         <v>40</v>
       </c>
@@ -15598,50 +16038,52 @@
         <v>0</v>
       </c>
       <c r="E27" s="3">
-        <v>253350301.3796923</v>
+        <v>263348213.7307218</v>
       </c>
       <c r="F27" s="3">
-        <v>259242168.8536388</v>
+        <v>269472590.794227</v>
       </c>
       <c r="G27" s="3">
-        <v>263955662.8327957</v>
+        <v>274372092.445031</v>
       </c>
       <c r="H27" s="3">
-        <v>268669156.8119528</v>
+        <v>279271594.0958351</v>
       </c>
       <c r="I27" s="3">
-        <v>274561024.2858991</v>
+        <v>285395971.1593403</v>
       </c>
       <c r="J27" s="3">
-        <v>280452891.7598454</v>
+        <v>291520348.2228454</v>
       </c>
       <c r="K27" s="3">
-        <v>285166385.7390026</v>
+        <v>296419849.8736495</v>
       </c>
       <c r="L27" s="3">
-        <v>292236626.7077382</v>
+        <v>303769102.3498557</v>
       </c>
       <c r="M27" s="3">
-        <v>298128494.1816843</v>
+        <v>309893479.4133608</v>
       </c>
       <c r="N27" s="3">
-        <v>304020361.6556309</v>
+        <v>316017856.4768662</v>
       </c>
       <c r="O27" s="3">
-        <v>309912229.1295773</v>
+        <v>322142233.5403714</v>
       </c>
       <c r="P27" s="3">
-        <v>316982470.0983128</v>
+        <v>329491486.0165773</v>
       </c>
       <c r="Q27" s="3">
-        <v>322874337.5722591</v>
+        <v>335615863.0800826</v>
       </c>
       <c r="R27" s="3">
-        <v>3729552111.00803</v>
+        <v>3876730681.198764</v>
       </c>
     </row>
     <row r="28" spans="1:18">
-      <c r="A28" s="2"/>
+      <c r="A28" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B28" s="3" t="s">
         <v>40</v>
       </c>
@@ -15652,50 +16094,52 @@
         <v>0</v>
       </c>
       <c r="E28" s="3">
-        <v>492935409.4793717</v>
+        <v>517454059.0277524</v>
       </c>
       <c r="F28" s="3">
-        <v>502280156.5785067</v>
+        <v>527263614.6491316</v>
       </c>
       <c r="G28" s="3">
-        <v>513961090.4524255</v>
+        <v>539525559.1758556</v>
       </c>
       <c r="H28" s="3">
-        <v>523305837.5515603</v>
+        <v>549335114.7972348</v>
       </c>
       <c r="I28" s="3">
-        <v>532650584.6506955</v>
+        <v>559144670.4186139</v>
       </c>
       <c r="J28" s="3">
-        <v>544331518.5246145</v>
+        <v>571406614.945338</v>
       </c>
       <c r="K28" s="3">
-        <v>556012452.3985329</v>
+        <v>583668559.4720618</v>
       </c>
       <c r="L28" s="3">
-        <v>565357199.4976683</v>
+        <v>593478115.0934411</v>
       </c>
       <c r="M28" s="3">
-        <v>579374320.1463703</v>
+        <v>608192448.5255101</v>
       </c>
       <c r="N28" s="3">
-        <v>591055254.0202894</v>
+        <v>620454393.0522339</v>
       </c>
       <c r="O28" s="3">
-        <v>602736187.8942081</v>
+        <v>632716337.5789579</v>
       </c>
       <c r="P28" s="3">
-        <v>614417121.7681268</v>
+        <v>644978282.1056819</v>
       </c>
       <c r="Q28" s="3">
-        <v>628434242.4168293</v>
+        <v>659692615.5377506</v>
       </c>
       <c r="R28" s="3">
-        <v>7246851375.379198</v>
+        <v>7607310384.379562</v>
       </c>
     </row>
     <row r="29" spans="1:18">
-      <c r="A29" s="2"/>
+      <c r="A29" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B29" s="3" t="s">
         <v>40</v>
       </c>
@@ -15749,7 +16193,9 @@
       </c>
     </row>
     <row r="30" spans="1:18">
-      <c r="A30" s="2"/>
+      <c r="A30" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B30" s="3" t="s">
         <v>40</v>
       </c>
@@ -15760,46 +16206,46 @@
         <v>0</v>
       </c>
       <c r="E30" s="3">
-        <v>82289051120.54446</v>
+        <v>85541470193.56918</v>
       </c>
       <c r="F30" s="3">
-        <v>82895882827.85736</v>
+        <v>86172345139.93823</v>
       </c>
       <c r="G30" s="3">
-        <v>83565332115.47328</v>
+        <v>86868332756.94853</v>
       </c>
       <c r="H30" s="3">
-        <v>84319767419.17938</v>
+        <v>87652636166.57243</v>
       </c>
       <c r="I30" s="3">
-        <v>85308010897.82478</v>
+        <v>88679974460.84073</v>
       </c>
       <c r="J30" s="3">
-        <v>86488567053.73636</v>
+        <v>89907238638.81313</v>
       </c>
       <c r="K30" s="3">
-        <v>87771863118.46143</v>
+        <v>91241297145.71661</v>
       </c>
       <c r="L30" s="3">
-        <v>89315283347.32379</v>
+        <v>92845721003.81821</v>
       </c>
       <c r="M30" s="3">
-        <v>90924466503.55721</v>
+        <v>94518551013.49059</v>
       </c>
       <c r="N30" s="3">
-        <v>92627493605.49867</v>
+        <v>96288904304.10214</v>
       </c>
       <c r="O30" s="3">
-        <v>94405905825.94839</v>
+        <v>98137617621.09976</v>
       </c>
       <c r="P30" s="3">
-        <v>96305255306.00609</v>
+        <v>100112040705.0183</v>
       </c>
       <c r="Q30" s="3">
-        <v>98197847180.96642</v>
+        <v>102079463535.09</v>
       </c>
       <c r="R30" s="3">
-        <v>1154414726322.378</v>
+        <v>1200045592685.018</v>
       </c>
     </row>
     <row r="31" spans="1:18">
@@ -15832,50 +16278,52 @@
         <v>0</v>
       </c>
       <c r="E32" s="3">
-        <v>21884945801.82627</v>
+        <v>22748381805.20618</v>
       </c>
       <c r="F32" s="3">
-        <v>21677070843.86264</v>
+        <v>22520353600.47911</v>
       </c>
       <c r="G32" s="3">
-        <v>21640770753.81274</v>
+        <v>22473745657.09102</v>
       </c>
       <c r="H32" s="3">
-        <v>21944734220.94604</v>
+        <v>22788709163.15194</v>
       </c>
       <c r="I32" s="3">
-        <v>22336704514.5255</v>
+        <v>23195438106.64322</v>
       </c>
       <c r="J32" s="3">
-        <v>22762618314.26274</v>
+        <v>23637539550.00182</v>
       </c>
       <c r="K32" s="3">
-        <v>23150556310.51683</v>
+        <v>24040291257.60387</v>
       </c>
       <c r="L32" s="3">
-        <v>23646202966.80606</v>
+        <v>24554869924.81215</v>
       </c>
       <c r="M32" s="3">
-        <v>24122098162.45147</v>
+        <v>25048997352.36107</v>
       </c>
       <c r="N32" s="3">
-        <v>24596616949.96372</v>
+        <v>25541714967.60299</v>
       </c>
       <c r="O32" s="3">
-        <v>25074899886.72953</v>
+        <v>26038353838.91957</v>
       </c>
       <c r="P32" s="3">
-        <v>25612252827.47128</v>
+        <v>26596315378.36823</v>
       </c>
       <c r="Q32" s="3">
-        <v>26112752186.19914</v>
+        <v>27116045769.73991</v>
       </c>
       <c r="R32" s="3">
-        <v>304562223739.374</v>
+        <v>316300756371.9811</v>
       </c>
     </row>
     <row r="33" spans="1:18">
-      <c r="A33" s="2"/>
+      <c r="A33" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B33" s="3" t="s">
         <v>9</v>
       </c>
@@ -15886,50 +16334,52 @@
         <v>0</v>
       </c>
       <c r="E33" s="3">
-        <v>2680504164.922783</v>
+        <v>2786284365.504835</v>
       </c>
       <c r="F33" s="3">
-        <v>2754427457.209621</v>
+        <v>2863124877.913214</v>
       </c>
       <c r="G33" s="3">
-        <v>2750383706.875756</v>
+        <v>2858921549.867434</v>
       </c>
       <c r="H33" s="3">
-        <v>2799497701.641396</v>
+        <v>2909973720.400781</v>
       </c>
       <c r="I33" s="3">
-        <v>2860890195.098444</v>
+        <v>2973788933.567464</v>
       </c>
       <c r="J33" s="3">
-        <v>2922282688.555493</v>
+        <v>3037604146.73415</v>
       </c>
       <c r="K33" s="3">
-        <v>2971396683.321131</v>
+        <v>3088656317.267495</v>
       </c>
       <c r="L33" s="3">
-        <v>3045067675.469589</v>
+        <v>3165234573.067517</v>
       </c>
       <c r="M33" s="3">
-        <v>3106460168.926635</v>
+        <v>3229049786.2342</v>
       </c>
       <c r="N33" s="3">
-        <v>3167852662.383685</v>
+        <v>3292864999.400885</v>
       </c>
       <c r="O33" s="3">
-        <v>3229245155.840732</v>
+        <v>3356680212.567567</v>
       </c>
       <c r="P33" s="3">
-        <v>3302916147.98919</v>
+        <v>3433258468.367589</v>
       </c>
       <c r="Q33" s="3">
-        <v>3364308641.446238</v>
+        <v>3497073681.534271</v>
       </c>
       <c r="R33" s="3">
-        <v>38955233049.68069</v>
+        <v>40492515632.4274</v>
       </c>
     </row>
     <row r="34" spans="1:18">
-      <c r="A34" s="2"/>
+      <c r="A34" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B34" s="3" t="s">
         <v>9</v>
       </c>
@@ -15940,50 +16390,52 @@
         <v>0</v>
       </c>
       <c r="E34" s="3">
-        <v>56770206471.41622</v>
+        <v>59010443727.66352</v>
       </c>
       <c r="F34" s="3">
-        <v>56990402933.03811</v>
+        <v>59238382616.6305</v>
       </c>
       <c r="G34" s="3">
-        <v>57173619873.0841</v>
+        <v>59426353759.1616</v>
       </c>
       <c r="H34" s="3">
-        <v>57330676745.15218</v>
+        <v>59584899351.43102</v>
       </c>
       <c r="I34" s="3">
-        <v>57564591490.42344</v>
+        <v>59821673615.33611</v>
       </c>
       <c r="J34" s="3">
-        <v>57963969953.29761</v>
+        <v>60230612433.13</v>
       </c>
       <c r="K34" s="3">
-        <v>58560814492.08675</v>
+        <v>60845803965.30045</v>
       </c>
       <c r="L34" s="3">
-        <v>59324608084.48129</v>
+        <v>61635607559.62009</v>
       </c>
       <c r="M34" s="3">
-        <v>60220211158.03037</v>
+        <v>62563317470.77316</v>
       </c>
       <c r="N34" s="3">
-        <v>61240399016.13001</v>
+        <v>63621192211.56274</v>
       </c>
       <c r="O34" s="3">
-        <v>62351819266.56856</v>
+        <v>64774384990.14632</v>
       </c>
       <c r="P34" s="3">
-        <v>63523258851.17417</v>
+        <v>65990318228.44353</v>
       </c>
       <c r="Q34" s="3">
-        <v>64747544751.67329</v>
+        <v>67261427826.00018</v>
       </c>
       <c r="R34" s="3">
-        <v>773762123086.5563</v>
+        <v>804004417755.1992</v>
       </c>
     </row>
     <row r="35" spans="1:18">
-      <c r="A35" s="2"/>
+      <c r="A35" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B35" s="3" t="s">
         <v>9</v>
       </c>
@@ -15994,50 +16446,52 @@
         <v>0</v>
       </c>
       <c r="E35" s="3">
-        <v>529972494.6767978</v>
+        <v>550886798.978663</v>
       </c>
       <c r="F35" s="3">
-        <v>532474662.7688444</v>
+        <v>553493130.8700848</v>
       </c>
       <c r="G35" s="3">
-        <v>537372665.5023327</v>
+        <v>558594778.3392249</v>
       </c>
       <c r="H35" s="3">
-        <v>543823236.1426177</v>
+        <v>565309893.0017341</v>
       </c>
       <c r="I35" s="3">
-        <v>551720457.8767807</v>
+        <v>573526506.703522</v>
       </c>
       <c r="J35" s="3">
-        <v>560897848.7338876</v>
+        <v>583071987.7818178</v>
       </c>
       <c r="K35" s="3">
-        <v>570577534.0425009</v>
+        <v>593138214.4618096</v>
       </c>
       <c r="L35" s="3">
-        <v>581204143.6913787</v>
+        <v>604187791.6373742</v>
       </c>
       <c r="M35" s="3">
-        <v>592580426.0295131</v>
+        <v>616015959.5233783</v>
       </c>
       <c r="N35" s="3">
-        <v>604269519.9748185</v>
+        <v>628168784.0985376</v>
       </c>
       <c r="O35" s="3">
-        <v>616159333.4607642</v>
+        <v>640529887.858981</v>
       </c>
       <c r="P35" s="3">
-        <v>628617052.5660479</v>
+        <v>653481084.7038864</v>
       </c>
       <c r="Q35" s="3">
-        <v>641315059.3753026</v>
+        <v>666681880.1555153</v>
       </c>
       <c r="R35" s="3">
-        <v>7490984434.841586</v>
+        <v>7787086698.114529</v>
       </c>
     </row>
     <row r="36" spans="1:18">
-      <c r="A36" s="2"/>
+      <c r="A36" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B36" s="3" t="s">
         <v>9</v>
       </c>
@@ -16048,50 +16502,52 @@
         <v>0</v>
       </c>
       <c r="E36" s="3">
-        <v>371163625.402302</v>
+        <v>385811020.4889482</v>
       </c>
       <c r="F36" s="3">
-        <v>378620893.8698726</v>
+        <v>393577984.022957</v>
       </c>
       <c r="G36" s="3">
-        <v>386068646.3792014</v>
+        <v>401332410.1549103</v>
       </c>
       <c r="H36" s="3">
-        <v>393028796.0285628</v>
+        <v>408568979.0064408</v>
       </c>
       <c r="I36" s="3">
-        <v>401501268.2732271</v>
+        <v>417376543.61866</v>
       </c>
       <c r="J36" s="3">
-        <v>410125146.3449111</v>
+        <v>426341415.3563595</v>
       </c>
       <c r="K36" s="3">
-        <v>417198588.8630757</v>
+        <v>433694543.1925827</v>
       </c>
       <c r="L36" s="3">
-        <v>427238829.040643</v>
+        <v>444131769.0192203</v>
       </c>
       <c r="M36" s="3">
-        <v>436018280.0764921</v>
+        <v>453258359.6934142</v>
       </c>
       <c r="N36" s="3">
-        <v>444662832.8317538</v>
+        <v>462244716.8475319</v>
       </c>
       <c r="O36" s="3">
-        <v>453298285.814876</v>
+        <v>471221614.2471001</v>
       </c>
       <c r="P36" s="3">
-        <v>463493741.0943753</v>
+        <v>481820194.118144</v>
       </c>
       <c r="Q36" s="3">
-        <v>472283660.6022543</v>
+        <v>490957667.4032573</v>
       </c>
       <c r="R36" s="3">
-        <v>5454702594.621547</v>
+        <v>5670337217.169526</v>
       </c>
     </row>
     <row r="37" spans="1:18">
-      <c r="A37" s="2"/>
+      <c r="A37" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B37" s="3" t="s">
         <v>9</v>
       </c>
@@ -16102,50 +16558,52 @@
         <v>0</v>
       </c>
       <c r="E37" s="3">
-        <v>222872877.7558642</v>
+        <v>230913108.9920408</v>
       </c>
       <c r="F37" s="3">
-        <v>207136079.422949</v>
+        <v>214016878.5984456</v>
       </c>
       <c r="G37" s="3">
-        <v>145813233.0428246</v>
+        <v>148630843.675634</v>
       </c>
       <c r="H37" s="3">
-        <v>148417040.7757322</v>
+        <v>151284965.8841275</v>
       </c>
       <c r="I37" s="3">
-        <v>151671800.4418667</v>
+        <v>154602618.6447443</v>
       </c>
       <c r="J37" s="3">
-        <v>154926560.1080012</v>
+        <v>157920271.4053611</v>
       </c>
       <c r="K37" s="3">
-        <v>157530367.8409087</v>
+        <v>160574393.6138546</v>
       </c>
       <c r="L37" s="3">
-        <v>161436079.4402701</v>
+        <v>164555576.9265949</v>
       </c>
       <c r="M37" s="3">
-        <v>164690839.1064045</v>
+        <v>167873229.6872117</v>
       </c>
       <c r="N37" s="3">
-        <v>167945598.7725391</v>
+        <v>171190882.4478285</v>
       </c>
       <c r="O37" s="3">
-        <v>171200358.4386736</v>
+        <v>174508535.2084453</v>
       </c>
       <c r="P37" s="3">
-        <v>175106070.0380349</v>
+        <v>178489718.5211855</v>
       </c>
       <c r="Q37" s="3">
-        <v>178360829.7041695</v>
+        <v>181807371.2818024</v>
       </c>
       <c r="R37" s="3">
-        <v>2207107734.888238</v>
+        <v>2256368394.887276</v>
       </c>
     </row>
     <row r="38" spans="1:18">
-      <c r="A38" s="2"/>
+      <c r="A38" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B38" s="3" t="s">
         <v>9</v>
       </c>
@@ -16156,50 +16614,52 @@
         <v>0</v>
       </c>
       <c r="E38" s="3">
-        <v>485784315.9795026</v>
+        <v>509947269.5238243</v>
       </c>
       <c r="F38" s="3">
-        <v>490009462.2680261</v>
+        <v>514382574.9511451</v>
       </c>
       <c r="G38" s="3">
-        <v>486105202.6107273</v>
+        <v>510284117.0836095</v>
       </c>
       <c r="H38" s="3">
-        <v>494943479.0218313</v>
+        <v>519562010.1214934</v>
       </c>
       <c r="I38" s="3">
-        <v>503781755.4329355</v>
+        <v>528839903.1593772</v>
       </c>
       <c r="J38" s="3">
-        <v>514829600.9468156</v>
+        <v>540437269.456732</v>
       </c>
       <c r="K38" s="3">
-        <v>525877446.4606958</v>
+        <v>552034635.7540869</v>
       </c>
       <c r="L38" s="3">
-        <v>534715722.8717999</v>
+        <v>561312528.7919705</v>
       </c>
       <c r="M38" s="3">
-        <v>547973137.4884562</v>
+        <v>575229368.3487964</v>
       </c>
       <c r="N38" s="3">
-        <v>559020983.0023365</v>
+        <v>586826734.6461511</v>
       </c>
       <c r="O38" s="3">
-        <v>570068828.5162165</v>
+        <v>598424100.9435059</v>
       </c>
       <c r="P38" s="3">
-        <v>581116674.0300967</v>
+        <v>610021467.2408607</v>
       </c>
       <c r="Q38" s="3">
-        <v>594374088.646753</v>
+        <v>623938306.7976865</v>
       </c>
       <c r="R38" s="3">
-        <v>6888600697.276194</v>
+        <v>7231240286.819241</v>
       </c>
     </row>
     <row r="39" spans="1:18">
-      <c r="A39" s="2"/>
+      <c r="A39" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B39" s="3" t="s">
         <v>9</v>
       </c>
@@ -16253,7 +16713,9 @@
       </c>
     </row>
     <row r="40" spans="1:18">
-      <c r="A40" s="2"/>
+      <c r="A40" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B40" s="3" t="s">
         <v>9</v>
       </c>
@@ -16264,46 +16726,46 @@
         <v>0</v>
       </c>
       <c r="E40" s="3">
-        <v>82203200189.72493</v>
+        <v>85451123743.9299</v>
       </c>
       <c r="F40" s="3">
-        <v>82272974880.66551</v>
+        <v>85510250031.38475</v>
       </c>
       <c r="G40" s="3">
-        <v>82348056716.77629</v>
+        <v>85575258223.2906</v>
       </c>
       <c r="H40" s="3">
-        <v>82869124626.02515</v>
+        <v>86111231123.35857</v>
       </c>
       <c r="I40" s="3">
-        <v>83567921281.5833</v>
+        <v>86830555476.49335</v>
       </c>
       <c r="J40" s="3">
-        <v>84469463493.30084</v>
+        <v>87760907916.89471</v>
       </c>
       <c r="K40" s="3">
-        <v>85519618989.29384</v>
+        <v>88846868984.6971</v>
       </c>
       <c r="L40" s="3">
-        <v>86866062192.8282</v>
+        <v>90241702534.94495</v>
       </c>
       <c r="M40" s="3">
-        <v>88318063298.74846</v>
+        <v>91747292494.02652</v>
       </c>
       <c r="N40" s="3">
-        <v>89891510921.87111</v>
+        <v>93379782887.38736</v>
       </c>
       <c r="O40" s="3">
-        <v>91560164905.899</v>
+        <v>95111730313.55669</v>
       </c>
       <c r="P40" s="3">
-        <v>93359845849.55421</v>
+        <v>96980136118.90689</v>
       </c>
       <c r="Q40" s="3">
-        <v>95166445201.50604</v>
+        <v>98856090473.16951</v>
       </c>
       <c r="R40" s="3">
-        <v>1128412452547.777</v>
+        <v>1172402930322.041</v>
       </c>
     </row>
     <row r="41" spans="1:18">
@@ -16336,50 +16798,52 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>21884945801.82627</v>
+        <v>22748381805.20618</v>
       </c>
       <c r="F42" s="3">
-        <v>21677070843.86264</v>
+        <v>22520353600.47911</v>
       </c>
       <c r="G42" s="3">
-        <v>21640770753.81274</v>
+        <v>22473745657.09102</v>
       </c>
       <c r="H42" s="3">
-        <v>21944734220.94604</v>
+        <v>22788709163.15194</v>
       </c>
       <c r="I42" s="3">
-        <v>22336704514.5255</v>
+        <v>23195438106.64322</v>
       </c>
       <c r="J42" s="3">
-        <v>22762618314.26274</v>
+        <v>23637539550.00182</v>
       </c>
       <c r="K42" s="3">
-        <v>23150556310.51683</v>
+        <v>24040291257.60387</v>
       </c>
       <c r="L42" s="3">
-        <v>23646202966.80606</v>
+        <v>24554869924.81215</v>
       </c>
       <c r="M42" s="3">
-        <v>24122098162.45147</v>
+        <v>25048997352.36107</v>
       </c>
       <c r="N42" s="3">
-        <v>24596616949.96372</v>
+        <v>25541714967.60299</v>
       </c>
       <c r="O42" s="3">
-        <v>25074899886.72953</v>
+        <v>26038353838.91957</v>
       </c>
       <c r="P42" s="3">
-        <v>25612252827.47128</v>
+        <v>26596315378.36823</v>
       </c>
       <c r="Q42" s="3">
-        <v>26112752186.19914</v>
+        <v>27116045769.73991</v>
       </c>
       <c r="R42" s="3">
-        <v>304562223739.374</v>
+        <v>316300756371.9811</v>
       </c>
     </row>
     <row r="43" spans="1:18">
-      <c r="A43" s="2"/>
+      <c r="A43" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B43" s="3" t="s">
         <v>39</v>
       </c>
@@ -16390,50 +16854,52 @@
         <v>0</v>
       </c>
       <c r="E43" s="3">
-        <v>2680504164.922783</v>
+        <v>2786284365.504835</v>
       </c>
       <c r="F43" s="3">
-        <v>2754427457.209621</v>
+        <v>2863124877.913214</v>
       </c>
       <c r="G43" s="3">
-        <v>2750383706.875756</v>
+        <v>2858921549.867434</v>
       </c>
       <c r="H43" s="3">
-        <v>2799497701.641396</v>
+        <v>2909973720.400781</v>
       </c>
       <c r="I43" s="3">
-        <v>2860890195.098444</v>
+        <v>2973788933.567464</v>
       </c>
       <c r="J43" s="3">
-        <v>2922282688.555493</v>
+        <v>3037604146.73415</v>
       </c>
       <c r="K43" s="3">
-        <v>2971396683.321131</v>
+        <v>3088656317.267495</v>
       </c>
       <c r="L43" s="3">
-        <v>3045067675.469589</v>
+        <v>3165234573.067517</v>
       </c>
       <c r="M43" s="3">
-        <v>3106460168.926635</v>
+        <v>3229049786.2342</v>
       </c>
       <c r="N43" s="3">
-        <v>3167852662.383685</v>
+        <v>3292864999.400885</v>
       </c>
       <c r="O43" s="3">
-        <v>3229245155.840732</v>
+        <v>3356680212.567567</v>
       </c>
       <c r="P43" s="3">
-        <v>3302916147.98919</v>
+        <v>3433258468.367589</v>
       </c>
       <c r="Q43" s="3">
-        <v>3364308641.446238</v>
+        <v>3497073681.534271</v>
       </c>
       <c r="R43" s="3">
-        <v>38955233049.68069</v>
+        <v>40492515632.4274</v>
       </c>
     </row>
     <row r="44" spans="1:18">
-      <c r="A44" s="2"/>
+      <c r="A44" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B44" s="3" t="s">
         <v>39</v>
       </c>
@@ -16444,50 +16910,52 @@
         <v>0</v>
       </c>
       <c r="E44" s="3">
-        <v>56770206471.41622</v>
+        <v>59010443727.66352</v>
       </c>
       <c r="F44" s="3">
-        <v>56990402933.03811</v>
+        <v>59238382616.6305</v>
       </c>
       <c r="G44" s="3">
-        <v>57173619873.0841</v>
+        <v>59426353759.1616</v>
       </c>
       <c r="H44" s="3">
-        <v>57330676745.15218</v>
+        <v>59584899351.43102</v>
       </c>
       <c r="I44" s="3">
-        <v>57564591490.42344</v>
+        <v>59821673615.33611</v>
       </c>
       <c r="J44" s="3">
-        <v>57963969953.29761</v>
+        <v>60230612433.13</v>
       </c>
       <c r="K44" s="3">
-        <v>58560814492.08675</v>
+        <v>60845803965.30045</v>
       </c>
       <c r="L44" s="3">
-        <v>59324608084.48129</v>
+        <v>61635607559.62009</v>
       </c>
       <c r="M44" s="3">
-        <v>60220211158.03037</v>
+        <v>62563317470.77316</v>
       </c>
       <c r="N44" s="3">
-        <v>61240399016.13001</v>
+        <v>63621192211.56274</v>
       </c>
       <c r="O44" s="3">
-        <v>62351819266.56856</v>
+        <v>64774384990.14632</v>
       </c>
       <c r="P44" s="3">
-        <v>63523258851.17417</v>
+        <v>65990318228.44353</v>
       </c>
       <c r="Q44" s="3">
-        <v>64747544751.67329</v>
+        <v>67261427826.00018</v>
       </c>
       <c r="R44" s="3">
-        <v>773762123086.5563</v>
+        <v>804004417755.1992</v>
       </c>
     </row>
     <row r="45" spans="1:18">
-      <c r="A45" s="2"/>
+      <c r="A45" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B45" s="3" t="s">
         <v>39</v>
       </c>
@@ -16498,50 +16966,52 @@
         <v>0</v>
       </c>
       <c r="E45" s="3">
-        <v>529972494.6767978</v>
+        <v>550886798.978663</v>
       </c>
       <c r="F45" s="3">
-        <v>532474662.7688444</v>
+        <v>553493130.8700848</v>
       </c>
       <c r="G45" s="3">
-        <v>537372665.5023327</v>
+        <v>558594778.3392249</v>
       </c>
       <c r="H45" s="3">
-        <v>543823236.1426177</v>
+        <v>565309893.0017341</v>
       </c>
       <c r="I45" s="3">
-        <v>551720457.8767807</v>
+        <v>573526506.703522</v>
       </c>
       <c r="J45" s="3">
-        <v>560897848.7338876</v>
+        <v>583071987.7818178</v>
       </c>
       <c r="K45" s="3">
-        <v>570577534.0425009</v>
+        <v>593138214.4618096</v>
       </c>
       <c r="L45" s="3">
-        <v>581204143.6913787</v>
+        <v>604187791.6373742</v>
       </c>
       <c r="M45" s="3">
-        <v>592580426.0295131</v>
+        <v>616015959.5233783</v>
       </c>
       <c r="N45" s="3">
-        <v>604269519.9748185</v>
+        <v>628168784.0985376</v>
       </c>
       <c r="O45" s="3">
-        <v>616159333.4607642</v>
+        <v>640529887.858981</v>
       </c>
       <c r="P45" s="3">
-        <v>628617052.5660479</v>
+        <v>653481084.7038864</v>
       </c>
       <c r="Q45" s="3">
-        <v>641315059.3753026</v>
+        <v>666681880.1555153</v>
       </c>
       <c r="R45" s="3">
-        <v>7490984434.841586</v>
+        <v>7787086698.114529</v>
       </c>
     </row>
     <row r="46" spans="1:18">
-      <c r="A46" s="2"/>
+      <c r="A46" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B46" s="3" t="s">
         <v>39</v>
       </c>
@@ -16552,50 +17022,52 @@
         <v>0</v>
       </c>
       <c r="E46" s="3">
-        <v>371163625.402302</v>
+        <v>385811020.4889482</v>
       </c>
       <c r="F46" s="3">
-        <v>378620893.8698726</v>
+        <v>393577984.022957</v>
       </c>
       <c r="G46" s="3">
-        <v>386068646.3792014</v>
+        <v>401332410.1549103</v>
       </c>
       <c r="H46" s="3">
-        <v>393028796.0285628</v>
+        <v>408568979.0064408</v>
       </c>
       <c r="I46" s="3">
-        <v>401501268.2732271</v>
+        <v>417376543.61866</v>
       </c>
       <c r="J46" s="3">
-        <v>410125146.3449111</v>
+        <v>426341415.3563595</v>
       </c>
       <c r="K46" s="3">
-        <v>417198588.8630757</v>
+        <v>433694543.1925827</v>
       </c>
       <c r="L46" s="3">
-        <v>427238829.040643</v>
+        <v>444131769.0192203</v>
       </c>
       <c r="M46" s="3">
-        <v>436018280.0764921</v>
+        <v>453258359.6934142</v>
       </c>
       <c r="N46" s="3">
-        <v>444662832.8317538</v>
+        <v>462244716.8475319</v>
       </c>
       <c r="O46" s="3">
-        <v>453298285.814876</v>
+        <v>471221614.2471001</v>
       </c>
       <c r="P46" s="3">
-        <v>463493741.0943753</v>
+        <v>481820194.118144</v>
       </c>
       <c r="Q46" s="3">
-        <v>472283660.6022543</v>
+        <v>490957667.4032573</v>
       </c>
       <c r="R46" s="3">
-        <v>5454702594.621547</v>
+        <v>5670337217.169526</v>
       </c>
     </row>
     <row r="47" spans="1:18">
-      <c r="A47" s="2"/>
+      <c r="A47" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B47" s="3" t="s">
         <v>39</v>
       </c>
@@ -16606,50 +17078,52 @@
         <v>0</v>
       </c>
       <c r="E47" s="3">
-        <v>222872877.7558642</v>
+        <v>230913108.9920408</v>
       </c>
       <c r="F47" s="3">
-        <v>207136079.422949</v>
+        <v>214016878.5984456</v>
       </c>
       <c r="G47" s="3">
-        <v>145813233.0428246</v>
+        <v>148630843.675634</v>
       </c>
       <c r="H47" s="3">
-        <v>148417040.7757322</v>
+        <v>151284965.8841275</v>
       </c>
       <c r="I47" s="3">
-        <v>151671800.4418667</v>
+        <v>154602618.6447443</v>
       </c>
       <c r="J47" s="3">
-        <v>154926560.1080012</v>
+        <v>157920271.4053611</v>
       </c>
       <c r="K47" s="3">
-        <v>157530367.8409087</v>
+        <v>160574393.6138546</v>
       </c>
       <c r="L47" s="3">
-        <v>161436079.4402701</v>
+        <v>164555576.9265949</v>
       </c>
       <c r="M47" s="3">
-        <v>164690839.1064045</v>
+        <v>167873229.6872117</v>
       </c>
       <c r="N47" s="3">
-        <v>167945598.7725391</v>
+        <v>171190882.4478285</v>
       </c>
       <c r="O47" s="3">
-        <v>171200358.4386736</v>
+        <v>174508535.2084453</v>
       </c>
       <c r="P47" s="3">
-        <v>175106070.0380349</v>
+        <v>178489718.5211855</v>
       </c>
       <c r="Q47" s="3">
-        <v>178360829.7041695</v>
+        <v>181807371.2818024</v>
       </c>
       <c r="R47" s="3">
-        <v>2207107734.888238</v>
+        <v>2256368394.887276</v>
       </c>
     </row>
     <row r="48" spans="1:18">
-      <c r="A48" s="2"/>
+      <c r="A48" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B48" s="3" t="s">
         <v>39</v>
       </c>
@@ -16660,50 +17134,52 @@
         <v>0</v>
       </c>
       <c r="E48" s="3">
-        <v>485784315.9795026</v>
+        <v>509947269.5238243</v>
       </c>
       <c r="F48" s="3">
-        <v>490009462.2680261</v>
+        <v>514382574.9511451</v>
       </c>
       <c r="G48" s="3">
-        <v>486105202.6107273</v>
+        <v>510284117.0836095</v>
       </c>
       <c r="H48" s="3">
-        <v>494943479.0218313</v>
+        <v>519562010.1214934</v>
       </c>
       <c r="I48" s="3">
-        <v>503781755.4329355</v>
+        <v>528839903.1593772</v>
       </c>
       <c r="J48" s="3">
-        <v>514829600.9468156</v>
+        <v>540437269.456732</v>
       </c>
       <c r="K48" s="3">
-        <v>525877446.4606958</v>
+        <v>552034635.7540869</v>
       </c>
       <c r="L48" s="3">
-        <v>534715722.8717999</v>
+        <v>561312528.7919705</v>
       </c>
       <c r="M48" s="3">
-        <v>547973137.4884562</v>
+        <v>575229368.3487964</v>
       </c>
       <c r="N48" s="3">
-        <v>559020983.0023365</v>
+        <v>586826734.6461511</v>
       </c>
       <c r="O48" s="3">
-        <v>570068828.5162165</v>
+        <v>598424100.9435059</v>
       </c>
       <c r="P48" s="3">
-        <v>581116674.0300967</v>
+        <v>610021467.2408607</v>
       </c>
       <c r="Q48" s="3">
-        <v>594374088.646753</v>
+        <v>623938306.7976865</v>
       </c>
       <c r="R48" s="3">
-        <v>6888600697.276194</v>
+        <v>7231240286.819241</v>
       </c>
     </row>
     <row r="49" spans="1:18">
-      <c r="A49" s="2"/>
+      <c r="A49" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B49" s="3" t="s">
         <v>39</v>
       </c>
@@ -16757,7 +17233,9 @@
       </c>
     </row>
     <row r="50" spans="1:18">
-      <c r="A50" s="2"/>
+      <c r="A50" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B50" s="3" t="s">
         <v>39</v>
       </c>
@@ -16768,46 +17246,46 @@
         <v>0</v>
       </c>
       <c r="E50" s="3">
-        <v>82203200189.72493</v>
+        <v>85451123743.9299</v>
       </c>
       <c r="F50" s="3">
-        <v>82272974880.66551</v>
+        <v>85510250031.38475</v>
       </c>
       <c r="G50" s="3">
-        <v>82348056716.77629</v>
+        <v>85575258223.2906</v>
       </c>
       <c r="H50" s="3">
-        <v>82869124626.02515</v>
+        <v>86111231123.35857</v>
       </c>
       <c r="I50" s="3">
-        <v>83567921281.5833</v>
+        <v>86830555476.49335</v>
       </c>
       <c r="J50" s="3">
-        <v>84469463493.30084</v>
+        <v>87760907916.89471</v>
       </c>
       <c r="K50" s="3">
-        <v>85519618989.29384</v>
+        <v>88846868984.6971</v>
       </c>
       <c r="L50" s="3">
-        <v>86866062192.8282</v>
+        <v>90241702534.94495</v>
       </c>
       <c r="M50" s="3">
-        <v>88318063298.74846</v>
+        <v>91747292494.02652</v>
       </c>
       <c r="N50" s="3">
-        <v>89891510921.87111</v>
+        <v>93379782887.38736</v>
       </c>
       <c r="O50" s="3">
-        <v>91560164905.899</v>
+        <v>95111730313.55669</v>
       </c>
       <c r="P50" s="3">
-        <v>93359845849.55421</v>
+        <v>96980136118.90689</v>
       </c>
       <c r="Q50" s="3">
-        <v>95166445201.50604</v>
+        <v>98856090473.16951</v>
       </c>
       <c r="R50" s="3">
-        <v>1128412452547.777</v>
+        <v>1172402930322.041</v>
       </c>
     </row>
     <row r="51" spans="1:18">
@@ -16840,50 +17318,52 @@
         <v>0</v>
       </c>
       <c r="E52" s="3">
-        <v>21884945801.82627</v>
+        <v>22748381805.20618</v>
       </c>
       <c r="F52" s="3">
-        <v>21677070843.86264</v>
+        <v>22520353600.47911</v>
       </c>
       <c r="G52" s="3">
-        <v>21640770753.81274</v>
+        <v>22473745657.09102</v>
       </c>
       <c r="H52" s="3">
-        <v>21944734220.94604</v>
+        <v>22788709163.15194</v>
       </c>
       <c r="I52" s="3">
-        <v>22336704514.5255</v>
+        <v>23195438106.64322</v>
       </c>
       <c r="J52" s="3">
-        <v>22762618314.26274</v>
+        <v>23637539550.00182</v>
       </c>
       <c r="K52" s="3">
-        <v>23150556310.51683</v>
+        <v>24040291257.60387</v>
       </c>
       <c r="L52" s="3">
-        <v>23646202966.80606</v>
+        <v>24554869924.81215</v>
       </c>
       <c r="M52" s="3">
-        <v>24122098162.45147</v>
+        <v>25048997352.36107</v>
       </c>
       <c r="N52" s="3">
-        <v>24596616949.96372</v>
+        <v>25541714967.60299</v>
       </c>
       <c r="O52" s="3">
-        <v>25074899886.72953</v>
+        <v>26038353838.91957</v>
       </c>
       <c r="P52" s="3">
-        <v>25612252827.47128</v>
+        <v>26596315378.36823</v>
       </c>
       <c r="Q52" s="3">
-        <v>26112752186.19914</v>
+        <v>27116045769.73991</v>
       </c>
       <c r="R52" s="3">
-        <v>304562223739.374</v>
+        <v>316300756371.9811</v>
       </c>
     </row>
     <row r="53" spans="1:18">
-      <c r="A53" s="2"/>
+      <c r="A53" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B53" s="3" t="s">
         <v>40</v>
       </c>
@@ -16894,50 +17374,52 @@
         <v>0</v>
       </c>
       <c r="E53" s="3">
-        <v>2680504164.922783</v>
+        <v>2786284365.504835</v>
       </c>
       <c r="F53" s="3">
-        <v>2754427457.209621</v>
+        <v>2863124877.913214</v>
       </c>
       <c r="G53" s="3">
-        <v>2750383706.875756</v>
+        <v>2858921549.867434</v>
       </c>
       <c r="H53" s="3">
-        <v>2799497701.641396</v>
+        <v>2909973720.400781</v>
       </c>
       <c r="I53" s="3">
-        <v>2860890195.098444</v>
+        <v>2973788933.567464</v>
       </c>
       <c r="J53" s="3">
-        <v>2922282688.555493</v>
+        <v>3037604146.73415</v>
       </c>
       <c r="K53" s="3">
-        <v>2971396683.321131</v>
+        <v>3088656317.267495</v>
       </c>
       <c r="L53" s="3">
-        <v>3045067675.469589</v>
+        <v>3165234573.067517</v>
       </c>
       <c r="M53" s="3">
-        <v>3106460168.926635</v>
+        <v>3229049786.2342</v>
       </c>
       <c r="N53" s="3">
-        <v>3167852662.383685</v>
+        <v>3292864999.400885</v>
       </c>
       <c r="O53" s="3">
-        <v>3229245155.840732</v>
+        <v>3356680212.567567</v>
       </c>
       <c r="P53" s="3">
-        <v>3302916147.98919</v>
+        <v>3433258468.367589</v>
       </c>
       <c r="Q53" s="3">
-        <v>3364308641.446238</v>
+        <v>3497073681.534271</v>
       </c>
       <c r="R53" s="3">
-        <v>38955233049.68069</v>
+        <v>40492515632.4274</v>
       </c>
     </row>
     <row r="54" spans="1:18">
-      <c r="A54" s="2"/>
+      <c r="A54" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B54" s="3" t="s">
         <v>40</v>
       </c>
@@ -16948,50 +17430,52 @@
         <v>0</v>
       </c>
       <c r="E54" s="3">
-        <v>56770206471.41622</v>
+        <v>59010443727.66352</v>
       </c>
       <c r="F54" s="3">
-        <v>56990402933.03811</v>
+        <v>59238382616.6305</v>
       </c>
       <c r="G54" s="3">
-        <v>57173619873.0841</v>
+        <v>59426353759.1616</v>
       </c>
       <c r="H54" s="3">
-        <v>57330676745.15218</v>
+        <v>59584899351.43102</v>
       </c>
       <c r="I54" s="3">
-        <v>57564591490.42344</v>
+        <v>59821673615.33611</v>
       </c>
       <c r="J54" s="3">
-        <v>57963969953.29761</v>
+        <v>60230612433.13</v>
       </c>
       <c r="K54" s="3">
-        <v>58560814492.08675</v>
+        <v>60845803965.30045</v>
       </c>
       <c r="L54" s="3">
-        <v>59324608084.48129</v>
+        <v>61635607559.62009</v>
       </c>
       <c r="M54" s="3">
-        <v>60220211158.03037</v>
+        <v>62563317470.77316</v>
       </c>
       <c r="N54" s="3">
-        <v>61240399016.13001</v>
+        <v>63621192211.56274</v>
       </c>
       <c r="O54" s="3">
-        <v>62351819266.56856</v>
+        <v>64774384990.14632</v>
       </c>
       <c r="P54" s="3">
-        <v>63523258851.17417</v>
+        <v>65990318228.44353</v>
       </c>
       <c r="Q54" s="3">
-        <v>64747544751.67329</v>
+        <v>67261427826.00018</v>
       </c>
       <c r="R54" s="3">
-        <v>773762123086.5563</v>
+        <v>804004417755.1992</v>
       </c>
     </row>
     <row r="55" spans="1:18">
-      <c r="A55" s="2"/>
+      <c r="A55" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B55" s="3" t="s">
         <v>40</v>
       </c>
@@ -17002,50 +17486,52 @@
         <v>0</v>
       </c>
       <c r="E55" s="3">
-        <v>529972494.6767978</v>
+        <v>550886798.978663</v>
       </c>
       <c r="F55" s="3">
-        <v>532474662.7688444</v>
+        <v>553493130.8700848</v>
       </c>
       <c r="G55" s="3">
-        <v>537372665.5023327</v>
+        <v>558594778.3392249</v>
       </c>
       <c r="H55" s="3">
-        <v>543823236.1426177</v>
+        <v>565309893.0017341</v>
       </c>
       <c r="I55" s="3">
-        <v>551720457.8767807</v>
+        <v>573526506.703522</v>
       </c>
       <c r="J55" s="3">
-        <v>560897848.7338876</v>
+        <v>583071987.7818178</v>
       </c>
       <c r="K55" s="3">
-        <v>570577534.0425009</v>
+        <v>593138214.4618096</v>
       </c>
       <c r="L55" s="3">
-        <v>581204143.6913787</v>
+        <v>604187791.6373742</v>
       </c>
       <c r="M55" s="3">
-        <v>592580426.0295131</v>
+        <v>616015959.5233783</v>
       </c>
       <c r="N55" s="3">
-        <v>604269519.9748185</v>
+        <v>628168784.0985376</v>
       </c>
       <c r="O55" s="3">
-        <v>616159333.4607642</v>
+        <v>640529887.858981</v>
       </c>
       <c r="P55" s="3">
-        <v>628617052.5660479</v>
+        <v>653481084.7038864</v>
       </c>
       <c r="Q55" s="3">
-        <v>641315059.3753026</v>
+        <v>666681880.1555153</v>
       </c>
       <c r="R55" s="3">
-        <v>7490984434.841586</v>
+        <v>7787086698.114529</v>
       </c>
     </row>
     <row r="56" spans="1:18">
-      <c r="A56" s="2"/>
+      <c r="A56" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B56" s="3" t="s">
         <v>40</v>
       </c>
@@ -17056,50 +17542,52 @@
         <v>0</v>
       </c>
       <c r="E56" s="3">
-        <v>371163625.402302</v>
+        <v>385811020.4889482</v>
       </c>
       <c r="F56" s="3">
-        <v>378620893.8698726</v>
+        <v>393577984.022957</v>
       </c>
       <c r="G56" s="3">
-        <v>386068646.3792014</v>
+        <v>401332410.1549103</v>
       </c>
       <c r="H56" s="3">
-        <v>393028796.0285628</v>
+        <v>408568979.0064408</v>
       </c>
       <c r="I56" s="3">
-        <v>401501268.2732271</v>
+        <v>417376543.61866</v>
       </c>
       <c r="J56" s="3">
-        <v>410125146.3449111</v>
+        <v>426341415.3563595</v>
       </c>
       <c r="K56" s="3">
-        <v>417198588.8630757</v>
+        <v>433694543.1925827</v>
       </c>
       <c r="L56" s="3">
-        <v>427238829.040643</v>
+        <v>444131769.0192203</v>
       </c>
       <c r="M56" s="3">
-        <v>436018280.0764921</v>
+        <v>453258359.6934142</v>
       </c>
       <c r="N56" s="3">
-        <v>444662832.8317538</v>
+        <v>462244716.8475319</v>
       </c>
       <c r="O56" s="3">
-        <v>453298285.814876</v>
+        <v>471221614.2471001</v>
       </c>
       <c r="P56" s="3">
-        <v>463493741.0943753</v>
+        <v>481820194.118144</v>
       </c>
       <c r="Q56" s="3">
-        <v>472283660.6022543</v>
+        <v>490957667.4032573</v>
       </c>
       <c r="R56" s="3">
-        <v>5454702594.621547</v>
+        <v>5670337217.169526</v>
       </c>
     </row>
     <row r="57" spans="1:18">
-      <c r="A57" s="2"/>
+      <c r="A57" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B57" s="3" t="s">
         <v>40</v>
       </c>
@@ -17110,50 +17598,52 @@
         <v>0</v>
       </c>
       <c r="E57" s="3">
-        <v>222872877.7558642</v>
+        <v>230913108.9920408</v>
       </c>
       <c r="F57" s="3">
-        <v>207136079.422949</v>
+        <v>214016878.5984456</v>
       </c>
       <c r="G57" s="3">
-        <v>145813233.0428246</v>
+        <v>148630843.675634</v>
       </c>
       <c r="H57" s="3">
-        <v>148417040.7757322</v>
+        <v>151284965.8841275</v>
       </c>
       <c r="I57" s="3">
-        <v>151671800.4418667</v>
+        <v>154602618.6447443</v>
       </c>
       <c r="J57" s="3">
-        <v>154926560.1080012</v>
+        <v>157920271.4053611</v>
       </c>
       <c r="K57" s="3">
-        <v>157530367.8409087</v>
+        <v>160574393.6138546</v>
       </c>
       <c r="L57" s="3">
-        <v>161436079.4402701</v>
+        <v>164555576.9265949</v>
       </c>
       <c r="M57" s="3">
-        <v>164690839.1064045</v>
+        <v>167873229.6872117</v>
       </c>
       <c r="N57" s="3">
-        <v>167945598.7725391</v>
+        <v>171190882.4478285</v>
       </c>
       <c r="O57" s="3">
-        <v>171200358.4386736</v>
+        <v>174508535.2084453</v>
       </c>
       <c r="P57" s="3">
-        <v>175106070.0380349</v>
+        <v>178489718.5211855</v>
       </c>
       <c r="Q57" s="3">
-        <v>178360829.7041695</v>
+        <v>181807371.2818024</v>
       </c>
       <c r="R57" s="3">
-        <v>2207107734.888238</v>
+        <v>2256368394.887276</v>
       </c>
     </row>
     <row r="58" spans="1:18">
-      <c r="A58" s="2"/>
+      <c r="A58" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B58" s="3" t="s">
         <v>40</v>
       </c>
@@ -17164,50 +17654,52 @@
         <v>0</v>
       </c>
       <c r="E58" s="3">
-        <v>485784315.9795026</v>
+        <v>509947269.5238243</v>
       </c>
       <c r="F58" s="3">
-        <v>490009462.2680261</v>
+        <v>514382574.9511451</v>
       </c>
       <c r="G58" s="3">
-        <v>486105202.6107273</v>
+        <v>510284117.0836095</v>
       </c>
       <c r="H58" s="3">
-        <v>494943479.0218313</v>
+        <v>519562010.1214934</v>
       </c>
       <c r="I58" s="3">
-        <v>503781755.4329355</v>
+        <v>528839903.1593772</v>
       </c>
       <c r="J58" s="3">
-        <v>514829600.9468156</v>
+        <v>540437269.456732</v>
       </c>
       <c r="K58" s="3">
-        <v>525877446.4606958</v>
+        <v>552034635.7540869</v>
       </c>
       <c r="L58" s="3">
-        <v>534715722.8717999</v>
+        <v>561312528.7919705</v>
       </c>
       <c r="M58" s="3">
-        <v>547973137.4884562</v>
+        <v>575229368.3487964</v>
       </c>
       <c r="N58" s="3">
-        <v>559020983.0023365</v>
+        <v>586826734.6461511</v>
       </c>
       <c r="O58" s="3">
-        <v>570068828.5162165</v>
+        <v>598424100.9435059</v>
       </c>
       <c r="P58" s="3">
-        <v>581116674.0300967</v>
+        <v>610021467.2408607</v>
       </c>
       <c r="Q58" s="3">
-        <v>594374088.646753</v>
+        <v>623938306.7976865</v>
       </c>
       <c r="R58" s="3">
-        <v>6888600697.276194</v>
+        <v>7231240286.819241</v>
       </c>
     </row>
     <row r="59" spans="1:18">
-      <c r="A59" s="2"/>
+      <c r="A59" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B59" s="3" t="s">
         <v>40</v>
       </c>
@@ -17261,7 +17753,9 @@
       </c>
     </row>
     <row r="60" spans="1:18">
-      <c r="A60" s="2"/>
+      <c r="A60" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B60" s="3" t="s">
         <v>40</v>
       </c>
@@ -17272,46 +17766,46 @@
         <v>0</v>
       </c>
       <c r="E60" s="3">
-        <v>82203200189.72493</v>
+        <v>85451123743.9299</v>
       </c>
       <c r="F60" s="3">
-        <v>82272974880.66551</v>
+        <v>85510250031.38475</v>
       </c>
       <c r="G60" s="3">
-        <v>82348056716.77629</v>
+        <v>85575258223.2906</v>
       </c>
       <c r="H60" s="3">
-        <v>82869124626.02515</v>
+        <v>86111231123.35857</v>
       </c>
       <c r="I60" s="3">
-        <v>83567921281.5833</v>
+        <v>86830555476.49335</v>
       </c>
       <c r="J60" s="3">
-        <v>84469463493.30084</v>
+        <v>87760907916.89471</v>
       </c>
       <c r="K60" s="3">
-        <v>85519618989.29384</v>
+        <v>88846868984.6971</v>
       </c>
       <c r="L60" s="3">
-        <v>86866062192.8282</v>
+        <v>90241702534.94495</v>
       </c>
       <c r="M60" s="3">
-        <v>88318063298.74846</v>
+        <v>91747292494.02652</v>
       </c>
       <c r="N60" s="3">
-        <v>89891510921.87111</v>
+        <v>93379782887.38736</v>
       </c>
       <c r="O60" s="3">
-        <v>91560164905.899</v>
+        <v>95111730313.55669</v>
       </c>
       <c r="P60" s="3">
-        <v>93359845849.55421</v>
+        <v>96980136118.90689</v>
       </c>
       <c r="Q60" s="3">
-        <v>95166445201.50604</v>
+        <v>98856090473.16951</v>
       </c>
       <c r="R60" s="3">
-        <v>1128412452547.777</v>
+        <v>1172402930322.041</v>
       </c>
     </row>
     <row r="61" spans="1:18">

--- a/tests/scen_results_test_2025_stillbirths.xlsx
+++ b/tests/scen_results_test_2025_stillbirths.xlsx
@@ -280,6 +280,9 @@
     <t>Total (discounted)</t>
   </si>
   <si>
+    <t>Total economic cost (discounted)</t>
+  </si>
+  <si>
     <t>Economic cost of child deaths (discounted)</t>
   </si>
   <si>
@@ -302,9 +305,6 @@
   </si>
   <si>
     <t>Economic cost of maternal anemia (discounted)</t>
-  </si>
-  <si>
-    <t>Total economic cost (discounted)</t>
   </si>
 </sst>
 </file>
@@ -14718,46 +14718,46 @@
         <v>0</v>
       </c>
       <c r="E2" s="3">
-        <v>22757201772.49164</v>
+        <v>85541470193.56918</v>
       </c>
       <c r="F2" s="3">
-        <v>23042560365.86388</v>
+        <v>86172345139.93823</v>
       </c>
       <c r="G2" s="3">
-        <v>23377178548.50349</v>
+        <v>86868332756.94853</v>
       </c>
       <c r="H2" s="3">
-        <v>23734860495.93104</v>
+        <v>87652636166.57243</v>
       </c>
       <c r="I2" s="3">
-        <v>24172098023.37206</v>
+        <v>88679974460.84073</v>
       </c>
       <c r="J2" s="3">
-        <v>24640865574.72158</v>
+        <v>89907238638.81313</v>
       </c>
       <c r="K2" s="3">
-        <v>25064925644.98824</v>
+        <v>91241297145.71661</v>
       </c>
       <c r="L2" s="3">
-        <v>25606488870.38609</v>
+        <v>92845721003.81821</v>
       </c>
       <c r="M2" s="3">
-        <v>26124174487.84058</v>
+        <v>94518551013.49059</v>
       </c>
       <c r="N2" s="3">
-        <v>26639548412.42558</v>
+        <v>96288904304.10214</v>
       </c>
       <c r="O2" s="3">
-        <v>27158472360.46189</v>
+        <v>98137617621.09976</v>
       </c>
       <c r="P2" s="3">
-        <v>27742084303.51749</v>
+        <v>100112040705.0183</v>
       </c>
       <c r="Q2" s="3">
-        <v>28284164559.78339</v>
+        <v>102079463535.09</v>
       </c>
       <c r="R2" s="3">
-        <v>328344623420.2869</v>
+        <v>1200045592685.018</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -14774,46 +14774,46 @@
         <v>0</v>
       </c>
       <c r="E3" s="3">
-        <v>2824673820.668513</v>
+        <v>22757201772.49164</v>
       </c>
       <c r="F3" s="3">
-        <v>2890363909.521269</v>
+        <v>23042560365.86388</v>
       </c>
       <c r="G3" s="3">
-        <v>2942915980.603474</v>
+        <v>23377178548.50349</v>
       </c>
       <c r="H3" s="3">
-        <v>2995468051.685678</v>
+        <v>23734860495.93104</v>
       </c>
       <c r="I3" s="3">
-        <v>3061158140.538435</v>
+        <v>24172098023.37206</v>
       </c>
       <c r="J3" s="3">
-        <v>3126848229.391191</v>
+        <v>24640865574.72158</v>
       </c>
       <c r="K3" s="3">
-        <v>3179400300.473396</v>
+        <v>25064925644.98824</v>
       </c>
       <c r="L3" s="3">
-        <v>3258228407.096702</v>
+        <v>25606488870.38609</v>
       </c>
       <c r="M3" s="3">
-        <v>3323918495.949458</v>
+        <v>26124174487.84058</v>
       </c>
       <c r="N3" s="3">
-        <v>3389608584.802216</v>
+        <v>26639548412.42558</v>
       </c>
       <c r="O3" s="3">
-        <v>3455298673.654972</v>
+        <v>27158472360.46189</v>
       </c>
       <c r="P3" s="3">
-        <v>3534126780.278278</v>
+        <v>27742084303.51749</v>
       </c>
       <c r="Q3" s="3">
-        <v>3599816869.131035</v>
+        <v>28284164559.78339</v>
       </c>
       <c r="R3" s="3">
-        <v>41581826243.79461</v>
+        <v>328344623420.2869</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -14830,46 +14830,46 @@
         <v>0</v>
       </c>
       <c r="E4" s="3">
-        <v>59013625754.90613</v>
+        <v>2824673820.668513</v>
       </c>
       <c r="F4" s="3">
-        <v>59282247583.08624</v>
+        <v>2890363909.521269</v>
       </c>
       <c r="G4" s="3">
-        <v>59576451253.34721</v>
+        <v>2942915980.603474</v>
       </c>
       <c r="H4" s="3">
-        <v>59936685214.44153</v>
+        <v>2995468051.685678</v>
       </c>
       <c r="I4" s="3">
-        <v>60446051663.67387</v>
+        <v>3061158140.538435</v>
       </c>
       <c r="J4" s="3">
-        <v>61120114973.8288</v>
+        <v>3126848229.391191</v>
       </c>
       <c r="K4" s="3">
-        <v>61957857334.14098</v>
+        <v>3179400300.473396</v>
       </c>
       <c r="L4" s="3">
-        <v>62924238436.85561</v>
+        <v>3258228407.096702</v>
       </c>
       <c r="M4" s="3">
-        <v>63990247910.89261</v>
+        <v>3323918495.949458</v>
       </c>
       <c r="N4" s="3">
-        <v>65158058912.48797</v>
+        <v>3389608584.802216</v>
       </c>
       <c r="O4" s="3">
-        <v>66400446693.45375</v>
+        <v>3455298673.654972</v>
       </c>
       <c r="P4" s="3">
-        <v>67690509861.89019</v>
+        <v>3534126780.278278</v>
       </c>
       <c r="Q4" s="3">
-        <v>69025301774.41304</v>
+        <v>3599816869.131035</v>
       </c>
       <c r="R4" s="3">
-        <v>816521837367.4178</v>
+        <v>41581826243.79461</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -14886,46 +14886,46 @@
         <v>0</v>
       </c>
       <c r="E5" s="3">
-        <v>550882261.7792752</v>
+        <v>59013625754.90613</v>
       </c>
       <c r="F5" s="3">
-        <v>553255686.9078362</v>
+        <v>59282247583.08624</v>
       </c>
       <c r="G5" s="3">
-        <v>557912463.8037111</v>
+        <v>59576451253.34721</v>
       </c>
       <c r="H5" s="3">
-        <v>564198601.3069019</v>
+        <v>59936685214.44153</v>
       </c>
       <c r="I5" s="3">
-        <v>572082492.9499619</v>
+        <v>60446051663.67387</v>
       </c>
       <c r="J5" s="3">
-        <v>581373456.5547513</v>
+        <v>61120114973.8288</v>
       </c>
       <c r="K5" s="3">
-        <v>591244043.4304688</v>
+        <v>61957857334.14098</v>
       </c>
       <c r="L5" s="3">
-        <v>602138447.7234443</v>
+        <v>62924238436.85561</v>
       </c>
       <c r="M5" s="3">
-        <v>613840057.7498354</v>
+        <v>63990247910.89261</v>
       </c>
       <c r="N5" s="3">
-        <v>625887775.0801128</v>
+        <v>65158058912.48797</v>
       </c>
       <c r="O5" s="3">
-        <v>638159293.9903905</v>
+        <v>66400446693.45375</v>
       </c>
       <c r="P5" s="3">
-        <v>651030516.7296441</v>
+        <v>67690509861.89019</v>
       </c>
       <c r="Q5" s="3">
-        <v>664158708.5304384</v>
+        <v>69025301774.41304</v>
       </c>
       <c r="R5" s="3">
-        <v>7766163806.536771</v>
+        <v>816521837367.4178</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -14942,46 +14942,46 @@
         <v>0</v>
       </c>
       <c r="E6" s="3">
-        <v>385800749.0446984</v>
+        <v>550882261.7792752</v>
       </c>
       <c r="F6" s="3">
-        <v>392905649.0339075</v>
+        <v>553255686.9078362</v>
       </c>
       <c r="G6" s="3">
-        <v>400111761.5916485</v>
+        <v>557912463.8037111</v>
       </c>
       <c r="H6" s="3">
-        <v>407273108.8589906</v>
+        <v>564198601.3069019</v>
       </c>
       <c r="I6" s="3">
-        <v>416048682.5845155</v>
+        <v>572082492.9499619</v>
       </c>
       <c r="J6" s="3">
-        <v>424984718.3041024</v>
+        <v>581373456.5547513</v>
       </c>
       <c r="K6" s="3">
-        <v>432314328.6267064</v>
+        <v>591244043.4304688</v>
       </c>
       <c r="L6" s="3">
-        <v>442718491.4191913</v>
+        <v>602138447.7234443</v>
       </c>
       <c r="M6" s="3">
-        <v>451815960.7527988</v>
+        <v>613840057.7498354</v>
       </c>
       <c r="N6" s="3">
-        <v>460773702.2346267</v>
+        <v>625887775.0801128</v>
       </c>
       <c r="O6" s="3">
-        <v>469722021.7321313</v>
+        <v>638159293.9903905</v>
       </c>
       <c r="P6" s="3">
-        <v>480286949.4388104</v>
+        <v>651030516.7296441</v>
       </c>
       <c r="Q6" s="3">
-        <v>489395257.4447808</v>
+        <v>664158708.5304384</v>
       </c>
       <c r="R6" s="3">
-        <v>5654151381.066908</v>
+        <v>7766163806.536771</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -14998,46 +14998,46 @@
         <v>0</v>
       </c>
       <c r="E7" s="3">
-        <v>263348213.7307218</v>
+        <v>385800749.0446984</v>
       </c>
       <c r="F7" s="3">
-        <v>269472590.794227</v>
+        <v>392905649.0339075</v>
       </c>
       <c r="G7" s="3">
-        <v>274372092.445031</v>
+        <v>400111761.5916485</v>
       </c>
       <c r="H7" s="3">
-        <v>279271594.0958351</v>
+        <v>407273108.8589906</v>
       </c>
       <c r="I7" s="3">
-        <v>285395971.1593403</v>
+        <v>416048682.5845155</v>
       </c>
       <c r="J7" s="3">
-        <v>291520348.2228454</v>
+        <v>424984718.3041024</v>
       </c>
       <c r="K7" s="3">
-        <v>296419849.8736495</v>
+        <v>432314328.6267064</v>
       </c>
       <c r="L7" s="3">
-        <v>303769102.3498557</v>
+        <v>442718491.4191913</v>
       </c>
       <c r="M7" s="3">
-        <v>309893479.4133608</v>
+        <v>451815960.7527988</v>
       </c>
       <c r="N7" s="3">
-        <v>316017856.4768662</v>
+        <v>460773702.2346267</v>
       </c>
       <c r="O7" s="3">
-        <v>322142233.5403714</v>
+        <v>469722021.7321313</v>
       </c>
       <c r="P7" s="3">
-        <v>329491486.0165773</v>
+        <v>480286949.4388104</v>
       </c>
       <c r="Q7" s="3">
-        <v>335615863.0800826</v>
+        <v>489395257.4447808</v>
       </c>
       <c r="R7" s="3">
-        <v>3876730681.198764</v>
+        <v>5654151381.066908</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -15054,46 +15054,46 @@
         <v>0</v>
       </c>
       <c r="E8" s="3">
-        <v>517454059.0277524</v>
+        <v>263348213.7307218</v>
       </c>
       <c r="F8" s="3">
-        <v>527263614.6491316</v>
+        <v>269472590.794227</v>
       </c>
       <c r="G8" s="3">
-        <v>539525559.1758556</v>
+        <v>274372092.445031</v>
       </c>
       <c r="H8" s="3">
-        <v>549335114.7972348</v>
+        <v>279271594.0958351</v>
       </c>
       <c r="I8" s="3">
-        <v>559144670.4186139</v>
+        <v>285395971.1593403</v>
       </c>
       <c r="J8" s="3">
-        <v>571406614.945338</v>
+        <v>291520348.2228454</v>
       </c>
       <c r="K8" s="3">
-        <v>583668559.4720618</v>
+        <v>296419849.8736495</v>
       </c>
       <c r="L8" s="3">
-        <v>593478115.0934411</v>
+        <v>303769102.3498557</v>
       </c>
       <c r="M8" s="3">
-        <v>608192448.5255101</v>
+        <v>309893479.4133608</v>
       </c>
       <c r="N8" s="3">
-        <v>620454393.0522339</v>
+        <v>316017856.4768662</v>
       </c>
       <c r="O8" s="3">
-        <v>632716337.5789579</v>
+        <v>322142233.5403714</v>
       </c>
       <c r="P8" s="3">
-        <v>644978282.1056819</v>
+        <v>329491486.0165773</v>
       </c>
       <c r="Q8" s="3">
-        <v>659692615.5377506</v>
+        <v>335615863.0800826</v>
       </c>
       <c r="R8" s="3">
-        <v>7607310384.379562</v>
+        <v>3876730681.198764</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -15110,46 +15110,46 @@
         <v>0</v>
       </c>
       <c r="E9" s="3">
-        <v>85060.00982304836</v>
+        <v>517454059.0277524</v>
       </c>
       <c r="F9" s="3">
-        <v>87038.14958637506</v>
+        <v>527263614.6491316</v>
       </c>
       <c r="G9" s="3">
-        <v>88620.66139703641</v>
+        <v>539525559.1758556</v>
       </c>
       <c r="H9" s="3">
-        <v>90203.17320769779</v>
+        <v>549335114.7972348</v>
       </c>
       <c r="I9" s="3">
-        <v>92181.31297102448</v>
+        <v>559144670.4186139</v>
       </c>
       <c r="J9" s="3">
-        <v>94159.45273435117</v>
+        <v>571406614.945338</v>
       </c>
       <c r="K9" s="3">
-        <v>95741.96454501257</v>
+        <v>583668559.4720618</v>
       </c>
       <c r="L9" s="3">
-        <v>98115.73226100462</v>
+        <v>593478115.0934411</v>
       </c>
       <c r="M9" s="3">
-        <v>100093.8720243313</v>
+        <v>608192448.5255101</v>
       </c>
       <c r="N9" s="3">
-        <v>102072.011787658</v>
+        <v>620454393.0522339</v>
       </c>
       <c r="O9" s="3">
-        <v>104050.1515509847</v>
+        <v>632716337.5789579</v>
       </c>
       <c r="P9" s="3">
-        <v>106423.9192669768</v>
+        <v>644978282.1056819</v>
       </c>
       <c r="Q9" s="3">
-        <v>108402.0590303035</v>
+        <v>659692615.5377506</v>
       </c>
       <c r="R9" s="3">
-        <v>1252162.470185805</v>
+        <v>7607310384.379562</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -15166,46 +15166,46 @@
         <v>0</v>
       </c>
       <c r="E10" s="3">
-        <v>85541470193.56918</v>
+        <v>85060.00982304836</v>
       </c>
       <c r="F10" s="3">
-        <v>86172345139.93823</v>
+        <v>87038.14958637506</v>
       </c>
       <c r="G10" s="3">
-        <v>86868332756.94853</v>
+        <v>88620.66139703641</v>
       </c>
       <c r="H10" s="3">
-        <v>87652636166.57243</v>
+        <v>90203.17320769779</v>
       </c>
       <c r="I10" s="3">
-        <v>88679974460.84073</v>
+        <v>92181.31297102448</v>
       </c>
       <c r="J10" s="3">
-        <v>89907238638.81313</v>
+        <v>94159.45273435117</v>
       </c>
       <c r="K10" s="3">
-        <v>91241297145.71661</v>
+        <v>95741.96454501257</v>
       </c>
       <c r="L10" s="3">
-        <v>92845721003.81821</v>
+        <v>98115.73226100462</v>
       </c>
       <c r="M10" s="3">
-        <v>94518551013.49059</v>
+        <v>100093.8720243313</v>
       </c>
       <c r="N10" s="3">
-        <v>96288904304.10214</v>
+        <v>102072.011787658</v>
       </c>
       <c r="O10" s="3">
-        <v>98137617621.09976</v>
+        <v>104050.1515509847</v>
       </c>
       <c r="P10" s="3">
-        <v>100112040705.0183</v>
+        <v>106423.9192669768</v>
       </c>
       <c r="Q10" s="3">
-        <v>102079463535.09</v>
+        <v>108402.0590303035</v>
       </c>
       <c r="R10" s="3">
-        <v>1200045592685.018</v>
+        <v>1252162.470185805</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -15238,46 +15238,46 @@
         <v>0</v>
       </c>
       <c r="E12" s="3">
-        <v>22757201772.49164</v>
+        <v>85541470193.56918</v>
       </c>
       <c r="F12" s="3">
-        <v>23042560365.86388</v>
+        <v>86172345139.93823</v>
       </c>
       <c r="G12" s="3">
-        <v>23377178548.50349</v>
+        <v>86868332756.94853</v>
       </c>
       <c r="H12" s="3">
-        <v>23734860495.93104</v>
+        <v>87652636166.57243</v>
       </c>
       <c r="I12" s="3">
-        <v>24172098023.37206</v>
+        <v>88679974460.84073</v>
       </c>
       <c r="J12" s="3">
-        <v>24640865574.72158</v>
+        <v>89907238638.81313</v>
       </c>
       <c r="K12" s="3">
-        <v>25064925644.98824</v>
+        <v>91241297145.71661</v>
       </c>
       <c r="L12" s="3">
-        <v>25606488870.38609</v>
+        <v>92845721003.81821</v>
       </c>
       <c r="M12" s="3">
-        <v>26124174487.84058</v>
+        <v>94518551013.49059</v>
       </c>
       <c r="N12" s="3">
-        <v>26639548412.42558</v>
+        <v>96288904304.10214</v>
       </c>
       <c r="O12" s="3">
-        <v>27158472360.46189</v>
+        <v>98137617621.09976</v>
       </c>
       <c r="P12" s="3">
-        <v>27742084303.51749</v>
+        <v>100112040705.0183</v>
       </c>
       <c r="Q12" s="3">
-        <v>28284164559.78339</v>
+        <v>102079463535.09</v>
       </c>
       <c r="R12" s="3">
-        <v>328344623420.2869</v>
+        <v>1200045592685.018</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -15294,46 +15294,46 @@
         <v>0</v>
       </c>
       <c r="E13" s="3">
-        <v>2824673820.668513</v>
+        <v>22757201772.49164</v>
       </c>
       <c r="F13" s="3">
-        <v>2890363909.521269</v>
+        <v>23042560365.86388</v>
       </c>
       <c r="G13" s="3">
-        <v>2942915980.603474</v>
+        <v>23377178548.50349</v>
       </c>
       <c r="H13" s="3">
-        <v>2995468051.685678</v>
+        <v>23734860495.93104</v>
       </c>
       <c r="I13" s="3">
-        <v>3061158140.538435</v>
+        <v>24172098023.37206</v>
       </c>
       <c r="J13" s="3">
-        <v>3126848229.391191</v>
+        <v>24640865574.72158</v>
       </c>
       <c r="K13" s="3">
-        <v>3179400300.473396</v>
+        <v>25064925644.98824</v>
       </c>
       <c r="L13" s="3">
-        <v>3258228407.096702</v>
+        <v>25606488870.38609</v>
       </c>
       <c r="M13" s="3">
-        <v>3323918495.949458</v>
+        <v>26124174487.84058</v>
       </c>
       <c r="N13" s="3">
-        <v>3389608584.802216</v>
+        <v>26639548412.42558</v>
       </c>
       <c r="O13" s="3">
-        <v>3455298673.654972</v>
+        <v>27158472360.46189</v>
       </c>
       <c r="P13" s="3">
-        <v>3534126780.278278</v>
+        <v>27742084303.51749</v>
       </c>
       <c r="Q13" s="3">
-        <v>3599816869.131035</v>
+        <v>28284164559.78339</v>
       </c>
       <c r="R13" s="3">
-        <v>41581826243.79461</v>
+        <v>328344623420.2869</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -15350,46 +15350,46 @@
         <v>0</v>
       </c>
       <c r="E14" s="3">
-        <v>59013625754.90613</v>
+        <v>2824673820.668513</v>
       </c>
       <c r="F14" s="3">
-        <v>59282247583.08624</v>
+        <v>2890363909.521269</v>
       </c>
       <c r="G14" s="3">
-        <v>59576451253.34721</v>
+        <v>2942915980.603474</v>
       </c>
       <c r="H14" s="3">
-        <v>59936685214.44153</v>
+        <v>2995468051.685678</v>
       </c>
       <c r="I14" s="3">
-        <v>60446051663.67387</v>
+        <v>3061158140.538435</v>
       </c>
       <c r="J14" s="3">
-        <v>61120114973.8288</v>
+        <v>3126848229.391191</v>
       </c>
       <c r="K14" s="3">
-        <v>61957857334.14098</v>
+        <v>3179400300.473396</v>
       </c>
       <c r="L14" s="3">
-        <v>62924238436.85561</v>
+        <v>3258228407.096702</v>
       </c>
       <c r="M14" s="3">
-        <v>63990247910.89261</v>
+        <v>3323918495.949458</v>
       </c>
       <c r="N14" s="3">
-        <v>65158058912.48797</v>
+        <v>3389608584.802216</v>
       </c>
       <c r="O14" s="3">
-        <v>66400446693.45375</v>
+        <v>3455298673.654972</v>
       </c>
       <c r="P14" s="3">
-        <v>67690509861.89019</v>
+        <v>3534126780.278278</v>
       </c>
       <c r="Q14" s="3">
-        <v>69025301774.41304</v>
+        <v>3599816869.131035</v>
       </c>
       <c r="R14" s="3">
-        <v>816521837367.4178</v>
+        <v>41581826243.79461</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -15406,46 +15406,46 @@
         <v>0</v>
       </c>
       <c r="E15" s="3">
-        <v>550882261.7792752</v>
+        <v>59013625754.90613</v>
       </c>
       <c r="F15" s="3">
-        <v>553255686.9078362</v>
+        <v>59282247583.08624</v>
       </c>
       <c r="G15" s="3">
-        <v>557912463.8037111</v>
+        <v>59576451253.34721</v>
       </c>
       <c r="H15" s="3">
-        <v>564198601.3069019</v>
+        <v>59936685214.44153</v>
       </c>
       <c r="I15" s="3">
-        <v>572082492.9499619</v>
+        <v>60446051663.67387</v>
       </c>
       <c r="J15" s="3">
-        <v>581373456.5547513</v>
+        <v>61120114973.8288</v>
       </c>
       <c r="K15" s="3">
-        <v>591244043.4304688</v>
+        <v>61957857334.14098</v>
       </c>
       <c r="L15" s="3">
-        <v>602138447.7234443</v>
+        <v>62924238436.85561</v>
       </c>
       <c r="M15" s="3">
-        <v>613840057.7498354</v>
+        <v>63990247910.89261</v>
       </c>
       <c r="N15" s="3">
-        <v>625887775.0801128</v>
+        <v>65158058912.48797</v>
       </c>
       <c r="O15" s="3">
-        <v>638159293.9903905</v>
+        <v>66400446693.45375</v>
       </c>
       <c r="P15" s="3">
-        <v>651030516.7296441</v>
+        <v>67690509861.89019</v>
       </c>
       <c r="Q15" s="3">
-        <v>664158708.5304384</v>
+        <v>69025301774.41304</v>
       </c>
       <c r="R15" s="3">
-        <v>7766163806.536771</v>
+        <v>816521837367.4178</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -15462,46 +15462,46 @@
         <v>0</v>
       </c>
       <c r="E16" s="3">
-        <v>385800749.0446984</v>
+        <v>550882261.7792752</v>
       </c>
       <c r="F16" s="3">
-        <v>392905649.0339075</v>
+        <v>553255686.9078362</v>
       </c>
       <c r="G16" s="3">
-        <v>400111761.5916485</v>
+        <v>557912463.8037111</v>
       </c>
       <c r="H16" s="3">
-        <v>407273108.8589906</v>
+        <v>564198601.3069019</v>
       </c>
       <c r="I16" s="3">
-        <v>416048682.5845155</v>
+        <v>572082492.9499619</v>
       </c>
       <c r="J16" s="3">
-        <v>424984718.3041024</v>
+        <v>581373456.5547513</v>
       </c>
       <c r="K16" s="3">
-        <v>432314328.6267064</v>
+        <v>591244043.4304688</v>
       </c>
       <c r="L16" s="3">
-        <v>442718491.4191913</v>
+        <v>602138447.7234443</v>
       </c>
       <c r="M16" s="3">
-        <v>451815960.7527988</v>
+        <v>613840057.7498354</v>
       </c>
       <c r="N16" s="3">
-        <v>460773702.2346267</v>
+        <v>625887775.0801128</v>
       </c>
       <c r="O16" s="3">
-        <v>469722021.7321313</v>
+        <v>638159293.9903905</v>
       </c>
       <c r="P16" s="3">
-        <v>480286949.4388104</v>
+        <v>651030516.7296441</v>
       </c>
       <c r="Q16" s="3">
-        <v>489395257.4447808</v>
+        <v>664158708.5304384</v>
       </c>
       <c r="R16" s="3">
-        <v>5654151381.066908</v>
+        <v>7766163806.536771</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -15518,46 +15518,46 @@
         <v>0</v>
       </c>
       <c r="E17" s="3">
-        <v>263348213.7307218</v>
+        <v>385800749.0446984</v>
       </c>
       <c r="F17" s="3">
-        <v>269472590.794227</v>
+        <v>392905649.0339075</v>
       </c>
       <c r="G17" s="3">
-        <v>274372092.445031</v>
+        <v>400111761.5916485</v>
       </c>
       <c r="H17" s="3">
-        <v>279271594.0958351</v>
+        <v>407273108.8589906</v>
       </c>
       <c r="I17" s="3">
-        <v>285395971.1593403</v>
+        <v>416048682.5845155</v>
       </c>
       <c r="J17" s="3">
-        <v>291520348.2228454</v>
+        <v>424984718.3041024</v>
       </c>
       <c r="K17" s="3">
-        <v>296419849.8736495</v>
+        <v>432314328.6267064</v>
       </c>
       <c r="L17" s="3">
-        <v>303769102.3498557</v>
+        <v>442718491.4191913</v>
       </c>
       <c r="M17" s="3">
-        <v>309893479.4133608</v>
+        <v>451815960.7527988</v>
       </c>
       <c r="N17" s="3">
-        <v>316017856.4768662</v>
+        <v>460773702.2346267</v>
       </c>
       <c r="O17" s="3">
-        <v>322142233.5403714</v>
+        <v>469722021.7321313</v>
       </c>
       <c r="P17" s="3">
-        <v>329491486.0165773</v>
+        <v>480286949.4388104</v>
       </c>
       <c r="Q17" s="3">
-        <v>335615863.0800826</v>
+        <v>489395257.4447808</v>
       </c>
       <c r="R17" s="3">
-        <v>3876730681.198764</v>
+        <v>5654151381.066908</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -15574,46 +15574,46 @@
         <v>0</v>
       </c>
       <c r="E18" s="3">
-        <v>517454059.0277524</v>
+        <v>263348213.7307218</v>
       </c>
       <c r="F18" s="3">
-        <v>527263614.6491316</v>
+        <v>269472590.794227</v>
       </c>
       <c r="G18" s="3">
-        <v>539525559.1758556</v>
+        <v>274372092.445031</v>
       </c>
       <c r="H18" s="3">
-        <v>549335114.7972348</v>
+        <v>279271594.0958351</v>
       </c>
       <c r="I18" s="3">
-        <v>559144670.4186139</v>
+        <v>285395971.1593403</v>
       </c>
       <c r="J18" s="3">
-        <v>571406614.945338</v>
+        <v>291520348.2228454</v>
       </c>
       <c r="K18" s="3">
-        <v>583668559.4720618</v>
+        <v>296419849.8736495</v>
       </c>
       <c r="L18" s="3">
-        <v>593478115.0934411</v>
+        <v>303769102.3498557</v>
       </c>
       <c r="M18" s="3">
-        <v>608192448.5255101</v>
+        <v>309893479.4133608</v>
       </c>
       <c r="N18" s="3">
-        <v>620454393.0522339</v>
+        <v>316017856.4768662</v>
       </c>
       <c r="O18" s="3">
-        <v>632716337.5789579</v>
+        <v>322142233.5403714</v>
       </c>
       <c r="P18" s="3">
-        <v>644978282.1056819</v>
+        <v>329491486.0165773</v>
       </c>
       <c r="Q18" s="3">
-        <v>659692615.5377506</v>
+        <v>335615863.0800826</v>
       </c>
       <c r="R18" s="3">
-        <v>7607310384.379562</v>
+        <v>3876730681.198764</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -15630,46 +15630,46 @@
         <v>0</v>
       </c>
       <c r="E19" s="3">
-        <v>85060.00982304836</v>
+        <v>517454059.0277524</v>
       </c>
       <c r="F19" s="3">
-        <v>87038.14958637506</v>
+        <v>527263614.6491316</v>
       </c>
       <c r="G19" s="3">
-        <v>88620.66139703641</v>
+        <v>539525559.1758556</v>
       </c>
       <c r="H19" s="3">
-        <v>90203.17320769779</v>
+        <v>549335114.7972348</v>
       </c>
       <c r="I19" s="3">
-        <v>92181.31297102448</v>
+        <v>559144670.4186139</v>
       </c>
       <c r="J19" s="3">
-        <v>94159.45273435117</v>
+        <v>571406614.945338</v>
       </c>
       <c r="K19" s="3">
-        <v>95741.96454501257</v>
+        <v>583668559.4720618</v>
       </c>
       <c r="L19" s="3">
-        <v>98115.73226100462</v>
+        <v>593478115.0934411</v>
       </c>
       <c r="M19" s="3">
-        <v>100093.8720243313</v>
+        <v>608192448.5255101</v>
       </c>
       <c r="N19" s="3">
-        <v>102072.011787658</v>
+        <v>620454393.0522339</v>
       </c>
       <c r="O19" s="3">
-        <v>104050.1515509847</v>
+        <v>632716337.5789579</v>
       </c>
       <c r="P19" s="3">
-        <v>106423.9192669768</v>
+        <v>644978282.1056819</v>
       </c>
       <c r="Q19" s="3">
-        <v>108402.0590303035</v>
+        <v>659692615.5377506</v>
       </c>
       <c r="R19" s="3">
-        <v>1252162.470185805</v>
+        <v>7607310384.379562</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -15686,46 +15686,46 @@
         <v>0</v>
       </c>
       <c r="E20" s="3">
-        <v>85541470193.56918</v>
+        <v>85060.00982304836</v>
       </c>
       <c r="F20" s="3">
-        <v>86172345139.93823</v>
+        <v>87038.14958637506</v>
       </c>
       <c r="G20" s="3">
-        <v>86868332756.94853</v>
+        <v>88620.66139703641</v>
       </c>
       <c r="H20" s="3">
-        <v>87652636166.57243</v>
+        <v>90203.17320769779</v>
       </c>
       <c r="I20" s="3">
-        <v>88679974460.84073</v>
+        <v>92181.31297102448</v>
       </c>
       <c r="J20" s="3">
-        <v>89907238638.81313</v>
+        <v>94159.45273435117</v>
       </c>
       <c r="K20" s="3">
-        <v>91241297145.71661</v>
+        <v>95741.96454501257</v>
       </c>
       <c r="L20" s="3">
-        <v>92845721003.81821</v>
+        <v>98115.73226100462</v>
       </c>
       <c r="M20" s="3">
-        <v>94518551013.49059</v>
+        <v>100093.8720243313</v>
       </c>
       <c r="N20" s="3">
-        <v>96288904304.10214</v>
+        <v>102072.011787658</v>
       </c>
       <c r="O20" s="3">
-        <v>98137617621.09976</v>
+        <v>104050.1515509847</v>
       </c>
       <c r="P20" s="3">
-        <v>100112040705.0183</v>
+        <v>106423.9192669768</v>
       </c>
       <c r="Q20" s="3">
-        <v>102079463535.09</v>
+        <v>108402.0590303035</v>
       </c>
       <c r="R20" s="3">
-        <v>1200045592685.018</v>
+        <v>1252162.470185805</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -15758,46 +15758,46 @@
         <v>0</v>
       </c>
       <c r="E22" s="3">
-        <v>22757201772.49164</v>
+        <v>85541470193.56918</v>
       </c>
       <c r="F22" s="3">
-        <v>23042560365.86388</v>
+        <v>86172345139.93823</v>
       </c>
       <c r="G22" s="3">
-        <v>23377178548.50349</v>
+        <v>86868332756.94853</v>
       </c>
       <c r="H22" s="3">
-        <v>23734860495.93104</v>
+        <v>87652636166.57243</v>
       </c>
       <c r="I22" s="3">
-        <v>24172098023.37206</v>
+        <v>88679974460.84073</v>
       </c>
       <c r="J22" s="3">
-        <v>24640865574.72158</v>
+        <v>89907238638.81313</v>
       </c>
       <c r="K22" s="3">
-        <v>25064925644.98824</v>
+        <v>91241297145.71661</v>
       </c>
       <c r="L22" s="3">
-        <v>25606488870.38609</v>
+        <v>92845721003.81821</v>
       </c>
       <c r="M22" s="3">
-        <v>26124174487.84058</v>
+        <v>94518551013.49059</v>
       </c>
       <c r="N22" s="3">
-        <v>26639548412.42558</v>
+        <v>96288904304.10214</v>
       </c>
       <c r="O22" s="3">
-        <v>27158472360.46189</v>
+        <v>98137617621.09976</v>
       </c>
       <c r="P22" s="3">
-        <v>27742084303.51749</v>
+        <v>100112040705.0183</v>
       </c>
       <c r="Q22" s="3">
-        <v>28284164559.78339</v>
+        <v>102079463535.09</v>
       </c>
       <c r="R22" s="3">
-        <v>328344623420.2869</v>
+        <v>1200045592685.018</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -15814,46 +15814,46 @@
         <v>0</v>
       </c>
       <c r="E23" s="3">
-        <v>2824673820.668513</v>
+        <v>22757201772.49164</v>
       </c>
       <c r="F23" s="3">
-        <v>2890363909.521269</v>
+        <v>23042560365.86388</v>
       </c>
       <c r="G23" s="3">
-        <v>2942915980.603474</v>
+        <v>23377178548.50349</v>
       </c>
       <c r="H23" s="3">
-        <v>2995468051.685678</v>
+        <v>23734860495.93104</v>
       </c>
       <c r="I23" s="3">
-        <v>3061158140.538435</v>
+        <v>24172098023.37206</v>
       </c>
       <c r="J23" s="3">
-        <v>3126848229.391191</v>
+        <v>24640865574.72158</v>
       </c>
       <c r="K23" s="3">
-        <v>3179400300.473396</v>
+        <v>25064925644.98824</v>
       </c>
       <c r="L23" s="3">
-        <v>3258228407.096702</v>
+        <v>25606488870.38609</v>
       </c>
       <c r="M23" s="3">
-        <v>3323918495.949458</v>
+        <v>26124174487.84058</v>
       </c>
       <c r="N23" s="3">
-        <v>3389608584.802216</v>
+        <v>26639548412.42558</v>
       </c>
       <c r="O23" s="3">
-        <v>3455298673.654972</v>
+        <v>27158472360.46189</v>
       </c>
       <c r="P23" s="3">
-        <v>3534126780.278278</v>
+        <v>27742084303.51749</v>
       </c>
       <c r="Q23" s="3">
-        <v>3599816869.131035</v>
+        <v>28284164559.78339</v>
       </c>
       <c r="R23" s="3">
-        <v>41581826243.79461</v>
+        <v>328344623420.2869</v>
       </c>
     </row>
     <row r="24" spans="1:18">
@@ -15870,46 +15870,46 @@
         <v>0</v>
       </c>
       <c r="E24" s="3">
-        <v>59013625754.90613</v>
+        <v>2824673820.668513</v>
       </c>
       <c r="F24" s="3">
-        <v>59282247583.08624</v>
+        <v>2890363909.521269</v>
       </c>
       <c r="G24" s="3">
-        <v>59576451253.34721</v>
+        <v>2942915980.603474</v>
       </c>
       <c r="H24" s="3">
-        <v>59936685214.44153</v>
+        <v>2995468051.685678</v>
       </c>
       <c r="I24" s="3">
-        <v>60446051663.67387</v>
+        <v>3061158140.538435</v>
       </c>
       <c r="J24" s="3">
-        <v>61120114973.8288</v>
+        <v>3126848229.391191</v>
       </c>
       <c r="K24" s="3">
-        <v>61957857334.14098</v>
+        <v>3179400300.473396</v>
       </c>
       <c r="L24" s="3">
-        <v>62924238436.85561</v>
+        <v>3258228407.096702</v>
       </c>
       <c r="M24" s="3">
-        <v>63990247910.89261</v>
+        <v>3323918495.949458</v>
       </c>
       <c r="N24" s="3">
-        <v>65158058912.48797</v>
+        <v>3389608584.802216</v>
       </c>
       <c r="O24" s="3">
-        <v>66400446693.45375</v>
+        <v>3455298673.654972</v>
       </c>
       <c r="P24" s="3">
-        <v>67690509861.89019</v>
+        <v>3534126780.278278</v>
       </c>
       <c r="Q24" s="3">
-        <v>69025301774.41304</v>
+        <v>3599816869.131035</v>
       </c>
       <c r="R24" s="3">
-        <v>816521837367.4178</v>
+        <v>41581826243.79461</v>
       </c>
     </row>
     <row r="25" spans="1:18">
@@ -15926,46 +15926,46 @@
         <v>0</v>
       </c>
       <c r="E25" s="3">
-        <v>550882261.7792752</v>
+        <v>59013625754.90613</v>
       </c>
       <c r="F25" s="3">
-        <v>553255686.9078362</v>
+        <v>59282247583.08624</v>
       </c>
       <c r="G25" s="3">
-        <v>557912463.8037111</v>
+        <v>59576451253.34721</v>
       </c>
       <c r="H25" s="3">
-        <v>564198601.3069019</v>
+        <v>59936685214.44153</v>
       </c>
       <c r="I25" s="3">
-        <v>572082492.9499619</v>
+        <v>60446051663.67387</v>
       </c>
       <c r="J25" s="3">
-        <v>581373456.5547513</v>
+        <v>61120114973.8288</v>
       </c>
       <c r="K25" s="3">
-        <v>591244043.4304688</v>
+        <v>61957857334.14098</v>
       </c>
       <c r="L25" s="3">
-        <v>602138447.7234443</v>
+        <v>62924238436.85561</v>
       </c>
       <c r="M25" s="3">
-        <v>613840057.7498354</v>
+        <v>63990247910.89261</v>
       </c>
       <c r="N25" s="3">
-        <v>625887775.0801128</v>
+        <v>65158058912.48797</v>
       </c>
       <c r="O25" s="3">
-        <v>638159293.9903905</v>
+        <v>66400446693.45375</v>
       </c>
       <c r="P25" s="3">
-        <v>651030516.7296441</v>
+        <v>67690509861.89019</v>
       </c>
       <c r="Q25" s="3">
-        <v>664158708.5304384</v>
+        <v>69025301774.41304</v>
       </c>
       <c r="R25" s="3">
-        <v>7766163806.536771</v>
+        <v>816521837367.4178</v>
       </c>
     </row>
     <row r="26" spans="1:18">
@@ -15982,46 +15982,46 @@
         <v>0</v>
       </c>
       <c r="E26" s="3">
-        <v>385800749.0446984</v>
+        <v>550882261.7792752</v>
       </c>
       <c r="F26" s="3">
-        <v>392905649.0339075</v>
+        <v>553255686.9078362</v>
       </c>
       <c r="G26" s="3">
-        <v>400111761.5916485</v>
+        <v>557912463.8037111</v>
       </c>
       <c r="H26" s="3">
-        <v>407273108.8589906</v>
+        <v>564198601.3069019</v>
       </c>
       <c r="I26" s="3">
-        <v>416048682.5845155</v>
+        <v>572082492.9499619</v>
       </c>
       <c r="J26" s="3">
-        <v>424984718.3041024</v>
+        <v>581373456.5547513</v>
       </c>
       <c r="K26" s="3">
-        <v>432314328.6267064</v>
+        <v>591244043.4304688</v>
       </c>
       <c r="L26" s="3">
-        <v>442718491.4191913</v>
+        <v>602138447.7234443</v>
       </c>
       <c r="M26" s="3">
-        <v>451815960.7527988</v>
+        <v>613840057.7498354</v>
       </c>
       <c r="N26" s="3">
-        <v>460773702.2346267</v>
+        <v>625887775.0801128</v>
       </c>
       <c r="O26" s="3">
-        <v>469722021.7321313</v>
+        <v>638159293.9903905</v>
       </c>
       <c r="P26" s="3">
-        <v>480286949.4388104</v>
+        <v>651030516.7296441</v>
       </c>
       <c r="Q26" s="3">
-        <v>489395257.4447808</v>
+        <v>664158708.5304384</v>
       </c>
       <c r="R26" s="3">
-        <v>5654151381.066908</v>
+        <v>7766163806.536771</v>
       </c>
     </row>
     <row r="27" spans="1:18">
@@ -16038,46 +16038,46 @@
         <v>0</v>
       </c>
       <c r="E27" s="3">
-        <v>263348213.7307218</v>
+        <v>385800749.0446984</v>
       </c>
       <c r="F27" s="3">
-        <v>269472590.794227</v>
+        <v>392905649.0339075</v>
       </c>
       <c r="G27" s="3">
-        <v>274372092.445031</v>
+        <v>400111761.5916485</v>
       </c>
       <c r="H27" s="3">
-        <v>279271594.0958351</v>
+        <v>407273108.8589906</v>
       </c>
       <c r="I27" s="3">
-        <v>285395971.1593403</v>
+        <v>416048682.5845155</v>
       </c>
       <c r="J27" s="3">
-        <v>291520348.2228454</v>
+        <v>424984718.3041024</v>
       </c>
       <c r="K27" s="3">
-        <v>296419849.8736495</v>
+        <v>432314328.6267064</v>
       </c>
       <c r="L27" s="3">
-        <v>303769102.3498557</v>
+        <v>442718491.4191913</v>
       </c>
       <c r="M27" s="3">
-        <v>309893479.4133608</v>
+        <v>451815960.7527988</v>
       </c>
       <c r="N27" s="3">
-        <v>316017856.4768662</v>
+        <v>460773702.2346267</v>
       </c>
       <c r="O27" s="3">
-        <v>322142233.5403714</v>
+        <v>469722021.7321313</v>
       </c>
       <c r="P27" s="3">
-        <v>329491486.0165773</v>
+        <v>480286949.4388104</v>
       </c>
       <c r="Q27" s="3">
-        <v>335615863.0800826</v>
+        <v>489395257.4447808</v>
       </c>
       <c r="R27" s="3">
-        <v>3876730681.198764</v>
+        <v>5654151381.066908</v>
       </c>
     </row>
     <row r="28" spans="1:18">
@@ -16094,46 +16094,46 @@
         <v>0</v>
       </c>
       <c r="E28" s="3">
-        <v>517454059.0277524</v>
+        <v>263348213.7307218</v>
       </c>
       <c r="F28" s="3">
-        <v>527263614.6491316</v>
+        <v>269472590.794227</v>
       </c>
       <c r="G28" s="3">
-        <v>539525559.1758556</v>
+        <v>274372092.445031</v>
       </c>
       <c r="H28" s="3">
-        <v>549335114.7972348</v>
+        <v>279271594.0958351</v>
       </c>
       <c r="I28" s="3">
-        <v>559144670.4186139</v>
+        <v>285395971.1593403</v>
       </c>
       <c r="J28" s="3">
-        <v>571406614.945338</v>
+        <v>291520348.2228454</v>
       </c>
       <c r="K28" s="3">
-        <v>583668559.4720618</v>
+        <v>296419849.8736495</v>
       </c>
       <c r="L28" s="3">
-        <v>593478115.0934411</v>
+        <v>303769102.3498557</v>
       </c>
       <c r="M28" s="3">
-        <v>608192448.5255101</v>
+        <v>309893479.4133608</v>
       </c>
       <c r="N28" s="3">
-        <v>620454393.0522339</v>
+        <v>316017856.4768662</v>
       </c>
       <c r="O28" s="3">
-        <v>632716337.5789579</v>
+        <v>322142233.5403714</v>
       </c>
       <c r="P28" s="3">
-        <v>644978282.1056819</v>
+        <v>329491486.0165773</v>
       </c>
       <c r="Q28" s="3">
-        <v>659692615.5377506</v>
+        <v>335615863.0800826</v>
       </c>
       <c r="R28" s="3">
-        <v>7607310384.379562</v>
+        <v>3876730681.198764</v>
       </c>
     </row>
     <row r="29" spans="1:18">
@@ -16150,46 +16150,46 @@
         <v>0</v>
       </c>
       <c r="E29" s="3">
-        <v>85060.00982304836</v>
+        <v>517454059.0277524</v>
       </c>
       <c r="F29" s="3">
-        <v>87038.14958637506</v>
+        <v>527263614.6491316</v>
       </c>
       <c r="G29" s="3">
-        <v>88620.66139703641</v>
+        <v>539525559.1758556</v>
       </c>
       <c r="H29" s="3">
-        <v>90203.17320769779</v>
+        <v>549335114.7972348</v>
       </c>
       <c r="I29" s="3">
-        <v>92181.31297102448</v>
+        <v>559144670.4186139</v>
       </c>
       <c r="J29" s="3">
-        <v>94159.45273435117</v>
+        <v>571406614.945338</v>
       </c>
       <c r="K29" s="3">
-        <v>95741.96454501257</v>
+        <v>583668559.4720618</v>
       </c>
       <c r="L29" s="3">
-        <v>98115.73226100462</v>
+        <v>593478115.0934411</v>
       </c>
       <c r="M29" s="3">
-        <v>100093.8720243313</v>
+        <v>608192448.5255101</v>
       </c>
       <c r="N29" s="3">
-        <v>102072.011787658</v>
+        <v>620454393.0522339</v>
       </c>
       <c r="O29" s="3">
-        <v>104050.1515509847</v>
+        <v>632716337.5789579</v>
       </c>
       <c r="P29" s="3">
-        <v>106423.9192669768</v>
+        <v>644978282.1056819</v>
       </c>
       <c r="Q29" s="3">
-        <v>108402.0590303035</v>
+        <v>659692615.5377506</v>
       </c>
       <c r="R29" s="3">
-        <v>1252162.470185805</v>
+        <v>7607310384.379562</v>
       </c>
     </row>
     <row r="30" spans="1:18">
@@ -16206,46 +16206,46 @@
         <v>0</v>
       </c>
       <c r="E30" s="3">
-        <v>85541470193.56918</v>
+        <v>85060.00982304836</v>
       </c>
       <c r="F30" s="3">
-        <v>86172345139.93823</v>
+        <v>87038.14958637506</v>
       </c>
       <c r="G30" s="3">
-        <v>86868332756.94853</v>
+        <v>88620.66139703641</v>
       </c>
       <c r="H30" s="3">
-        <v>87652636166.57243</v>
+        <v>90203.17320769779</v>
       </c>
       <c r="I30" s="3">
-        <v>88679974460.84073</v>
+        <v>92181.31297102448</v>
       </c>
       <c r="J30" s="3">
-        <v>89907238638.81313</v>
+        <v>94159.45273435117</v>
       </c>
       <c r="K30" s="3">
-        <v>91241297145.71661</v>
+        <v>95741.96454501257</v>
       </c>
       <c r="L30" s="3">
-        <v>92845721003.81821</v>
+        <v>98115.73226100462</v>
       </c>
       <c r="M30" s="3">
-        <v>94518551013.49059</v>
+        <v>100093.8720243313</v>
       </c>
       <c r="N30" s="3">
-        <v>96288904304.10214</v>
+        <v>102072.011787658</v>
       </c>
       <c r="O30" s="3">
-        <v>98137617621.09976</v>
+        <v>104050.1515509847</v>
       </c>
       <c r="P30" s="3">
-        <v>100112040705.0183</v>
+        <v>106423.9192669768</v>
       </c>
       <c r="Q30" s="3">
-        <v>102079463535.09</v>
+        <v>108402.0590303035</v>
       </c>
       <c r="R30" s="3">
-        <v>1200045592685.018</v>
+        <v>1252162.470185805</v>
       </c>
     </row>
     <row r="31" spans="1:18">
@@ -16278,46 +16278,46 @@
         <v>0</v>
       </c>
       <c r="E32" s="3">
-        <v>22748381805.20618</v>
+        <v>85451123743.9299</v>
       </c>
       <c r="F32" s="3">
-        <v>22520353600.47911</v>
+        <v>85510250031.38475</v>
       </c>
       <c r="G32" s="3">
-        <v>22473745657.09102</v>
+        <v>85575258223.2906</v>
       </c>
       <c r="H32" s="3">
-        <v>22788709163.15194</v>
+        <v>86111231123.35857</v>
       </c>
       <c r="I32" s="3">
-        <v>23195438106.64322</v>
+        <v>86830555476.49335</v>
       </c>
       <c r="J32" s="3">
-        <v>23637539550.00182</v>
+        <v>87760907916.89471</v>
       </c>
       <c r="K32" s="3">
-        <v>24040291257.60387</v>
+        <v>88846868984.6971</v>
       </c>
       <c r="L32" s="3">
-        <v>24554869924.81215</v>
+        <v>90241702534.94495</v>
       </c>
       <c r="M32" s="3">
-        <v>25048997352.36107</v>
+        <v>91747292494.02652</v>
       </c>
       <c r="N32" s="3">
-        <v>25541714967.60299</v>
+        <v>93379782887.38736</v>
       </c>
       <c r="O32" s="3">
-        <v>26038353838.91957</v>
+        <v>95111730313.55669</v>
       </c>
       <c r="P32" s="3">
-        <v>26596315378.36823</v>
+        <v>96980136118.90689</v>
       </c>
       <c r="Q32" s="3">
-        <v>27116045769.73991</v>
+        <v>98856090473.16951</v>
       </c>
       <c r="R32" s="3">
-        <v>316300756371.9811</v>
+        <v>1172402930322.041</v>
       </c>
     </row>
     <row r="33" spans="1:18">
@@ -16334,46 +16334,46 @@
         <v>0</v>
       </c>
       <c r="E33" s="3">
-        <v>2786284365.504835</v>
+        <v>22748381805.20618</v>
       </c>
       <c r="F33" s="3">
-        <v>2863124877.913214</v>
+        <v>22520353600.47911</v>
       </c>
       <c r="G33" s="3">
-        <v>2858921549.867434</v>
+        <v>22473745657.09102</v>
       </c>
       <c r="H33" s="3">
-        <v>2909973720.400781</v>
+        <v>22788709163.15194</v>
       </c>
       <c r="I33" s="3">
-        <v>2973788933.567464</v>
+        <v>23195438106.64322</v>
       </c>
       <c r="J33" s="3">
-        <v>3037604146.73415</v>
+        <v>23637539550.00182</v>
       </c>
       <c r="K33" s="3">
-        <v>3088656317.267495</v>
+        <v>24040291257.60387</v>
       </c>
       <c r="L33" s="3">
-        <v>3165234573.067517</v>
+        <v>24554869924.81215</v>
       </c>
       <c r="M33" s="3">
-        <v>3229049786.2342</v>
+        <v>25048997352.36107</v>
       </c>
       <c r="N33" s="3">
-        <v>3292864999.400885</v>
+        <v>25541714967.60299</v>
       </c>
       <c r="O33" s="3">
-        <v>3356680212.567567</v>
+        <v>26038353838.91957</v>
       </c>
       <c r="P33" s="3">
-        <v>3433258468.367589</v>
+        <v>26596315378.36823</v>
       </c>
       <c r="Q33" s="3">
-        <v>3497073681.534271</v>
+        <v>27116045769.73991</v>
       </c>
       <c r="R33" s="3">
-        <v>40492515632.4274</v>
+        <v>316300756371.9811</v>
       </c>
     </row>
     <row r="34" spans="1:18">
@@ -16390,46 +16390,46 @@
         <v>0</v>
       </c>
       <c r="E34" s="3">
-        <v>59010443727.66352</v>
+        <v>2786284365.504835</v>
       </c>
       <c r="F34" s="3">
-        <v>59238382616.6305</v>
+        <v>2863124877.913214</v>
       </c>
       <c r="G34" s="3">
-        <v>59426353759.1616</v>
+        <v>2858921549.867434</v>
       </c>
       <c r="H34" s="3">
-        <v>59584899351.43102</v>
+        <v>2909973720.400781</v>
       </c>
       <c r="I34" s="3">
-        <v>59821673615.33611</v>
+        <v>2973788933.567464</v>
       </c>
       <c r="J34" s="3">
-        <v>60230612433.13</v>
+        <v>3037604146.73415</v>
       </c>
       <c r="K34" s="3">
-        <v>60845803965.30045</v>
+        <v>3088656317.267495</v>
       </c>
       <c r="L34" s="3">
-        <v>61635607559.62009</v>
+        <v>3165234573.067517</v>
       </c>
       <c r="M34" s="3">
-        <v>62563317470.77316</v>
+        <v>3229049786.2342</v>
       </c>
       <c r="N34" s="3">
-        <v>63621192211.56274</v>
+        <v>3292864999.400885</v>
       </c>
       <c r="O34" s="3">
-        <v>64774384990.14632</v>
+        <v>3356680212.567567</v>
       </c>
       <c r="P34" s="3">
-        <v>65990318228.44353</v>
+        <v>3433258468.367589</v>
       </c>
       <c r="Q34" s="3">
-        <v>67261427826.00018</v>
+        <v>3497073681.534271</v>
       </c>
       <c r="R34" s="3">
-        <v>804004417755.1992</v>
+        <v>40492515632.4274</v>
       </c>
     </row>
     <row r="35" spans="1:18">
@@ -16446,46 +16446,46 @@
         <v>0</v>
       </c>
       <c r="E35" s="3">
-        <v>550886798.978663</v>
+        <v>59010443727.66352</v>
       </c>
       <c r="F35" s="3">
-        <v>553493130.8700848</v>
+        <v>59238382616.6305</v>
       </c>
       <c r="G35" s="3">
-        <v>558594778.3392249</v>
+        <v>59426353759.1616</v>
       </c>
       <c r="H35" s="3">
-        <v>565309893.0017341</v>
+        <v>59584899351.43102</v>
       </c>
       <c r="I35" s="3">
-        <v>573526506.703522</v>
+        <v>59821673615.33611</v>
       </c>
       <c r="J35" s="3">
-        <v>583071987.7818178</v>
+        <v>60230612433.13</v>
       </c>
       <c r="K35" s="3">
-        <v>593138214.4618096</v>
+        <v>60845803965.30045</v>
       </c>
       <c r="L35" s="3">
-        <v>604187791.6373742</v>
+        <v>61635607559.62009</v>
       </c>
       <c r="M35" s="3">
-        <v>616015959.5233783</v>
+        <v>62563317470.77316</v>
       </c>
       <c r="N35" s="3">
-        <v>628168784.0985376</v>
+        <v>63621192211.56274</v>
       </c>
       <c r="O35" s="3">
-        <v>640529887.858981</v>
+        <v>64774384990.14632</v>
       </c>
       <c r="P35" s="3">
-        <v>653481084.7038864</v>
+        <v>65990318228.44353</v>
       </c>
       <c r="Q35" s="3">
-        <v>666681880.1555153</v>
+        <v>67261427826.00018</v>
       </c>
       <c r="R35" s="3">
-        <v>7787086698.114529</v>
+        <v>804004417755.1992</v>
       </c>
     </row>
     <row r="36" spans="1:18">
@@ -16502,46 +16502,46 @@
         <v>0</v>
       </c>
       <c r="E36" s="3">
-        <v>385811020.4889482</v>
+        <v>550886798.978663</v>
       </c>
       <c r="F36" s="3">
-        <v>393577984.022957</v>
+        <v>553493130.8700848</v>
       </c>
       <c r="G36" s="3">
-        <v>401332410.1549103</v>
+        <v>558594778.3392249</v>
       </c>
       <c r="H36" s="3">
-        <v>408568979.0064408</v>
+        <v>565309893.0017341</v>
       </c>
       <c r="I36" s="3">
-        <v>417376543.61866</v>
+        <v>573526506.703522</v>
       </c>
       <c r="J36" s="3">
-        <v>426341415.3563595</v>
+        <v>583071987.7818178</v>
       </c>
       <c r="K36" s="3">
-        <v>433694543.1925827</v>
+        <v>593138214.4618096</v>
       </c>
       <c r="L36" s="3">
-        <v>444131769.0192203</v>
+        <v>604187791.6373742</v>
       </c>
       <c r="M36" s="3">
-        <v>453258359.6934142</v>
+        <v>616015959.5233783</v>
       </c>
       <c r="N36" s="3">
-        <v>462244716.8475319</v>
+        <v>628168784.0985376</v>
       </c>
       <c r="O36" s="3">
-        <v>471221614.2471001</v>
+        <v>640529887.858981</v>
       </c>
       <c r="P36" s="3">
-        <v>481820194.118144</v>
+        <v>653481084.7038864</v>
       </c>
       <c r="Q36" s="3">
-        <v>490957667.4032573</v>
+        <v>666681880.1555153</v>
       </c>
       <c r="R36" s="3">
-        <v>5670337217.169526</v>
+        <v>7787086698.114529</v>
       </c>
     </row>
     <row r="37" spans="1:18">
@@ -16558,46 +16558,46 @@
         <v>0</v>
       </c>
       <c r="E37" s="3">
-        <v>230913108.9920408</v>
+        <v>385811020.4889482</v>
       </c>
       <c r="F37" s="3">
-        <v>214016878.5984456</v>
+        <v>393577984.022957</v>
       </c>
       <c r="G37" s="3">
-        <v>148630843.675634</v>
+        <v>401332410.1549103</v>
       </c>
       <c r="H37" s="3">
-        <v>151284965.8841275</v>
+        <v>408568979.0064408</v>
       </c>
       <c r="I37" s="3">
-        <v>154602618.6447443</v>
+        <v>417376543.61866</v>
       </c>
       <c r="J37" s="3">
-        <v>157920271.4053611</v>
+        <v>426341415.3563595</v>
       </c>
       <c r="K37" s="3">
-        <v>160574393.6138546</v>
+        <v>433694543.1925827</v>
       </c>
       <c r="L37" s="3">
-        <v>164555576.9265949</v>
+        <v>444131769.0192203</v>
       </c>
       <c r="M37" s="3">
-        <v>167873229.6872117</v>
+        <v>453258359.6934142</v>
       </c>
       <c r="N37" s="3">
-        <v>171190882.4478285</v>
+        <v>462244716.8475319</v>
       </c>
       <c r="O37" s="3">
-        <v>174508535.2084453</v>
+        <v>471221614.2471001</v>
       </c>
       <c r="P37" s="3">
-        <v>178489718.5211855</v>
+        <v>481820194.118144</v>
       </c>
       <c r="Q37" s="3">
-        <v>181807371.2818024</v>
+        <v>490957667.4032573</v>
       </c>
       <c r="R37" s="3">
-        <v>2256368394.887276</v>
+        <v>5670337217.169526</v>
       </c>
     </row>
     <row r="38" spans="1:18">
@@ -16614,46 +16614,46 @@
         <v>0</v>
       </c>
       <c r="E38" s="3">
-        <v>509947269.5238243</v>
+        <v>230913108.9920408</v>
       </c>
       <c r="F38" s="3">
-        <v>514382574.9511451</v>
+        <v>214016878.5984456</v>
       </c>
       <c r="G38" s="3">
-        <v>510284117.0836095</v>
+        <v>148630843.675634</v>
       </c>
       <c r="H38" s="3">
-        <v>519562010.1214934</v>
+        <v>151284965.8841275</v>
       </c>
       <c r="I38" s="3">
-        <v>528839903.1593772</v>
+        <v>154602618.6447443</v>
       </c>
       <c r="J38" s="3">
-        <v>540437269.456732</v>
+        <v>157920271.4053611</v>
       </c>
       <c r="K38" s="3">
-        <v>552034635.7540869</v>
+        <v>160574393.6138546</v>
       </c>
       <c r="L38" s="3">
-        <v>561312528.7919705</v>
+        <v>164555576.9265949</v>
       </c>
       <c r="M38" s="3">
-        <v>575229368.3487964</v>
+        <v>167873229.6872117</v>
       </c>
       <c r="N38" s="3">
-        <v>586826734.6461511</v>
+        <v>171190882.4478285</v>
       </c>
       <c r="O38" s="3">
-        <v>598424100.9435059</v>
+        <v>174508535.2084453</v>
       </c>
       <c r="P38" s="3">
-        <v>610021467.2408607</v>
+        <v>178489718.5211855</v>
       </c>
       <c r="Q38" s="3">
-        <v>623938306.7976865</v>
+        <v>181807371.2818024</v>
       </c>
       <c r="R38" s="3">
-        <v>7231240286.819241</v>
+        <v>2256368394.887276</v>
       </c>
     </row>
     <row r="39" spans="1:18">
@@ -16670,46 +16670,46 @@
         <v>0</v>
       </c>
       <c r="E39" s="3">
-        <v>77688.54978406691</v>
+        <v>509947269.5238243</v>
       </c>
       <c r="F39" s="3">
-        <v>74335.96520844771</v>
+        <v>514382574.9511451</v>
       </c>
       <c r="G39" s="3">
-        <v>59928.22701223918</v>
+        <v>510284117.0836095</v>
       </c>
       <c r="H39" s="3">
-        <v>60998.37392317203</v>
+        <v>519562010.1214934</v>
       </c>
       <c r="I39" s="3">
-        <v>62336.05756183807</v>
+        <v>528839903.1593772</v>
       </c>
       <c r="J39" s="3">
-        <v>63673.74120050411</v>
+        <v>540437269.456732</v>
       </c>
       <c r="K39" s="3">
-        <v>64743.88811143697</v>
+        <v>552034635.7540869</v>
       </c>
       <c r="L39" s="3">
-        <v>66349.10847783624</v>
+        <v>561312528.7919705</v>
       </c>
       <c r="M39" s="3">
-        <v>67686.79211650229</v>
+        <v>575229368.3487964</v>
       </c>
       <c r="N39" s="3">
-        <v>69024.47575516834</v>
+        <v>586826734.6461511</v>
       </c>
       <c r="O39" s="3">
-        <v>70362.15939383442</v>
+        <v>598424100.9435059</v>
       </c>
       <c r="P39" s="3">
-        <v>71967.37976023366</v>
+        <v>610021467.2408607</v>
       </c>
       <c r="Q39" s="3">
-        <v>73305.0633988997</v>
+        <v>623938306.7976865</v>
       </c>
       <c r="R39" s="3">
-        <v>882399.7817041797</v>
+        <v>7231240286.819241</v>
       </c>
     </row>
     <row r="40" spans="1:18">
@@ -16726,46 +16726,46 @@
         <v>0</v>
       </c>
       <c r="E40" s="3">
-        <v>85451123743.9299</v>
+        <v>77688.54978406691</v>
       </c>
       <c r="F40" s="3">
-        <v>85510250031.38475</v>
+        <v>74335.96520844771</v>
       </c>
       <c r="G40" s="3">
-        <v>85575258223.2906</v>
+        <v>59928.22701223918</v>
       </c>
       <c r="H40" s="3">
-        <v>86111231123.35857</v>
+        <v>60998.37392317203</v>
       </c>
       <c r="I40" s="3">
-        <v>86830555476.49335</v>
+        <v>62336.05756183807</v>
       </c>
       <c r="J40" s="3">
-        <v>87760907916.89471</v>
+        <v>63673.74120050411</v>
       </c>
       <c r="K40" s="3">
-        <v>88846868984.6971</v>
+        <v>64743.88811143697</v>
       </c>
       <c r="L40" s="3">
-        <v>90241702534.94495</v>
+        <v>66349.10847783624</v>
       </c>
       <c r="M40" s="3">
-        <v>91747292494.02652</v>
+        <v>67686.79211650229</v>
       </c>
       <c r="N40" s="3">
-        <v>93379782887.38736</v>
+        <v>69024.47575516834</v>
       </c>
       <c r="O40" s="3">
-        <v>95111730313.55669</v>
+        <v>70362.15939383442</v>
       </c>
       <c r="P40" s="3">
-        <v>96980136118.90689</v>
+        <v>71967.37976023366</v>
       </c>
       <c r="Q40" s="3">
-        <v>98856090473.16951</v>
+        <v>73305.0633988997</v>
       </c>
       <c r="R40" s="3">
-        <v>1172402930322.041</v>
+        <v>882399.7817041797</v>
       </c>
     </row>
     <row r="41" spans="1:18">
@@ -16798,46 +16798,46 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>22748381805.20618</v>
+        <v>85451123743.9299</v>
       </c>
       <c r="F42" s="3">
-        <v>22520353600.47911</v>
+        <v>85510250031.38475</v>
       </c>
       <c r="G42" s="3">
-        <v>22473745657.09102</v>
+        <v>85575258223.2906</v>
       </c>
       <c r="H42" s="3">
-        <v>22788709163.15194</v>
+        <v>86111231123.35857</v>
       </c>
       <c r="I42" s="3">
-        <v>23195438106.64322</v>
+        <v>86830555476.49335</v>
       </c>
       <c r="J42" s="3">
-        <v>23637539550.00182</v>
+        <v>87760907916.89471</v>
       </c>
       <c r="K42" s="3">
-        <v>24040291257.60387</v>
+        <v>88846868984.6971</v>
       </c>
       <c r="L42" s="3">
-        <v>24554869924.81215</v>
+        <v>90241702534.94495</v>
       </c>
       <c r="M42" s="3">
-        <v>25048997352.36107</v>
+        <v>91747292494.02652</v>
       </c>
       <c r="N42" s="3">
-        <v>25541714967.60299</v>
+        <v>93379782887.38736</v>
       </c>
       <c r="O42" s="3">
-        <v>26038353838.91957</v>
+        <v>95111730313.55669</v>
       </c>
       <c r="P42" s="3">
-        <v>26596315378.36823</v>
+        <v>96980136118.90689</v>
       </c>
       <c r="Q42" s="3">
-        <v>27116045769.73991</v>
+        <v>98856090473.16951</v>
       </c>
       <c r="R42" s="3">
-        <v>316300756371.9811</v>
+        <v>1172402930322.041</v>
       </c>
     </row>
     <row r="43" spans="1:18">
@@ -16854,46 +16854,46 @@
         <v>0</v>
       </c>
       <c r="E43" s="3">
-        <v>2786284365.504835</v>
+        <v>22748381805.20618</v>
       </c>
       <c r="F43" s="3">
-        <v>2863124877.913214</v>
+        <v>22520353600.47911</v>
       </c>
       <c r="G43" s="3">
-        <v>2858921549.867434</v>
+        <v>22473745657.09102</v>
       </c>
       <c r="H43" s="3">
-        <v>2909973720.400781</v>
+        <v>22788709163.15194</v>
       </c>
       <c r="I43" s="3">
-        <v>2973788933.567464</v>
+        <v>23195438106.64322</v>
       </c>
       <c r="J43" s="3">
-        <v>3037604146.73415</v>
+        <v>23637539550.00182</v>
       </c>
       <c r="K43" s="3">
-        <v>3088656317.267495</v>
+        <v>24040291257.60387</v>
       </c>
       <c r="L43" s="3">
-        <v>3165234573.067517</v>
+        <v>24554869924.81215</v>
       </c>
       <c r="M43" s="3">
-        <v>3229049786.2342</v>
+        <v>25048997352.36107</v>
       </c>
       <c r="N43" s="3">
-        <v>3292864999.400885</v>
+        <v>25541714967.60299</v>
       </c>
       <c r="O43" s="3">
-        <v>3356680212.567567</v>
+        <v>26038353838.91957</v>
       </c>
       <c r="P43" s="3">
-        <v>3433258468.367589</v>
+        <v>26596315378.36823</v>
       </c>
       <c r="Q43" s="3">
-        <v>3497073681.534271</v>
+        <v>27116045769.73991</v>
       </c>
       <c r="R43" s="3">
-        <v>40492515632.4274</v>
+        <v>316300756371.9811</v>
       </c>
     </row>
     <row r="44" spans="1:18">
@@ -16910,46 +16910,46 @@
         <v>0</v>
       </c>
       <c r="E44" s="3">
-        <v>59010443727.66352</v>
+        <v>2786284365.504835</v>
       </c>
       <c r="F44" s="3">
-        <v>59238382616.6305</v>
+        <v>2863124877.913214</v>
       </c>
       <c r="G44" s="3">
-        <v>59426353759.1616</v>
+        <v>2858921549.867434</v>
       </c>
       <c r="H44" s="3">
-        <v>59584899351.43102</v>
+        <v>2909973720.400781</v>
       </c>
       <c r="I44" s="3">
-        <v>59821673615.33611</v>
+        <v>2973788933.567464</v>
       </c>
       <c r="J44" s="3">
-        <v>60230612433.13</v>
+        <v>3037604146.73415</v>
       </c>
       <c r="K44" s="3">
-        <v>60845803965.30045</v>
+        <v>3088656317.267495</v>
       </c>
       <c r="L44" s="3">
-        <v>61635607559.62009</v>
+        <v>3165234573.067517</v>
       </c>
       <c r="M44" s="3">
-        <v>62563317470.77316</v>
+        <v>3229049786.2342</v>
       </c>
       <c r="N44" s="3">
-        <v>63621192211.56274</v>
+        <v>3292864999.400885</v>
       </c>
       <c r="O44" s="3">
-        <v>64774384990.14632</v>
+        <v>3356680212.567567</v>
       </c>
       <c r="P44" s="3">
-        <v>65990318228.44353</v>
+        <v>3433258468.367589</v>
       </c>
       <c r="Q44" s="3">
-        <v>67261427826.00018</v>
+        <v>3497073681.534271</v>
       </c>
       <c r="R44" s="3">
-        <v>804004417755.1992</v>
+        <v>40492515632.4274</v>
       </c>
     </row>
     <row r="45" spans="1:18">
@@ -16966,46 +16966,46 @@
         <v>0</v>
       </c>
       <c r="E45" s="3">
-        <v>550886798.978663</v>
+        <v>59010443727.66352</v>
       </c>
       <c r="F45" s="3">
-        <v>553493130.8700848</v>
+        <v>59238382616.6305</v>
       </c>
       <c r="G45" s="3">
-        <v>558594778.3392249</v>
+        <v>59426353759.1616</v>
       </c>
       <c r="H45" s="3">
-        <v>565309893.0017341</v>
+        <v>59584899351.43102</v>
       </c>
       <c r="I45" s="3">
-        <v>573526506.703522</v>
+        <v>59821673615.33611</v>
       </c>
       <c r="J45" s="3">
-        <v>583071987.7818178</v>
+        <v>60230612433.13</v>
       </c>
       <c r="K45" s="3">
-        <v>593138214.4618096</v>
+        <v>60845803965.30045</v>
       </c>
       <c r="L45" s="3">
-        <v>604187791.6373742</v>
+        <v>61635607559.62009</v>
       </c>
       <c r="M45" s="3">
-        <v>616015959.5233783</v>
+        <v>62563317470.77316</v>
       </c>
       <c r="N45" s="3">
-        <v>628168784.0985376</v>
+        <v>63621192211.56274</v>
       </c>
       <c r="O45" s="3">
-        <v>640529887.858981</v>
+        <v>64774384990.14632</v>
       </c>
       <c r="P45" s="3">
-        <v>653481084.7038864</v>
+        <v>65990318228.44353</v>
       </c>
       <c r="Q45" s="3">
-        <v>666681880.1555153</v>
+        <v>67261427826.00018</v>
       </c>
       <c r="R45" s="3">
-        <v>7787086698.114529</v>
+        <v>804004417755.1992</v>
       </c>
     </row>
     <row r="46" spans="1:18">
@@ -17022,46 +17022,46 @@
         <v>0</v>
       </c>
       <c r="E46" s="3">
-        <v>385811020.4889482</v>
+        <v>550886798.978663</v>
       </c>
       <c r="F46" s="3">
-        <v>393577984.022957</v>
+        <v>553493130.8700848</v>
       </c>
       <c r="G46" s="3">
-        <v>401332410.1549103</v>
+        <v>558594778.3392249</v>
       </c>
       <c r="H46" s="3">
-        <v>408568979.0064408</v>
+        <v>565309893.0017341</v>
       </c>
       <c r="I46" s="3">
-        <v>417376543.61866</v>
+        <v>573526506.703522</v>
       </c>
       <c r="J46" s="3">
-        <v>426341415.3563595</v>
+        <v>583071987.7818178</v>
       </c>
       <c r="K46" s="3">
-        <v>433694543.1925827</v>
+        <v>593138214.4618096</v>
       </c>
       <c r="L46" s="3">
-        <v>444131769.0192203</v>
+        <v>604187791.6373742</v>
       </c>
       <c r="M46" s="3">
-        <v>453258359.6934142</v>
+        <v>616015959.5233783</v>
       </c>
       <c r="N46" s="3">
-        <v>462244716.8475319</v>
+        <v>628168784.0985376</v>
       </c>
       <c r="O46" s="3">
-        <v>471221614.2471001</v>
+        <v>640529887.858981</v>
       </c>
       <c r="P46" s="3">
-        <v>481820194.118144</v>
+        <v>653481084.7038864</v>
       </c>
       <c r="Q46" s="3">
-        <v>490957667.4032573</v>
+        <v>666681880.1555153</v>
       </c>
       <c r="R46" s="3">
-        <v>5670337217.169526</v>
+        <v>7787086698.114529</v>
       </c>
     </row>
     <row r="47" spans="1:18">
@@ -17078,46 +17078,46 @@
         <v>0</v>
       </c>
       <c r="E47" s="3">
-        <v>230913108.9920408</v>
+        <v>385811020.4889482</v>
       </c>
       <c r="F47" s="3">
-        <v>214016878.5984456</v>
+        <v>393577984.022957</v>
       </c>
       <c r="G47" s="3">
-        <v>148630843.675634</v>
+        <v>401332410.1549103</v>
       </c>
       <c r="H47" s="3">
-        <v>151284965.8841275</v>
+        <v>408568979.0064408</v>
       </c>
       <c r="I47" s="3">
-        <v>154602618.6447443</v>
+        <v>417376543.61866</v>
       </c>
       <c r="J47" s="3">
-        <v>157920271.4053611</v>
+        <v>426341415.3563595</v>
       </c>
       <c r="K47" s="3">
-        <v>160574393.6138546</v>
+        <v>433694543.1925827</v>
       </c>
       <c r="L47" s="3">
-        <v>164555576.9265949</v>
+        <v>444131769.0192203</v>
       </c>
       <c r="M47" s="3">
-        <v>167873229.6872117</v>
+        <v>453258359.6934142</v>
       </c>
       <c r="N47" s="3">
-        <v>171190882.4478285</v>
+        <v>462244716.8475319</v>
       </c>
       <c r="O47" s="3">
-        <v>174508535.2084453</v>
+        <v>471221614.2471001</v>
       </c>
       <c r="P47" s="3">
-        <v>178489718.5211855</v>
+        <v>481820194.118144</v>
       </c>
       <c r="Q47" s="3">
-        <v>181807371.2818024</v>
+        <v>490957667.4032573</v>
       </c>
       <c r="R47" s="3">
-        <v>2256368394.887276</v>
+        <v>5670337217.169526</v>
       </c>
     </row>
     <row r="48" spans="1:18">
@@ -17134,46 +17134,46 @@
         <v>0</v>
       </c>
       <c r="E48" s="3">
-        <v>509947269.5238243</v>
+        <v>230913108.9920408</v>
       </c>
       <c r="F48" s="3">
-        <v>514382574.9511451</v>
+        <v>214016878.5984456</v>
       </c>
       <c r="G48" s="3">
-        <v>510284117.0836095</v>
+        <v>148630843.675634</v>
       </c>
       <c r="H48" s="3">
-        <v>519562010.1214934</v>
+        <v>151284965.8841275</v>
       </c>
       <c r="I48" s="3">
-        <v>528839903.1593772</v>
+        <v>154602618.6447443</v>
       </c>
       <c r="J48" s="3">
-        <v>540437269.456732</v>
+        <v>157920271.4053611</v>
       </c>
       <c r="K48" s="3">
-        <v>552034635.7540869</v>
+        <v>160574393.6138546</v>
       </c>
       <c r="L48" s="3">
-        <v>561312528.7919705</v>
+        <v>164555576.9265949</v>
       </c>
       <c r="M48" s="3">
-        <v>575229368.3487964</v>
+        <v>167873229.6872117</v>
       </c>
       <c r="N48" s="3">
-        <v>586826734.6461511</v>
+        <v>171190882.4478285</v>
       </c>
       <c r="O48" s="3">
-        <v>598424100.9435059</v>
+        <v>174508535.2084453</v>
       </c>
       <c r="P48" s="3">
-        <v>610021467.2408607</v>
+        <v>178489718.5211855</v>
       </c>
       <c r="Q48" s="3">
-        <v>623938306.7976865</v>
+        <v>181807371.2818024</v>
       </c>
       <c r="R48" s="3">
-        <v>7231240286.819241</v>
+        <v>2256368394.887276</v>
       </c>
     </row>
     <row r="49" spans="1:18">
@@ -17190,46 +17190,46 @@
         <v>0</v>
       </c>
       <c r="E49" s="3">
-        <v>77688.54978406691</v>
+        <v>509947269.5238243</v>
       </c>
       <c r="F49" s="3">
-        <v>74335.96520844771</v>
+        <v>514382574.9511451</v>
       </c>
       <c r="G49" s="3">
-        <v>59928.22701223918</v>
+        <v>510284117.0836095</v>
       </c>
       <c r="H49" s="3">
-        <v>60998.37392317203</v>
+        <v>519562010.1214934</v>
       </c>
       <c r="I49" s="3">
-        <v>62336.05756183807</v>
+        <v>528839903.1593772</v>
       </c>
       <c r="J49" s="3">
-        <v>63673.74120050411</v>
+        <v>540437269.456732</v>
       </c>
       <c r="K49" s="3">
-        <v>64743.88811143697</v>
+        <v>552034635.7540869</v>
       </c>
       <c r="L49" s="3">
-        <v>66349.10847783624</v>
+        <v>561312528.7919705</v>
       </c>
       <c r="M49" s="3">
-        <v>67686.79211650229</v>
+        <v>575229368.3487964</v>
       </c>
       <c r="N49" s="3">
-        <v>69024.47575516834</v>
+        <v>586826734.6461511</v>
       </c>
       <c r="O49" s="3">
-        <v>70362.15939383442</v>
+        <v>598424100.9435059</v>
       </c>
       <c r="P49" s="3">
-        <v>71967.37976023366</v>
+        <v>610021467.2408607</v>
       </c>
       <c r="Q49" s="3">
-        <v>73305.0633988997</v>
+        <v>623938306.7976865</v>
       </c>
       <c r="R49" s="3">
-        <v>882399.7817041797</v>
+        <v>7231240286.819241</v>
       </c>
     </row>
     <row r="50" spans="1:18">
@@ -17246,46 +17246,46 @@
         <v>0</v>
       </c>
       <c r="E50" s="3">
-        <v>85451123743.9299</v>
+        <v>77688.54978406691</v>
       </c>
       <c r="F50" s="3">
-        <v>85510250031.38475</v>
+        <v>74335.96520844771</v>
       </c>
       <c r="G50" s="3">
-        <v>85575258223.2906</v>
+        <v>59928.22701223918</v>
       </c>
       <c r="H50" s="3">
-        <v>86111231123.35857</v>
+        <v>60998.37392317203</v>
       </c>
       <c r="I50" s="3">
-        <v>86830555476.49335</v>
+        <v>62336.05756183807</v>
       </c>
       <c r="J50" s="3">
-        <v>87760907916.89471</v>
+        <v>63673.74120050411</v>
       </c>
       <c r="K50" s="3">
-        <v>88846868984.6971</v>
+        <v>64743.88811143697</v>
       </c>
       <c r="L50" s="3">
-        <v>90241702534.94495</v>
+        <v>66349.10847783624</v>
       </c>
       <c r="M50" s="3">
-        <v>91747292494.02652</v>
+        <v>67686.79211650229</v>
       </c>
       <c r="N50" s="3">
-        <v>93379782887.38736</v>
+        <v>69024.47575516834</v>
       </c>
       <c r="O50" s="3">
-        <v>95111730313.55669</v>
+        <v>70362.15939383442</v>
       </c>
       <c r="P50" s="3">
-        <v>96980136118.90689</v>
+        <v>71967.37976023366</v>
       </c>
       <c r="Q50" s="3">
-        <v>98856090473.16951</v>
+        <v>73305.0633988997</v>
       </c>
       <c r="R50" s="3">
-        <v>1172402930322.041</v>
+        <v>882399.7817041797</v>
       </c>
     </row>
     <row r="51" spans="1:18">
@@ -17318,46 +17318,46 @@
         <v>0</v>
       </c>
       <c r="E52" s="3">
-        <v>22748381805.20618</v>
+        <v>85451123743.9299</v>
       </c>
       <c r="F52" s="3">
-        <v>22520353600.47911</v>
+        <v>85510250031.38475</v>
       </c>
       <c r="G52" s="3">
-        <v>22473745657.09102</v>
+        <v>85575258223.2906</v>
       </c>
       <c r="H52" s="3">
-        <v>22788709163.15194</v>
+        <v>86111231123.35857</v>
       </c>
       <c r="I52" s="3">
-        <v>23195438106.64322</v>
+        <v>86830555476.49335</v>
       </c>
       <c r="J52" s="3">
-        <v>23637539550.00182</v>
+        <v>87760907916.89471</v>
       </c>
       <c r="K52" s="3">
-        <v>24040291257.60387</v>
+        <v>88846868984.6971</v>
       </c>
       <c r="L52" s="3">
-        <v>24554869924.81215</v>
+        <v>90241702534.94495</v>
       </c>
       <c r="M52" s="3">
-        <v>25048997352.36107</v>
+        <v>91747292494.02652</v>
       </c>
       <c r="N52" s="3">
-        <v>25541714967.60299</v>
+        <v>93379782887.38736</v>
       </c>
       <c r="O52" s="3">
-        <v>26038353838.91957</v>
+        <v>95111730313.55669</v>
       </c>
       <c r="P52" s="3">
-        <v>26596315378.36823</v>
+        <v>96980136118.90689</v>
       </c>
       <c r="Q52" s="3">
-        <v>27116045769.73991</v>
+        <v>98856090473.16951</v>
       </c>
       <c r="R52" s="3">
-        <v>316300756371.9811</v>
+        <v>1172402930322.041</v>
       </c>
     </row>
     <row r="53" spans="1:18">
@@ -17374,46 +17374,46 @@
         <v>0</v>
       </c>
       <c r="E53" s="3">
-        <v>2786284365.504835</v>
+        <v>22748381805.20618</v>
       </c>
       <c r="F53" s="3">
-        <v>2863124877.913214</v>
+        <v>22520353600.47911</v>
       </c>
       <c r="G53" s="3">
-        <v>2858921549.867434</v>
+        <v>22473745657.09102</v>
       </c>
       <c r="H53" s="3">
-        <v>2909973720.400781</v>
+        <v>22788709163.15194</v>
       </c>
       <c r="I53" s="3">
-        <v>2973788933.567464</v>
+        <v>23195438106.64322</v>
       </c>
       <c r="J53" s="3">
-        <v>3037604146.73415</v>
+        <v>23637539550.00182</v>
       </c>
       <c r="K53" s="3">
-        <v>3088656317.267495</v>
+        <v>24040291257.60387</v>
       </c>
       <c r="L53" s="3">
-        <v>3165234573.067517</v>
+        <v>24554869924.81215</v>
       </c>
       <c r="M53" s="3">
-        <v>3229049786.2342</v>
+        <v>25048997352.36107</v>
       </c>
       <c r="N53" s="3">
-        <v>3292864999.400885</v>
+        <v>25541714967.60299</v>
       </c>
       <c r="O53" s="3">
-        <v>3356680212.567567</v>
+        <v>26038353838.91957</v>
       </c>
       <c r="P53" s="3">
-        <v>3433258468.367589</v>
+        <v>26596315378.36823</v>
       </c>
       <c r="Q53" s="3">
-        <v>3497073681.534271</v>
+        <v>27116045769.73991</v>
       </c>
       <c r="R53" s="3">
-        <v>40492515632.4274</v>
+        <v>316300756371.9811</v>
       </c>
     </row>
     <row r="54" spans="1:18">
@@ -17430,46 +17430,46 @@
         <v>0</v>
       </c>
       <c r="E54" s="3">
-        <v>59010443727.66352</v>
+        <v>2786284365.504835</v>
       </c>
       <c r="F54" s="3">
-        <v>59238382616.6305</v>
+        <v>2863124877.913214</v>
       </c>
       <c r="G54" s="3">
-        <v>59426353759.1616</v>
+        <v>2858921549.867434</v>
       </c>
       <c r="H54" s="3">
-        <v>59584899351.43102</v>
+        <v>2909973720.400781</v>
       </c>
       <c r="I54" s="3">
-        <v>59821673615.33611</v>
+        <v>2973788933.567464</v>
       </c>
       <c r="J54" s="3">
-        <v>60230612433.13</v>
+        <v>3037604146.73415</v>
       </c>
       <c r="K54" s="3">
-        <v>60845803965.30045</v>
+        <v>3088656317.267495</v>
       </c>
       <c r="L54" s="3">
-        <v>61635607559.62009</v>
+        <v>3165234573.067517</v>
       </c>
       <c r="M54" s="3">
-        <v>62563317470.77316</v>
+        <v>3229049786.2342</v>
       </c>
       <c r="N54" s="3">
-        <v>63621192211.56274</v>
+        <v>3292864999.400885</v>
       </c>
       <c r="O54" s="3">
-        <v>64774384990.14632</v>
+        <v>3356680212.567567</v>
       </c>
       <c r="P54" s="3">
-        <v>65990318228.44353</v>
+        <v>3433258468.367589</v>
       </c>
       <c r="Q54" s="3">
-        <v>67261427826.00018</v>
+        <v>3497073681.534271</v>
       </c>
       <c r="R54" s="3">
-        <v>804004417755.1992</v>
+        <v>40492515632.4274</v>
       </c>
     </row>
     <row r="55" spans="1:18">
@@ -17486,46 +17486,46 @@
         <v>0</v>
       </c>
       <c r="E55" s="3">
-        <v>550886798.978663</v>
+        <v>59010443727.66352</v>
       </c>
       <c r="F55" s="3">
-        <v>553493130.8700848</v>
+        <v>59238382616.6305</v>
       </c>
       <c r="G55" s="3">
-        <v>558594778.3392249</v>
+        <v>59426353759.1616</v>
       </c>
       <c r="H55" s="3">
-        <v>565309893.0017341</v>
+        <v>59584899351.43102</v>
       </c>
       <c r="I55" s="3">
-        <v>573526506.703522</v>
+        <v>59821673615.33611</v>
       </c>
       <c r="J55" s="3">
-        <v>583071987.7818178</v>
+        <v>60230612433.13</v>
       </c>
       <c r="K55" s="3">
-        <v>593138214.4618096</v>
+        <v>60845803965.30045</v>
       </c>
       <c r="L55" s="3">
-        <v>604187791.6373742</v>
+        <v>61635607559.62009</v>
       </c>
       <c r="M55" s="3">
-        <v>616015959.5233783</v>
+        <v>62563317470.77316</v>
       </c>
       <c r="N55" s="3">
-        <v>628168784.0985376</v>
+        <v>63621192211.56274</v>
       </c>
       <c r="O55" s="3">
-        <v>640529887.858981</v>
+        <v>64774384990.14632</v>
       </c>
       <c r="P55" s="3">
-        <v>653481084.7038864</v>
+        <v>65990318228.44353</v>
       </c>
       <c r="Q55" s="3">
-        <v>666681880.1555153</v>
+        <v>67261427826.00018</v>
       </c>
       <c r="R55" s="3">
-        <v>7787086698.114529</v>
+        <v>804004417755.1992</v>
       </c>
     </row>
     <row r="56" spans="1:18">
@@ -17542,46 +17542,46 @@
         <v>0</v>
       </c>
       <c r="E56" s="3">
-        <v>385811020.4889482</v>
+        <v>550886798.978663</v>
       </c>
       <c r="F56" s="3">
-        <v>393577984.022957</v>
+        <v>553493130.8700848</v>
       </c>
       <c r="G56" s="3">
-        <v>401332410.1549103</v>
+        <v>558594778.3392249</v>
       </c>
       <c r="H56" s="3">
-        <v>408568979.0064408</v>
+        <v>565309893.0017341</v>
       </c>
       <c r="I56" s="3">
-        <v>417376543.61866</v>
+        <v>573526506.703522</v>
       </c>
       <c r="J56" s="3">
-        <v>426341415.3563595</v>
+        <v>583071987.7818178</v>
       </c>
       <c r="K56" s="3">
-        <v>433694543.1925827</v>
+        <v>593138214.4618096</v>
       </c>
       <c r="L56" s="3">
-        <v>444131769.0192203</v>
+        <v>604187791.6373742</v>
       </c>
       <c r="M56" s="3">
-        <v>453258359.6934142</v>
+        <v>616015959.5233783</v>
       </c>
       <c r="N56" s="3">
-        <v>462244716.8475319</v>
+        <v>628168784.0985376</v>
       </c>
       <c r="O56" s="3">
-        <v>471221614.2471001</v>
+        <v>640529887.858981</v>
       </c>
       <c r="P56" s="3">
-        <v>481820194.118144</v>
+        <v>653481084.7038864</v>
       </c>
       <c r="Q56" s="3">
-        <v>490957667.4032573</v>
+        <v>666681880.1555153</v>
       </c>
       <c r="R56" s="3">
-        <v>5670337217.169526</v>
+        <v>7787086698.114529</v>
       </c>
     </row>
     <row r="57" spans="1:18">
@@ -17598,46 +17598,46 @@
         <v>0</v>
       </c>
       <c r="E57" s="3">
-        <v>230913108.9920408</v>
+        <v>385811020.4889482</v>
       </c>
       <c r="F57" s="3">
-        <v>214016878.5984456</v>
+        <v>393577984.022957</v>
       </c>
       <c r="G57" s="3">
-        <v>148630843.675634</v>
+        <v>401332410.1549103</v>
       </c>
       <c r="H57" s="3">
-        <v>151284965.8841275</v>
+        <v>408568979.0064408</v>
       </c>
       <c r="I57" s="3">
-        <v>154602618.6447443</v>
+        <v>417376543.61866</v>
       </c>
       <c r="J57" s="3">
-        <v>157920271.4053611</v>
+        <v>426341415.3563595</v>
       </c>
       <c r="K57" s="3">
-        <v>160574393.6138546</v>
+        <v>433694543.1925827</v>
       </c>
       <c r="L57" s="3">
-        <v>164555576.9265949</v>
+        <v>444131769.0192203</v>
       </c>
       <c r="M57" s="3">
-        <v>167873229.6872117</v>
+        <v>453258359.6934142</v>
       </c>
       <c r="N57" s="3">
-        <v>171190882.4478285</v>
+        <v>462244716.8475319</v>
       </c>
       <c r="O57" s="3">
-        <v>174508535.2084453</v>
+        <v>471221614.2471001</v>
       </c>
       <c r="P57" s="3">
-        <v>178489718.5211855</v>
+        <v>481820194.118144</v>
       </c>
       <c r="Q57" s="3">
-        <v>181807371.2818024</v>
+        <v>490957667.4032573</v>
       </c>
       <c r="R57" s="3">
-        <v>2256368394.887276</v>
+        <v>5670337217.169526</v>
       </c>
     </row>
     <row r="58" spans="1:18">
@@ -17654,46 +17654,46 @@
         <v>0</v>
       </c>
       <c r="E58" s="3">
-        <v>509947269.5238243</v>
+        <v>230913108.9920408</v>
       </c>
       <c r="F58" s="3">
-        <v>514382574.9511451</v>
+        <v>214016878.5984456</v>
       </c>
       <c r="G58" s="3">
-        <v>510284117.0836095</v>
+        <v>148630843.675634</v>
       </c>
       <c r="H58" s="3">
-        <v>519562010.1214934</v>
+        <v>151284965.8841275</v>
       </c>
       <c r="I58" s="3">
-        <v>528839903.1593772</v>
+        <v>154602618.6447443</v>
       </c>
       <c r="J58" s="3">
-        <v>540437269.456732</v>
+        <v>157920271.4053611</v>
       </c>
       <c r="K58" s="3">
-        <v>552034635.7540869</v>
+        <v>160574393.6138546</v>
       </c>
       <c r="L58" s="3">
-        <v>561312528.7919705</v>
+        <v>164555576.9265949</v>
       </c>
       <c r="M58" s="3">
-        <v>575229368.3487964</v>
+        <v>167873229.6872117</v>
       </c>
       <c r="N58" s="3">
-        <v>586826734.6461511</v>
+        <v>171190882.4478285</v>
       </c>
       <c r="O58" s="3">
-        <v>598424100.9435059</v>
+        <v>174508535.2084453</v>
       </c>
       <c r="P58" s="3">
-        <v>610021467.2408607</v>
+        <v>178489718.5211855</v>
       </c>
       <c r="Q58" s="3">
-        <v>623938306.7976865</v>
+        <v>181807371.2818024</v>
       </c>
       <c r="R58" s="3">
-        <v>7231240286.819241</v>
+        <v>2256368394.887276</v>
       </c>
     </row>
     <row r="59" spans="1:18">
@@ -17710,46 +17710,46 @@
         <v>0</v>
       </c>
       <c r="E59" s="3">
-        <v>77688.54978406691</v>
+        <v>509947269.5238243</v>
       </c>
       <c r="F59" s="3">
-        <v>74335.96520844771</v>
+        <v>514382574.9511451</v>
       </c>
       <c r="G59" s="3">
-        <v>59928.22701223918</v>
+        <v>510284117.0836095</v>
       </c>
       <c r="H59" s="3">
-        <v>60998.37392317203</v>
+        <v>519562010.1214934</v>
       </c>
       <c r="I59" s="3">
-        <v>62336.05756183807</v>
+        <v>528839903.1593772</v>
       </c>
       <c r="J59" s="3">
-        <v>63673.74120050411</v>
+        <v>540437269.456732</v>
       </c>
       <c r="K59" s="3">
-        <v>64743.88811143697</v>
+        <v>552034635.7540869</v>
       </c>
       <c r="L59" s="3">
-        <v>66349.10847783624</v>
+        <v>561312528.7919705</v>
       </c>
       <c r="M59" s="3">
-        <v>67686.79211650229</v>
+        <v>575229368.3487964</v>
       </c>
       <c r="N59" s="3">
-        <v>69024.47575516834</v>
+        <v>586826734.6461511</v>
       </c>
       <c r="O59" s="3">
-        <v>70362.15939383442</v>
+        <v>598424100.9435059</v>
       </c>
       <c r="P59" s="3">
-        <v>71967.37976023366</v>
+        <v>610021467.2408607</v>
       </c>
       <c r="Q59" s="3">
-        <v>73305.0633988997</v>
+        <v>623938306.7976865</v>
       </c>
       <c r="R59" s="3">
-        <v>882399.7817041797</v>
+        <v>7231240286.819241</v>
       </c>
     </row>
     <row r="60" spans="1:18">
@@ -17766,46 +17766,46 @@
         <v>0</v>
       </c>
       <c r="E60" s="3">
-        <v>85451123743.9299</v>
+        <v>77688.54978406691</v>
       </c>
       <c r="F60" s="3">
-        <v>85510250031.38475</v>
+        <v>74335.96520844771</v>
       </c>
       <c r="G60" s="3">
-        <v>85575258223.2906</v>
+        <v>59928.22701223918</v>
       </c>
       <c r="H60" s="3">
-        <v>86111231123.35857</v>
+        <v>60998.37392317203</v>
       </c>
       <c r="I60" s="3">
-        <v>86830555476.49335</v>
+        <v>62336.05756183807</v>
       </c>
       <c r="J60" s="3">
-        <v>87760907916.89471</v>
+        <v>63673.74120050411</v>
       </c>
       <c r="K60" s="3">
-        <v>88846868984.6971</v>
+        <v>64743.88811143697</v>
       </c>
       <c r="L60" s="3">
-        <v>90241702534.94495</v>
+        <v>66349.10847783624</v>
       </c>
       <c r="M60" s="3">
-        <v>91747292494.02652</v>
+        <v>67686.79211650229</v>
       </c>
       <c r="N60" s="3">
-        <v>93379782887.38736</v>
+        <v>69024.47575516834</v>
       </c>
       <c r="O60" s="3">
-        <v>95111730313.55669</v>
+        <v>70362.15939383442</v>
       </c>
       <c r="P60" s="3">
-        <v>96980136118.90689</v>
+        <v>71967.37976023366</v>
       </c>
       <c r="Q60" s="3">
-        <v>98856090473.16951</v>
+        <v>73305.0633988997</v>
       </c>
       <c r="R60" s="3">
-        <v>1172402930322.041</v>
+        <v>882399.7817041797</v>
       </c>
     </row>
     <row r="61" spans="1:18">

--- a/tests/scen_results_test_2025_stillbirths.xlsx
+++ b/tests/scen_results_test_2025_stillbirths.xlsx
@@ -28,7 +28,7 @@
     <t>2.0.11</t>
   </si>
   <si>
-    <t>2025-06-30</t>
+    <t>2025-07-03</t>
   </si>
   <si>
     <t>Scenario</t>

--- a/tests/scen_results_test_2025_stillbirths.xlsx
+++ b/tests/scen_results_test_2025_stillbirths.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1015" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1060" uniqueCount="96">
   <si>
     <t>Version</t>
   </si>
@@ -25,10 +25,10 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2.0.11</t>
+    <t>2.1.0</t>
   </si>
   <si>
-    <t>2025-07-03</t>
+    <t>2025-07-15</t>
   </si>
   <si>
     <t>Scenario</t>
@@ -1694,8 +1694,8 @@
       <c r="Q18" s="3">
         <v>88.43911185492993</v>
       </c>
-      <c r="R18" s="3">
-        <v>1157.198578217362</v>
+      <c r="R18" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -3278,8 +3278,8 @@
       <c r="Q47" s="3">
         <v>88.43911185492993</v>
       </c>
-      <c r="R47" s="3">
-        <v>1157.198578217362</v>
+      <c r="R47" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="48" spans="1:18">
@@ -4862,8 +4862,8 @@
       <c r="Q76" s="3">
         <v>88.43911185492993</v>
       </c>
-      <c r="R76" s="3">
-        <v>1157.198578217362</v>
+      <c r="R76" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="77" spans="1:18">
@@ -6446,8 +6446,8 @@
       <c r="Q105" s="3">
         <v>85.19511506291421</v>
       </c>
-      <c r="R105" s="3">
-        <v>1125.074011717089</v>
+      <c r="R105" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="106" spans="1:18">
@@ -8030,8 +8030,8 @@
       <c r="Q134" s="3">
         <v>85.19511506291421</v>
       </c>
-      <c r="R134" s="3">
-        <v>1125.074011717089</v>
+      <c r="R134" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="135" spans="1:18">
@@ -9614,8 +9614,8 @@
       <c r="Q163" s="3">
         <v>85.19511506291421</v>
       </c>
-      <c r="R163" s="3">
-        <v>1125.074011717089</v>
+      <c r="R163" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="164" spans="1:18">
@@ -12445,7 +12445,9 @@
       </c>
     </row>
     <row r="40" spans="1:18">
-      <c r="A40" s="2"/>
+      <c r="A40" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B40" s="3" t="s">
         <v>45</v>
       </c>
@@ -12499,7 +12501,9 @@
       </c>
     </row>
     <row r="41" spans="1:18">
-      <c r="A41" s="2"/>
+      <c r="A41" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B41" s="3" t="s">
         <v>48</v>
       </c>
@@ -12553,7 +12557,9 @@
       </c>
     </row>
     <row r="42" spans="1:18">
-      <c r="A42" s="2"/>
+      <c r="A42" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B42" s="3" t="s">
         <v>49</v>
       </c>
@@ -12607,7 +12613,9 @@
       </c>
     </row>
     <row r="43" spans="1:18">
-      <c r="A43" s="2"/>
+      <c r="A43" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B43" s="3" t="s">
         <v>50</v>
       </c>
@@ -12661,7 +12669,9 @@
       </c>
     </row>
     <row r="44" spans="1:18">
-      <c r="A44" s="2"/>
+      <c r="A44" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B44" s="3" t="s">
         <v>51</v>
       </c>
@@ -12715,7 +12725,9 @@
       </c>
     </row>
     <row r="45" spans="1:18">
-      <c r="A45" s="2"/>
+      <c r="A45" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B45" s="3" t="s">
         <v>52</v>
       </c>
@@ -12769,7 +12781,9 @@
       </c>
     </row>
     <row r="46" spans="1:18">
-      <c r="A46" s="2"/>
+      <c r="A46" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B46" s="3" t="s">
         <v>53</v>
       </c>
@@ -12823,7 +12837,9 @@
       </c>
     </row>
     <row r="47" spans="1:18">
-      <c r="A47" s="2"/>
+      <c r="A47" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B47" s="3" t="s">
         <v>54</v>
       </c>
@@ -12877,7 +12893,9 @@
       </c>
     </row>
     <row r="48" spans="1:18">
-      <c r="A48" s="2"/>
+      <c r="A48" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B48" s="3" t="s">
         <v>55</v>
       </c>
@@ -12931,7 +12949,9 @@
       </c>
     </row>
     <row r="49" spans="1:18">
-      <c r="A49" s="2"/>
+      <c r="A49" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B49" s="3" t="s">
         <v>56</v>
       </c>
@@ -12985,7 +13005,9 @@
       </c>
     </row>
     <row r="50" spans="1:18">
-      <c r="A50" s="2"/>
+      <c r="A50" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B50" s="3" t="s">
         <v>57</v>
       </c>
@@ -13039,7 +13061,9 @@
       </c>
     </row>
     <row r="51" spans="1:18">
-      <c r="A51" s="2"/>
+      <c r="A51" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B51" s="3" t="s">
         <v>58</v>
       </c>
@@ -13093,7 +13117,9 @@
       </c>
     </row>
     <row r="52" spans="1:18">
-      <c r="A52" s="2"/>
+      <c r="A52" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B52" s="3" t="s">
         <v>59</v>
       </c>
@@ -13147,7 +13173,9 @@
       </c>
     </row>
     <row r="53" spans="1:18">
-      <c r="A53" s="2"/>
+      <c r="A53" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B53" s="3" t="s">
         <v>60</v>
       </c>
@@ -13201,7 +13229,9 @@
       </c>
     </row>
     <row r="54" spans="1:18">
-      <c r="A54" s="2"/>
+      <c r="A54" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B54" s="3" t="s">
         <v>61</v>
       </c>
@@ -13255,7 +13285,9 @@
       </c>
     </row>
     <row r="55" spans="1:18">
-      <c r="A55" s="2"/>
+      <c r="A55" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B55" s="3" t="s">
         <v>62</v>
       </c>
@@ -13309,7 +13341,9 @@
       </c>
     </row>
     <row r="56" spans="1:18">
-      <c r="A56" s="2"/>
+      <c r="A56" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B56" s="3" t="s">
         <v>63</v>
       </c>
@@ -13363,7 +13397,9 @@
       </c>
     </row>
     <row r="57" spans="1:18">
-      <c r="A57" s="2"/>
+      <c r="A57" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B57" s="3" t="s">
         <v>64</v>
       </c>
@@ -13417,7 +13453,9 @@
       </c>
     </row>
     <row r="58" spans="1:18">
-      <c r="A58" s="2"/>
+      <c r="A58" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B58" s="3" t="s">
         <v>65</v>
       </c>
@@ -13471,7 +13509,9 @@
       </c>
     </row>
     <row r="59" spans="1:18">
-      <c r="A59" s="2"/>
+      <c r="A59" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B59" s="3" t="s">
         <v>66</v>
       </c>
@@ -13525,7 +13565,9 @@
       </c>
     </row>
     <row r="60" spans="1:18">
-      <c r="A60" s="2"/>
+      <c r="A60" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B60" s="3" t="s">
         <v>67</v>
       </c>
@@ -13579,7 +13621,9 @@
       </c>
     </row>
     <row r="61" spans="1:18">
-      <c r="A61" s="2"/>
+      <c r="A61" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B61" s="3" t="s">
         <v>68</v>
       </c>
@@ -13633,7 +13677,9 @@
       </c>
     </row>
     <row r="62" spans="1:18">
-      <c r="A62" s="2"/>
+      <c r="A62" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B62" s="3" t="s">
         <v>69</v>
       </c>
@@ -13687,7 +13733,9 @@
       </c>
     </row>
     <row r="63" spans="1:18">
-      <c r="A63" s="2"/>
+      <c r="A63" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B63" s="3" t="s">
         <v>70</v>
       </c>
@@ -13741,7 +13789,9 @@
       </c>
     </row>
     <row r="64" spans="1:18">
-      <c r="A64" s="2"/>
+      <c r="A64" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B64" s="3" t="s">
         <v>71</v>
       </c>
@@ -13795,7 +13845,9 @@
       </c>
     </row>
     <row r="65" spans="1:18">
-      <c r="A65" s="2"/>
+      <c r="A65" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B65" s="3" t="s">
         <v>72</v>
       </c>
@@ -13849,7 +13901,9 @@
       </c>
     </row>
     <row r="66" spans="1:18">
-      <c r="A66" s="2"/>
+      <c r="A66" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B66" s="3" t="s">
         <v>73</v>
       </c>
@@ -13903,7 +13957,9 @@
       </c>
     </row>
     <row r="67" spans="1:18">
-      <c r="A67" s="2"/>
+      <c r="A67" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B67" s="3" t="s">
         <v>74</v>
       </c>
@@ -13957,7 +14013,9 @@
       </c>
     </row>
     <row r="68" spans="1:18">
-      <c r="A68" s="2"/>
+      <c r="A68" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B68" s="3" t="s">
         <v>75</v>
       </c>
@@ -14011,7 +14069,9 @@
       </c>
     </row>
     <row r="69" spans="1:18">
-      <c r="A69" s="2"/>
+      <c r="A69" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B69" s="3" t="s">
         <v>76</v>
       </c>
@@ -14065,7 +14125,9 @@
       </c>
     </row>
     <row r="70" spans="1:18">
-      <c r="A70" s="2"/>
+      <c r="A70" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B70" s="3" t="s">
         <v>77</v>
       </c>
@@ -14119,7 +14181,9 @@
       </c>
     </row>
     <row r="71" spans="1:18">
-      <c r="A71" s="2"/>
+      <c r="A71" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B71" s="3" t="s">
         <v>78</v>
       </c>
@@ -14173,7 +14237,9 @@
       </c>
     </row>
     <row r="72" spans="1:18">
-      <c r="A72" s="2"/>
+      <c r="A72" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B72" s="3" t="s">
         <v>79</v>
       </c>
@@ -14227,7 +14293,9 @@
       </c>
     </row>
     <row r="73" spans="1:18">
-      <c r="A73" s="2"/>
+      <c r="A73" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B73" s="3" t="s">
         <v>80</v>
       </c>
@@ -14281,7 +14349,9 @@
       </c>
     </row>
     <row r="74" spans="1:18">
-      <c r="A74" s="2"/>
+      <c r="A74" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B74" s="3" t="s">
         <v>81</v>
       </c>
@@ -14335,7 +14405,9 @@
       </c>
     </row>
     <row r="75" spans="1:18">
-      <c r="A75" s="2"/>
+      <c r="A75" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B75" s="3" t="s">
         <v>82</v>
       </c>
@@ -14389,7 +14461,9 @@
       </c>
     </row>
     <row r="76" spans="1:18">
-      <c r="A76" s="2"/>
+      <c r="A76" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B76" s="3" t="s">
         <v>83</v>
       </c>
@@ -14443,7 +14517,9 @@
       </c>
     </row>
     <row r="77" spans="1:18">
-      <c r="A77" s="2"/>
+      <c r="A77" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B77" s="3" t="s">
         <v>84</v>
       </c>
@@ -14569,7 +14645,9 @@
       </c>
     </row>
     <row r="80" spans="1:18">
-      <c r="A80" s="2"/>
+      <c r="A80" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="B80" s="3" t="s">
         <v>72</v>
       </c>

--- a/tests/scen_results_test_2025_stillbirths.xlsx
+++ b/tests/scen_results_test_2025_stillbirths.xlsx
@@ -28,7 +28,7 @@
     <t>2.1.0</t>
   </si>
   <si>
-    <t>2025-07-15</t>
+    <t>2025-07-23</t>
   </si>
   <si>
     <t>Scenario</t>

--- a/tests/scen_results_test_2025_stillbirths.xlsx
+++ b/tests/scen_results_test_2025_stillbirths.xlsx
@@ -28,7 +28,7 @@
     <t>2.1.0</t>
   </si>
   <si>
-    <t>2025-07-23</t>
+    <t>2025-07-29</t>
   </si>
   <si>
     <t>Scenario</t>
